--- a/datasets/local-data/FoE-local-env-data-LAD-2026.xlsx
+++ b/datasets/local-data/FoE-local-env-data-LAD-2026.xlsx
@@ -158,19 +158,19 @@
     <t xml:space="preserve">Greenspace: m2 perpop tertile</t>
   </si>
   <si>
-    <t xml:space="preserve">Flooding (England): current high risk people</t>
+    <t xml:space="preserve">Flooding (England): current high risk properties</t>
   </si>
   <si>
-    <t xml:space="preserve">Flooding (England): current high risk properties</t>
+    <t xml:space="preserve">Flooding (England): future high risk properties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flooding (England): current high risk people</t>
   </si>
   <si>
     <t xml:space="preserve">Flooding (England): current high risk homes</t>
   </si>
   <si>
     <t xml:space="preserve">Flooding (England): future high risk people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flooding (England): future high risk properties</t>
   </si>
   <si>
     <t xml:space="preserve">Flooding (England): future high risk homes</t>
@@ -3097,19 +3097,19 @@
         <v>92</v>
       </c>
       <c r="AW2" s="5" t="n">
+        <v>2620</v>
+      </c>
+      <c r="AX2" s="5" t="n">
+        <v>5120</v>
+      </c>
+      <c r="AY2" s="5" t="n">
         <v>3590</v>
       </c>
-      <c r="AX2" s="5" t="n">
-        <v>2620</v>
-      </c>
-      <c r="AY2" s="5" t="n">
+      <c r="AZ2" s="5" t="n">
         <v>1660</v>
       </c>
-      <c r="AZ2" s="5" t="n">
+      <c r="BA2" s="5" t="n">
         <v>7190</v>
-      </c>
-      <c r="BA2" s="5" t="n">
-        <v>5120</v>
       </c>
       <c r="BB2" s="5" t="n">
         <v>3360</v>
@@ -3358,19 +3358,19 @@
         <v>96</v>
       </c>
       <c r="AW3" s="5" t="n">
+        <v>3090</v>
+      </c>
+      <c r="AX3" s="5" t="n">
+        <v>6240</v>
+      </c>
+      <c r="AY3" s="5" t="n">
         <v>4870</v>
       </c>
-      <c r="AX3" s="5" t="n">
-        <v>3090</v>
-      </c>
-      <c r="AY3" s="5" t="n">
+      <c r="AZ3" s="5" t="n">
         <v>2090</v>
       </c>
-      <c r="AZ3" s="5" t="n">
+      <c r="BA3" s="5" t="n">
         <v>9990</v>
-      </c>
-      <c r="BA3" s="5" t="n">
-        <v>6240</v>
       </c>
       <c r="BB3" s="5" t="n">
         <v>4290</v>
@@ -3619,19 +3619,19 @@
         <v>92</v>
       </c>
       <c r="AW4" s="5" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AX4" s="5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AY4" s="5" t="n">
         <v>8360</v>
       </c>
-      <c r="AX4" s="5" t="n">
-        <v>5300</v>
-      </c>
-      <c r="AY4" s="5" t="n">
+      <c r="AZ4" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="AZ4" s="5" t="n">
+      <c r="BA4" s="5" t="n">
         <v>14570</v>
-      </c>
-      <c r="BA4" s="5" t="n">
-        <v>9000</v>
       </c>
       <c r="BB4" s="5" t="n">
         <v>6650</v>
@@ -3829,7 +3829,7 @@
         <v>0.24</v>
       </c>
       <c r="AF5" s="5" t="n">
-        <v>5260</v>
+        <v>5250</v>
       </c>
       <c r="AG5" s="5" t="n">
         <v>692</v>
@@ -3880,19 +3880,19 @@
         <v>92</v>
       </c>
       <c r="AW5" s="5" t="n">
+        <v>4310</v>
+      </c>
+      <c r="AX5" s="5" t="n">
+        <v>9350</v>
+      </c>
+      <c r="AY5" s="5" t="n">
         <v>5870</v>
       </c>
-      <c r="AX5" s="5" t="n">
-        <v>4310</v>
-      </c>
-      <c r="AY5" s="5" t="n">
+      <c r="AZ5" s="5" t="n">
         <v>2690</v>
       </c>
-      <c r="AZ5" s="5" t="n">
+      <c r="BA5" s="5" t="n">
         <v>12420</v>
-      </c>
-      <c r="BA5" s="5" t="n">
-        <v>9350</v>
       </c>
       <c r="BB5" s="5" t="n">
         <v>5770</v>
@@ -4141,19 +4141,19 @@
         <v>96</v>
       </c>
       <c r="AW6" s="5" t="n">
+        <v>3070</v>
+      </c>
+      <c r="AX6" s="5" t="n">
+        <v>5530</v>
+      </c>
+      <c r="AY6" s="5" t="n">
         <v>4240</v>
       </c>
-      <c r="AX6" s="5" t="n">
-        <v>3070</v>
-      </c>
-      <c r="AY6" s="5" t="n">
+      <c r="AZ6" s="5" t="n">
         <v>1980</v>
       </c>
-      <c r="AZ6" s="5" t="n">
+      <c r="BA6" s="5" t="n">
         <v>7550</v>
-      </c>
-      <c r="BA6" s="5" t="n">
-        <v>5530</v>
       </c>
       <c r="BB6" s="5" t="n">
         <v>3600</v>
@@ -4351,7 +4351,7 @@
         <v>0.24</v>
       </c>
       <c r="AF7" s="5" t="n">
-        <v>2760</v>
+        <v>2740</v>
       </c>
       <c r="AG7" s="5" t="n">
         <v>256</v>
@@ -4402,19 +4402,19 @@
         <v>105</v>
       </c>
       <c r="AW7" s="5" t="n">
+        <v>2080</v>
+      </c>
+      <c r="AX7" s="5" t="n">
+        <v>4110</v>
+      </c>
+      <c r="AY7" s="5" t="n">
         <v>2620</v>
       </c>
-      <c r="AX7" s="5" t="n">
-        <v>2080</v>
-      </c>
-      <c r="AY7" s="5" t="n">
+      <c r="AZ7" s="5" t="n">
         <v>1170</v>
       </c>
-      <c r="AZ7" s="5" t="n">
+      <c r="BA7" s="5" t="n">
         <v>5510</v>
-      </c>
-      <c r="BA7" s="5" t="n">
-        <v>4110</v>
       </c>
       <c r="BB7" s="5" t="n">
         <v>2480</v>
@@ -4612,7 +4612,7 @@
         <v>0.37</v>
       </c>
       <c r="AF8" s="5" t="n">
-        <v>5540</v>
+        <v>5550</v>
       </c>
       <c r="AG8" s="5" t="n">
         <v>370</v>
@@ -4663,19 +4663,19 @@
         <v>105</v>
       </c>
       <c r="AW8" s="5" t="n">
+        <v>3860</v>
+      </c>
+      <c r="AX8" s="5" t="n">
+        <v>8900</v>
+      </c>
+      <c r="AY8" s="5" t="n">
         <v>5830</v>
       </c>
-      <c r="AX8" s="5" t="n">
-        <v>3860</v>
-      </c>
-      <c r="AY8" s="5" t="n">
+      <c r="AZ8" s="5" t="n">
         <v>2390</v>
       </c>
-      <c r="AZ8" s="5" t="n">
+      <c r="BA8" s="5" t="n">
         <v>14390</v>
-      </c>
-      <c r="BA8" s="5" t="n">
-        <v>8900</v>
       </c>
       <c r="BB8" s="5" t="n">
         <v>6050</v>
@@ -4924,19 +4924,19 @@
         <v>92</v>
       </c>
       <c r="AW9" s="5" t="n">
+        <v>4990</v>
+      </c>
+      <c r="AX9" s="5" t="n">
+        <v>7790</v>
+      </c>
+      <c r="AY9" s="5" t="n">
         <v>6260</v>
       </c>
-      <c r="AX9" s="5" t="n">
-        <v>4990</v>
-      </c>
-      <c r="AY9" s="5" t="n">
+      <c r="AZ9" s="5" t="n">
         <v>2520</v>
       </c>
-      <c r="AZ9" s="5" t="n">
+      <c r="BA9" s="5" t="n">
         <v>9510</v>
-      </c>
-      <c r="BA9" s="5" t="n">
-        <v>7790</v>
       </c>
       <c r="BB9" s="5" t="n">
         <v>3950</v>
@@ -5185,19 +5185,19 @@
         <v>96</v>
       </c>
       <c r="AW10" s="5" t="n">
+        <v>4450</v>
+      </c>
+      <c r="AX10" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="AY10" s="5" t="n">
         <v>5870</v>
       </c>
-      <c r="AX10" s="5" t="n">
-        <v>4450</v>
-      </c>
-      <c r="AY10" s="5" t="n">
+      <c r="AZ10" s="5" t="n">
         <v>2880</v>
       </c>
-      <c r="AZ10" s="5" t="n">
+      <c r="BA10" s="5" t="n">
         <v>11800</v>
-      </c>
-      <c r="BA10" s="5" t="n">
-        <v>8850</v>
       </c>
       <c r="BB10" s="5" t="n">
         <v>5680</v>
@@ -5446,19 +5446,19 @@
         <v>96</v>
       </c>
       <c r="AW11" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="AX11" s="5" t="n">
+        <v>14820</v>
+      </c>
+      <c r="AY11" s="5" t="n">
         <v>9170</v>
       </c>
-      <c r="AX11" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="AY11" s="5" t="n">
+      <c r="AZ11" s="5" t="n">
         <v>4120</v>
       </c>
-      <c r="AZ11" s="5" t="n">
+      <c r="BA11" s="5" t="n">
         <v>18940</v>
-      </c>
-      <c r="BA11" s="5" t="n">
-        <v>14820</v>
       </c>
       <c r="BB11" s="5" t="n">
         <v>8600</v>
@@ -5707,19 +5707,19 @@
         <v>92</v>
       </c>
       <c r="AW12" s="5" t="n">
+        <v>24210</v>
+      </c>
+      <c r="AX12" s="5" t="n">
+        <v>33490</v>
+      </c>
+      <c r="AY12" s="5" t="n">
         <v>32500</v>
       </c>
-      <c r="AX12" s="5" t="n">
-        <v>24210</v>
-      </c>
-      <c r="AY12" s="5" t="n">
+      <c r="AZ12" s="5" t="n">
         <v>14310</v>
       </c>
-      <c r="AZ12" s="5" t="n">
+      <c r="BA12" s="5" t="n">
         <v>43780</v>
-      </c>
-      <c r="BA12" s="5" t="n">
-        <v>33490</v>
       </c>
       <c r="BB12" s="5" t="n">
         <v>19590</v>
@@ -5917,7 +5917,7 @@
         <v>0.32</v>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>4070</v>
+        <v>4090</v>
       </c>
       <c r="AG13" s="5" t="n">
         <v>919</v>
@@ -5968,19 +5968,19 @@
         <v>96</v>
       </c>
       <c r="AW13" s="5" t="n">
+        <v>9090</v>
+      </c>
+      <c r="AX13" s="5" t="n">
+        <v>19630</v>
+      </c>
+      <c r="AY13" s="5" t="n">
         <v>9250</v>
       </c>
-      <c r="AX13" s="5" t="n">
-        <v>9090</v>
-      </c>
-      <c r="AY13" s="5" t="n">
+      <c r="AZ13" s="5" t="n">
         <v>4370</v>
       </c>
-      <c r="AZ13" s="5" t="n">
+      <c r="BA13" s="5" t="n">
         <v>25610</v>
-      </c>
-      <c r="BA13" s="5" t="n">
-        <v>19630</v>
       </c>
       <c r="BB13" s="5" t="n">
         <v>11740</v>
@@ -6178,7 +6178,7 @@
         <v>0.29</v>
       </c>
       <c r="AF14" s="5" t="n">
-        <v>7470</v>
+        <v>7450</v>
       </c>
       <c r="AG14" s="5" t="n">
         <v>1850</v>
@@ -6229,19 +6229,19 @@
         <v>105</v>
       </c>
       <c r="AW14" s="5" t="n">
+        <v>3560</v>
+      </c>
+      <c r="AX14" s="5" t="n">
+        <v>9290</v>
+      </c>
+      <c r="AY14" s="5" t="n">
         <v>3980</v>
       </c>
-      <c r="AX14" s="5" t="n">
-        <v>3560</v>
-      </c>
-      <c r="AY14" s="5" t="n">
+      <c r="AZ14" s="5" t="n">
         <v>1780</v>
       </c>
-      <c r="AZ14" s="5" t="n">
+      <c r="BA14" s="5" t="n">
         <v>10870</v>
-      </c>
-      <c r="BA14" s="5" t="n">
-        <v>9290</v>
       </c>
       <c r="BB14" s="5" t="n">
         <v>4900</v>
@@ -6490,19 +6490,19 @@
         <v>105</v>
       </c>
       <c r="AW15" s="5" t="n">
+        <v>4210</v>
+      </c>
+      <c r="AX15" s="5" t="n">
+        <v>10710</v>
+      </c>
+      <c r="AY15" s="5" t="n">
         <v>5670</v>
       </c>
-      <c r="AX15" s="5" t="n">
-        <v>4210</v>
-      </c>
-      <c r="AY15" s="5" t="n">
+      <c r="AZ15" s="5" t="n">
         <v>2490</v>
       </c>
-      <c r="AZ15" s="5" t="n">
+      <c r="BA15" s="5" t="n">
         <v>14510</v>
-      </c>
-      <c r="BA15" s="5" t="n">
-        <v>10710</v>
       </c>
       <c r="BB15" s="5" t="n">
         <v>6500</v>
@@ -6700,7 +6700,7 @@
         <v>0.26</v>
       </c>
       <c r="AF16" s="5" t="n">
-        <v>6810</v>
+        <v>6800</v>
       </c>
       <c r="AG16" s="5" t="n">
         <v>550</v>
@@ -6751,19 +6751,19 @@
         <v>96</v>
       </c>
       <c r="AW16" s="5" t="n">
+        <v>6260</v>
+      </c>
+      <c r="AX16" s="5" t="n">
+        <v>13160</v>
+      </c>
+      <c r="AY16" s="5" t="n">
         <v>9410</v>
       </c>
-      <c r="AX16" s="5" t="n">
-        <v>6260</v>
-      </c>
-      <c r="AY16" s="5" t="n">
+      <c r="AZ16" s="5" t="n">
         <v>3930</v>
       </c>
-      <c r="AZ16" s="5" t="n">
+      <c r="BA16" s="5" t="n">
         <v>18550</v>
-      </c>
-      <c r="BA16" s="5" t="n">
-        <v>13160</v>
       </c>
       <c r="BB16" s="5" t="n">
         <v>7700</v>
@@ -7012,19 +7012,19 @@
         <v>96</v>
       </c>
       <c r="AW17" s="5" t="n">
+        <v>9120</v>
+      </c>
+      <c r="AX17" s="5" t="n">
+        <v>19080</v>
+      </c>
+      <c r="AY17" s="5" t="n">
         <v>16110</v>
       </c>
-      <c r="AX17" s="5" t="n">
-        <v>9120</v>
-      </c>
-      <c r="AY17" s="5" t="n">
+      <c r="AZ17" s="5" t="n">
         <v>5560</v>
       </c>
-      <c r="AZ17" s="5" t="n">
+      <c r="BA17" s="5" t="n">
         <v>34230</v>
-      </c>
-      <c r="BA17" s="5" t="n">
-        <v>19080</v>
       </c>
       <c r="BB17" s="5" t="n">
         <v>11670</v>
@@ -7273,19 +7273,19 @@
         <v>92</v>
       </c>
       <c r="AW18" s="5" t="n">
+        <v>1030</v>
+      </c>
+      <c r="AX18" s="5" t="n">
+        <v>1550</v>
+      </c>
+      <c r="AY18" s="5" t="n">
         <v>890</v>
       </c>
-      <c r="AX18" s="5" t="n">
-        <v>1030</v>
-      </c>
-      <c r="AY18" s="5" t="n">
+      <c r="AZ18" s="5" t="n">
         <v>390</v>
       </c>
-      <c r="AZ18" s="5" t="n">
+      <c r="BA18" s="5" t="n">
         <v>1440</v>
-      </c>
-      <c r="BA18" s="5" t="n">
-        <v>1550</v>
       </c>
       <c r="BB18" s="5" t="n">
         <v>650</v>
@@ -7483,7 +7483,7 @@
         <v>0.48</v>
       </c>
       <c r="AF19" s="5" t="n">
-        <v>9370</v>
+        <v>9360</v>
       </c>
       <c r="AG19" s="5" t="n">
         <v>937</v>
@@ -7534,19 +7534,19 @@
         <v>96</v>
       </c>
       <c r="AW19" s="5" t="n">
+        <v>6980</v>
+      </c>
+      <c r="AX19" s="5" t="n">
+        <v>19270</v>
+      </c>
+      <c r="AY19" s="5" t="n">
         <v>10830</v>
       </c>
-      <c r="AX19" s="5" t="n">
-        <v>6980</v>
-      </c>
-      <c r="AY19" s="5" t="n">
+      <c r="AZ19" s="5" t="n">
         <v>3760</v>
       </c>
-      <c r="AZ19" s="5" t="n">
+      <c r="BA19" s="5" t="n">
         <v>27560</v>
-      </c>
-      <c r="BA19" s="5" t="n">
-        <v>19270</v>
       </c>
       <c r="BB19" s="5" t="n">
         <v>10440</v>
@@ -7795,19 +7795,19 @@
         <v>92</v>
       </c>
       <c r="AW20" s="5" t="n">
+        <v>8500</v>
+      </c>
+      <c r="AX20" s="5" t="n">
+        <v>13860</v>
+      </c>
+      <c r="AY20" s="5" t="n">
         <v>8270</v>
       </c>
-      <c r="AX20" s="5" t="n">
-        <v>8500</v>
-      </c>
-      <c r="AY20" s="5" t="n">
+      <c r="AZ20" s="5" t="n">
         <v>3570</v>
       </c>
-      <c r="AZ20" s="5" t="n">
+      <c r="BA20" s="5" t="n">
         <v>13750</v>
-      </c>
-      <c r="BA20" s="5" t="n">
-        <v>13860</v>
       </c>
       <c r="BB20" s="5" t="n">
         <v>6000</v>
@@ -8005,7 +8005,7 @@
         <v>0.47</v>
       </c>
       <c r="AF21" s="5" t="n">
-        <v>4780</v>
+        <v>4790</v>
       </c>
       <c r="AG21" s="5" t="n">
         <v>1182</v>
@@ -8056,19 +8056,19 @@
         <v>105</v>
       </c>
       <c r="AW21" s="5" t="n">
+        <v>3110</v>
+      </c>
+      <c r="AX21" s="5" t="n">
+        <v>6160</v>
+      </c>
+      <c r="AY21" s="5" t="n">
         <v>4500</v>
       </c>
-      <c r="AX21" s="5" t="n">
-        <v>3110</v>
-      </c>
-      <c r="AY21" s="5" t="n">
+      <c r="AZ21" s="5" t="n">
         <v>1870</v>
       </c>
-      <c r="AZ21" s="5" t="n">
+      <c r="BA21" s="5" t="n">
         <v>9340</v>
-      </c>
-      <c r="BA21" s="5" t="n">
-        <v>6160</v>
       </c>
       <c r="BB21" s="5" t="n">
         <v>3930</v>
@@ -8266,7 +8266,7 @@
         <v>0.21</v>
       </c>
       <c r="AF22" s="5" t="n">
-        <v>8670</v>
+        <v>8660</v>
       </c>
       <c r="AG22" s="5" t="n">
         <v>437</v>
@@ -8317,19 +8317,19 @@
         <v>105</v>
       </c>
       <c r="AW22" s="5" t="n">
+        <v>3850</v>
+      </c>
+      <c r="AX22" s="5" t="n">
+        <v>9030</v>
+      </c>
+      <c r="AY22" s="5" t="n">
         <v>5200</v>
       </c>
-      <c r="AX22" s="5" t="n">
-        <v>3850</v>
-      </c>
-      <c r="AY22" s="5" t="n">
+      <c r="AZ22" s="5" t="n">
         <v>2240</v>
       </c>
-      <c r="AZ22" s="5" t="n">
+      <c r="BA22" s="5" t="n">
         <v>12390</v>
-      </c>
-      <c r="BA22" s="5" t="n">
-        <v>9030</v>
       </c>
       <c r="BB22" s="5" t="n">
         <v>5410</v>
@@ -8578,19 +8578,19 @@
         <v>105</v>
       </c>
       <c r="AW23" s="5" t="n">
+        <v>3090</v>
+      </c>
+      <c r="AX23" s="5" t="n">
+        <v>8720</v>
+      </c>
+      <c r="AY23" s="5" t="n">
         <v>3730</v>
       </c>
-      <c r="AX23" s="5" t="n">
-        <v>3090</v>
-      </c>
-      <c r="AY23" s="5" t="n">
+      <c r="AZ23" s="5" t="n">
         <v>1580</v>
       </c>
-      <c r="AZ23" s="5" t="n">
+      <c r="BA23" s="5" t="n">
         <v>10210</v>
-      </c>
-      <c r="BA23" s="5" t="n">
-        <v>8720</v>
       </c>
       <c r="BB23" s="5" t="n">
         <v>4690</v>
@@ -8839,19 +8839,19 @@
         <v>96</v>
       </c>
       <c r="AW24" s="5" t="n">
+        <v>27280</v>
+      </c>
+      <c r="AX24" s="5" t="n">
+        <v>45430</v>
+      </c>
+      <c r="AY24" s="5" t="n">
         <v>40770</v>
       </c>
-      <c r="AX24" s="5" t="n">
-        <v>27280</v>
-      </c>
-      <c r="AY24" s="5" t="n">
+      <c r="AZ24" s="5" t="n">
         <v>17020</v>
       </c>
-      <c r="AZ24" s="5" t="n">
+      <c r="BA24" s="5" t="n">
         <v>68650</v>
-      </c>
-      <c r="BA24" s="5" t="n">
-        <v>45430</v>
       </c>
       <c r="BB24" s="5" t="n">
         <v>28890</v>
@@ -9049,7 +9049,7 @@
         <v>0.47</v>
       </c>
       <c r="AF25" s="5" t="n">
-        <v>11000</v>
+        <v>11010</v>
       </c>
       <c r="AG25" s="5" t="n">
         <v>1987</v>
@@ -9100,19 +9100,19 @@
         <v>105</v>
       </c>
       <c r="AW25" s="5" t="n">
+        <v>2950</v>
+      </c>
+      <c r="AX25" s="5" t="n">
+        <v>8150</v>
+      </c>
+      <c r="AY25" s="5" t="n">
         <v>3550</v>
       </c>
-      <c r="AX25" s="5" t="n">
-        <v>2950</v>
-      </c>
-      <c r="AY25" s="5" t="n">
+      <c r="AZ25" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="AZ25" s="5" t="n">
+      <c r="BA25" s="5" t="n">
         <v>9560</v>
-      </c>
-      <c r="BA25" s="5" t="n">
-        <v>8150</v>
       </c>
       <c r="BB25" s="5" t="n">
         <v>4510</v>
@@ -9310,7 +9310,7 @@
         <v>0.54</v>
       </c>
       <c r="AF26" s="5" t="n">
-        <v>8910</v>
+        <v>8920</v>
       </c>
       <c r="AG26" s="5" t="n">
         <v>3122</v>
@@ -9361,19 +9361,19 @@
         <v>105</v>
       </c>
       <c r="AW26" s="5" t="n">
+        <v>6670</v>
+      </c>
+      <c r="AX26" s="5" t="n">
+        <v>11800</v>
+      </c>
+      <c r="AY26" s="5" t="n">
         <v>10540</v>
       </c>
-      <c r="AX26" s="5" t="n">
-        <v>6670</v>
-      </c>
-      <c r="AY26" s="5" t="n">
+      <c r="AZ26" s="5" t="n">
         <v>4370</v>
       </c>
-      <c r="AZ26" s="5" t="n">
+      <c r="BA26" s="5" t="n">
         <v>19640</v>
-      </c>
-      <c r="BA26" s="5" t="n">
-        <v>11800</v>
       </c>
       <c r="BB26" s="5" t="n">
         <v>8260</v>
@@ -9571,7 +9571,7 @@
         <v>0.51</v>
       </c>
       <c r="AF27" s="5" t="n">
-        <v>9140</v>
+        <v>9130</v>
       </c>
       <c r="AG27" s="5" t="n">
         <v>626</v>
@@ -9622,19 +9622,19 @@
         <v>96</v>
       </c>
       <c r="AW27" s="5" t="n">
+        <v>3850</v>
+      </c>
+      <c r="AX27" s="5" t="n">
+        <v>6930</v>
+      </c>
+      <c r="AY27" s="5" t="n">
         <v>4670</v>
       </c>
-      <c r="AX27" s="5" t="n">
-        <v>3850</v>
-      </c>
-      <c r="AY27" s="5" t="n">
+      <c r="AZ27" s="5" t="n">
         <v>2180</v>
       </c>
-      <c r="AZ27" s="5" t="n">
+      <c r="BA27" s="5" t="n">
         <v>8790</v>
-      </c>
-      <c r="BA27" s="5" t="n">
-        <v>6930</v>
       </c>
       <c r="BB27" s="5" t="n">
         <v>4100</v>
@@ -9883,19 +9883,19 @@
         <v>96</v>
       </c>
       <c r="AW28" s="5" t="n">
+        <v>2640</v>
+      </c>
+      <c r="AX28" s="5" t="n">
+        <v>4900</v>
+      </c>
+      <c r="AY28" s="5" t="n">
         <v>2560</v>
       </c>
-      <c r="AX28" s="5" t="n">
-        <v>2640</v>
-      </c>
-      <c r="AY28" s="5" t="n">
+      <c r="AZ28" s="5" t="n">
         <v>1270</v>
       </c>
-      <c r="AZ28" s="5" t="n">
+      <c r="BA28" s="5" t="n">
         <v>4530</v>
-      </c>
-      <c r="BA28" s="5" t="n">
-        <v>4900</v>
       </c>
       <c r="BB28" s="5" t="n">
         <v>2240</v>
@@ -10093,7 +10093,7 @@
         <v>0.34</v>
       </c>
       <c r="AF29" s="5" t="n">
-        <v>6230</v>
+        <v>6270</v>
       </c>
       <c r="AG29" s="5" t="n">
         <v>1151</v>
@@ -10144,19 +10144,19 @@
         <v>96</v>
       </c>
       <c r="AW29" s="5" t="n">
+        <v>4220</v>
+      </c>
+      <c r="AX29" s="5" t="n">
+        <v>7140</v>
+      </c>
+      <c r="AY29" s="5" t="n">
         <v>7530</v>
       </c>
-      <c r="AX29" s="5" t="n">
-        <v>4220</v>
-      </c>
-      <c r="AY29" s="5" t="n">
+      <c r="AZ29" s="5" t="n">
         <v>3050</v>
       </c>
-      <c r="AZ29" s="5" t="n">
+      <c r="BA29" s="5" t="n">
         <v>13120</v>
-      </c>
-      <c r="BA29" s="5" t="n">
-        <v>7140</v>
       </c>
       <c r="BB29" s="5" t="n">
         <v>5310</v>
@@ -10354,7 +10354,7 @@
         <v>0.37</v>
       </c>
       <c r="AF30" s="5" t="n">
-        <v>11150</v>
+        <v>11160</v>
       </c>
       <c r="AG30" s="5" t="n">
         <v>1351</v>
@@ -10405,19 +10405,19 @@
         <v>105</v>
       </c>
       <c r="AW30" s="5" t="n">
+        <v>3820</v>
+      </c>
+      <c r="AX30" s="5" t="n">
+        <v>10910</v>
+      </c>
+      <c r="AY30" s="5" t="n">
         <v>5470</v>
       </c>
-      <c r="AX30" s="5" t="n">
-        <v>3820</v>
-      </c>
-      <c r="AY30" s="5" t="n">
+      <c r="AZ30" s="5" t="n">
         <v>2240</v>
       </c>
-      <c r="AZ30" s="5" t="n">
+      <c r="BA30" s="5" t="n">
         <v>16480</v>
-      </c>
-      <c r="BA30" s="5" t="n">
-        <v>10910</v>
       </c>
       <c r="BB30" s="5" t="n">
         <v>6780</v>
@@ -10615,7 +10615,7 @@
         <v>0.35</v>
       </c>
       <c r="AF31" s="5" t="n">
-        <v>2960</v>
+        <v>2950</v>
       </c>
       <c r="AG31" s="5" t="n">
         <v>296</v>
@@ -10666,19 +10666,19 @@
         <v>96</v>
       </c>
       <c r="AW31" s="5" t="n">
+        <v>9570</v>
+      </c>
+      <c r="AX31" s="5" t="n">
+        <v>12790</v>
+      </c>
+      <c r="AY31" s="5" t="n">
         <v>16330</v>
       </c>
-      <c r="AX31" s="5" t="n">
-        <v>9570</v>
-      </c>
-      <c r="AY31" s="5" t="n">
+      <c r="AZ31" s="5" t="n">
         <v>6000</v>
       </c>
-      <c r="AZ31" s="5" t="n">
+      <c r="BA31" s="5" t="n">
         <v>21990</v>
-      </c>
-      <c r="BA31" s="5" t="n">
-        <v>12790</v>
       </c>
       <c r="BB31" s="5" t="n">
         <v>8180</v>
@@ -10876,7 +10876,7 @@
         <v>0.21</v>
       </c>
       <c r="AF32" s="5" t="n">
-        <v>2820</v>
+        <v>2810</v>
       </c>
       <c r="AG32" s="5" t="n">
         <v>615</v>
@@ -10927,19 +10927,19 @@
         <v>96</v>
       </c>
       <c r="AW32" s="5" t="n">
+        <v>3110</v>
+      </c>
+      <c r="AX32" s="5" t="n">
+        <v>5520</v>
+      </c>
+      <c r="AY32" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="AX32" s="5" t="n">
-        <v>3110</v>
-      </c>
-      <c r="AY32" s="5" t="n">
+      <c r="AZ32" s="5" t="n">
         <v>2060</v>
       </c>
-      <c r="AZ32" s="5" t="n">
+      <c r="BA32" s="5" t="n">
         <v>8160</v>
-      </c>
-      <c r="BA32" s="5" t="n">
-        <v>5520</v>
       </c>
       <c r="BB32" s="5" t="n">
         <v>3780</v>
@@ -11188,19 +11188,19 @@
         <v>92</v>
       </c>
       <c r="AW33" s="5" t="n">
+        <v>29530</v>
+      </c>
+      <c r="AX33" s="5" t="n">
+        <v>35830</v>
+      </c>
+      <c r="AY33" s="5" t="n">
         <v>54480</v>
       </c>
-      <c r="AX33" s="5" t="n">
-        <v>29530</v>
-      </c>
-      <c r="AY33" s="5" t="n">
+      <c r="AZ33" s="5" t="n">
         <v>20500</v>
       </c>
-      <c r="AZ33" s="5" t="n">
+      <c r="BA33" s="5" t="n">
         <v>66090</v>
-      </c>
-      <c r="BA33" s="5" t="n">
-        <v>35830</v>
       </c>
       <c r="BB33" s="5" t="n">
         <v>25050</v>
@@ -11398,7 +11398,7 @@
         <v>0.4</v>
       </c>
       <c r="AF34" s="5" t="n">
-        <v>3890</v>
+        <v>3880</v>
       </c>
       <c r="AG34" s="5" t="n">
         <v>1063</v>
@@ -11449,19 +11449,19 @@
         <v>105</v>
       </c>
       <c r="AW34" s="5" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AX34" s="5" t="n">
+        <v>9810</v>
+      </c>
+      <c r="AY34" s="5" t="n">
         <v>7720</v>
       </c>
-      <c r="AX34" s="5" t="n">
-        <v>5510</v>
-      </c>
-      <c r="AY34" s="5" t="n">
+      <c r="AZ34" s="5" t="n">
         <v>3130</v>
       </c>
-      <c r="AZ34" s="5" t="n">
+      <c r="BA34" s="5" t="n">
         <v>13590</v>
-      </c>
-      <c r="BA34" s="5" t="n">
-        <v>9810</v>
       </c>
       <c r="BB34" s="5" t="n">
         <v>5570</v>
@@ -11710,19 +11710,19 @@
         <v>105</v>
       </c>
       <c r="AW35" s="5" t="n">
+        <v>3230</v>
+      </c>
+      <c r="AX35" s="5" t="n">
+        <v>5170</v>
+      </c>
+      <c r="AY35" s="5" t="n">
         <v>5430</v>
       </c>
-      <c r="AX35" s="5" t="n">
-        <v>3230</v>
-      </c>
-      <c r="AY35" s="5" t="n">
+      <c r="AZ35" s="5" t="n">
         <v>2250</v>
       </c>
-      <c r="AZ35" s="5" t="n">
+      <c r="BA35" s="5" t="n">
         <v>8610</v>
-      </c>
-      <c r="BA35" s="5" t="n">
-        <v>5170</v>
       </c>
       <c r="BB35" s="5" t="n">
         <v>3640</v>
@@ -11971,19 +11971,19 @@
         <v>92</v>
       </c>
       <c r="AW36" s="5" t="n">
+        <v>4610</v>
+      </c>
+      <c r="AX36" s="5" t="n">
+        <v>8120</v>
+      </c>
+      <c r="AY36" s="5" t="n">
         <v>6430</v>
       </c>
-      <c r="AX36" s="5" t="n">
-        <v>4610</v>
-      </c>
-      <c r="AY36" s="5" t="n">
+      <c r="AZ36" s="5" t="n">
         <v>2600</v>
       </c>
-      <c r="AZ36" s="5" t="n">
+      <c r="BA36" s="5" t="n">
         <v>11130</v>
-      </c>
-      <c r="BA36" s="5" t="n">
-        <v>8120</v>
       </c>
       <c r="BB36" s="5" t="n">
         <v>4800</v>
@@ -12181,7 +12181,7 @@
         <v>0.47</v>
       </c>
       <c r="AF37" s="5" t="n">
-        <v>3280</v>
+        <v>3270</v>
       </c>
       <c r="AG37" s="5" t="n">
         <v>1477</v>
@@ -12232,19 +12232,19 @@
         <v>96</v>
       </c>
       <c r="AW37" s="5" t="n">
+        <v>2410</v>
+      </c>
+      <c r="AX37" s="5" t="n">
+        <v>6270</v>
+      </c>
+      <c r="AY37" s="5" t="n">
         <v>3900</v>
       </c>
-      <c r="AX37" s="5" t="n">
-        <v>2410</v>
-      </c>
-      <c r="AY37" s="5" t="n">
+      <c r="AZ37" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="AZ37" s="5" t="n">
+      <c r="BA37" s="5" t="n">
         <v>10780</v>
-      </c>
-      <c r="BA37" s="5" t="n">
-        <v>6270</v>
       </c>
       <c r="BB37" s="5" t="n">
         <v>4450</v>
@@ -12493,19 +12493,19 @@
         <v>96</v>
       </c>
       <c r="AW38" s="5" t="n">
+        <v>2520</v>
+      </c>
+      <c r="AX38" s="5" t="n">
+        <v>4730</v>
+      </c>
+      <c r="AY38" s="5" t="n">
         <v>6360</v>
       </c>
-      <c r="AX38" s="5" t="n">
-        <v>2520</v>
-      </c>
-      <c r="AY38" s="5" t="n">
+      <c r="AZ38" s="5" t="n">
         <v>1990</v>
       </c>
-      <c r="AZ38" s="5" t="n">
+      <c r="BA38" s="5" t="n">
         <v>11720</v>
-      </c>
-      <c r="BA38" s="5" t="n">
-        <v>4730</v>
       </c>
       <c r="BB38" s="5" t="n">
         <v>3710</v>
@@ -12703,7 +12703,7 @@
         <v>0.43</v>
       </c>
       <c r="AF39" s="5" t="n">
-        <v>3220</v>
+        <v>3210</v>
       </c>
       <c r="AG39" s="5" t="n">
         <v>1620</v>
@@ -12754,19 +12754,19 @@
         <v>92</v>
       </c>
       <c r="AW39" s="5" t="n">
+        <v>5530</v>
+      </c>
+      <c r="AX39" s="5" t="n">
+        <v>11680</v>
+      </c>
+      <c r="AY39" s="5" t="n">
         <v>8830</v>
       </c>
-      <c r="AX39" s="5" t="n">
-        <v>5530</v>
-      </c>
-      <c r="AY39" s="5" t="n">
+      <c r="AZ39" s="5" t="n">
         <v>3470</v>
       </c>
-      <c r="AZ39" s="5" t="n">
+      <c r="BA39" s="5" t="n">
         <v>18260</v>
-      </c>
-      <c r="BA39" s="5" t="n">
-        <v>11680</v>
       </c>
       <c r="BB39" s="5" t="n">
         <v>7360</v>
@@ -12964,7 +12964,7 @@
         <v>0.51</v>
       </c>
       <c r="AF40" s="5" t="n">
-        <v>4800</v>
+        <v>4810</v>
       </c>
       <c r="AG40" s="5" t="n">
         <v>949</v>
@@ -13015,19 +13015,19 @@
         <v>105</v>
       </c>
       <c r="AW40" s="5" t="n">
+        <v>3740</v>
+      </c>
+      <c r="AX40" s="5" t="n">
+        <v>6280</v>
+      </c>
+      <c r="AY40" s="5" t="n">
         <v>5960</v>
       </c>
-      <c r="AX40" s="5" t="n">
-        <v>3740</v>
-      </c>
-      <c r="AY40" s="5" t="n">
+      <c r="AZ40" s="5" t="n">
         <v>2450</v>
       </c>
-      <c r="AZ40" s="5" t="n">
+      <c r="BA40" s="5" t="n">
         <v>10680</v>
-      </c>
-      <c r="BA40" s="5" t="n">
-        <v>6280</v>
       </c>
       <c r="BB40" s="5" t="n">
         <v>4320</v>
@@ -13276,19 +13276,19 @@
         <v>105</v>
       </c>
       <c r="AW41" s="5" t="n">
+        <v>7940</v>
+      </c>
+      <c r="AX41" s="5" t="n">
+        <v>13020</v>
+      </c>
+      <c r="AY41" s="5" t="n">
         <v>13970</v>
       </c>
-      <c r="AX41" s="5" t="n">
-        <v>7940</v>
-      </c>
-      <c r="AY41" s="5" t="n">
+      <c r="AZ41" s="5" t="n">
         <v>5440</v>
       </c>
-      <c r="AZ41" s="5" t="n">
+      <c r="BA41" s="5" t="n">
         <v>22680</v>
-      </c>
-      <c r="BA41" s="5" t="n">
-        <v>13020</v>
       </c>
       <c r="BB41" s="5" t="n">
         <v>8980</v>
@@ -13537,19 +13537,19 @@
         <v>105</v>
       </c>
       <c r="AW42" s="5" t="n">
+        <v>7770</v>
+      </c>
+      <c r="AX42" s="5" t="n">
+        <v>15460</v>
+      </c>
+      <c r="AY42" s="5" t="n">
         <v>7630</v>
       </c>
-      <c r="AX42" s="5" t="n">
-        <v>7770</v>
-      </c>
-      <c r="AY42" s="5" t="n">
+      <c r="AZ42" s="5" t="n">
         <v>3770</v>
       </c>
-      <c r="AZ42" s="5" t="n">
+      <c r="BA42" s="5" t="n">
         <v>15820</v>
-      </c>
-      <c r="BA42" s="5" t="n">
-        <v>15460</v>
       </c>
       <c r="BB42" s="5" t="n">
         <v>7620</v>
@@ -13798,19 +13798,19 @@
         <v>105</v>
       </c>
       <c r="AW43" s="5" t="n">
+        <v>4490</v>
+      </c>
+      <c r="AX43" s="5" t="n">
+        <v>9570</v>
+      </c>
+      <c r="AY43" s="5" t="n">
         <v>4290</v>
       </c>
-      <c r="AX43" s="5" t="n">
-        <v>4490</v>
-      </c>
-      <c r="AY43" s="5" t="n">
+      <c r="AZ43" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="AZ43" s="5" t="n">
+      <c r="BA43" s="5" t="n">
         <v>11200</v>
-      </c>
-      <c r="BA43" s="5" t="n">
-        <v>9570</v>
       </c>
       <c r="BB43" s="5" t="n">
         <v>5070</v>
@@ -14059,19 +14059,19 @@
         <v>96</v>
       </c>
       <c r="AW44" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="AX44" s="5" t="n">
+        <v>7220</v>
+      </c>
+      <c r="AY44" s="5" t="n">
         <v>5370</v>
       </c>
-      <c r="AX44" s="5" t="n">
-        <v>3400</v>
-      </c>
-      <c r="AY44" s="5" t="n">
+      <c r="AZ44" s="5" t="n">
         <v>2050</v>
       </c>
-      <c r="AZ44" s="5" t="n">
+      <c r="BA44" s="5" t="n">
         <v>10490</v>
-      </c>
-      <c r="BA44" s="5" t="n">
-        <v>7220</v>
       </c>
       <c r="BB44" s="5" t="n">
         <v>4110</v>
@@ -14320,19 +14320,19 @@
         <v>92</v>
       </c>
       <c r="AW45" s="5" t="n">
+        <v>4600</v>
+      </c>
+      <c r="AX45" s="5" t="n">
+        <v>6360</v>
+      </c>
+      <c r="AY45" s="5" t="n">
         <v>4130</v>
       </c>
-      <c r="AX45" s="5" t="n">
-        <v>4600</v>
-      </c>
-      <c r="AY45" s="5" t="n">
+      <c r="AZ45" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="AZ45" s="5" t="n">
+      <c r="BA45" s="5" t="n">
         <v>6050</v>
-      </c>
-      <c r="BA45" s="5" t="n">
-        <v>6360</v>
       </c>
       <c r="BB45" s="5" t="n">
         <v>2950</v>
@@ -14581,19 +14581,19 @@
         <v>92</v>
       </c>
       <c r="AW46" s="5" t="n">
+        <v>11550</v>
+      </c>
+      <c r="AX46" s="5" t="n">
+        <v>19560</v>
+      </c>
+      <c r="AY46" s="5" t="n">
         <v>13990</v>
       </c>
-      <c r="AX46" s="5" t="n">
-        <v>11550</v>
-      </c>
-      <c r="AY46" s="5" t="n">
+      <c r="AZ46" s="5" t="n">
         <v>6400</v>
       </c>
-      <c r="AZ46" s="5" t="n">
+      <c r="BA46" s="5" t="n">
         <v>24620</v>
-      </c>
-      <c r="BA46" s="5" t="n">
-        <v>19560</v>
       </c>
       <c r="BB46" s="5" t="n">
         <v>11310</v>
@@ -14842,19 +14842,19 @@
         <v>92</v>
       </c>
       <c r="AW47" s="5" t="n">
+        <v>11040</v>
+      </c>
+      <c r="AX47" s="5" t="n">
+        <v>18230</v>
+      </c>
+      <c r="AY47" s="5" t="n">
         <v>12570</v>
       </c>
-      <c r="AX47" s="5" t="n">
-        <v>11040</v>
-      </c>
-      <c r="AY47" s="5" t="n">
+      <c r="AZ47" s="5" t="n">
         <v>5560</v>
       </c>
-      <c r="AZ47" s="5" t="n">
+      <c r="BA47" s="5" t="n">
         <v>22340</v>
-      </c>
-      <c r="BA47" s="5" t="n">
-        <v>18230</v>
       </c>
       <c r="BB47" s="5" t="n">
         <v>10060</v>
@@ -15103,19 +15103,19 @@
         <v>105</v>
       </c>
       <c r="AW48" s="5" t="n">
+        <v>11340</v>
+      </c>
+      <c r="AX48" s="5" t="n">
+        <v>18470</v>
+      </c>
+      <c r="AY48" s="5" t="n">
         <v>11540</v>
       </c>
-      <c r="AX48" s="5" t="n">
-        <v>11340</v>
-      </c>
-      <c r="AY48" s="5" t="n">
+      <c r="AZ48" s="5" t="n">
         <v>5120</v>
       </c>
-      <c r="AZ48" s="5" t="n">
+      <c r="BA48" s="5" t="n">
         <v>21090</v>
-      </c>
-      <c r="BA48" s="5" t="n">
-        <v>18470</v>
       </c>
       <c r="BB48" s="5" t="n">
         <v>9370</v>
@@ -15364,19 +15364,19 @@
         <v>92</v>
       </c>
       <c r="AW49" s="5" t="n">
+        <v>11170</v>
+      </c>
+      <c r="AX49" s="5" t="n">
+        <v>18100</v>
+      </c>
+      <c r="AY49" s="5" t="n">
         <v>12460</v>
       </c>
-      <c r="AX49" s="5" t="n">
-        <v>11170</v>
-      </c>
-      <c r="AY49" s="5" t="n">
+      <c r="AZ49" s="5" t="n">
         <v>5390</v>
       </c>
-      <c r="AZ49" s="5" t="n">
+      <c r="BA49" s="5" t="n">
         <v>21240</v>
-      </c>
-      <c r="BA49" s="5" t="n">
-        <v>18100</v>
       </c>
       <c r="BB49" s="5" t="n">
         <v>9350</v>
@@ -15625,19 +15625,19 @@
         <v>92</v>
       </c>
       <c r="AW50" s="5" t="n">
+        <v>16220</v>
+      </c>
+      <c r="AX50" s="5" t="n">
+        <v>25920</v>
+      </c>
+      <c r="AY50" s="5" t="n">
         <v>14030</v>
       </c>
-      <c r="AX50" s="5" t="n">
-        <v>16220</v>
-      </c>
-      <c r="AY50" s="5" t="n">
+      <c r="AZ50" s="5" t="n">
         <v>6300</v>
       </c>
-      <c r="AZ50" s="5" t="n">
+      <c r="BA50" s="5" t="n">
         <v>23990</v>
-      </c>
-      <c r="BA50" s="5" t="n">
-        <v>25920</v>
       </c>
       <c r="BB50" s="5" t="n">
         <v>10810</v>
@@ -15886,19 +15886,19 @@
         <v>105</v>
       </c>
       <c r="AW51" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="AX51" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="AY51" s="5" t="n">
         <v>190</v>
       </c>
-      <c r="AX51" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="AY51" s="5" t="n">
+      <c r="AZ51" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="AZ51" s="5" t="n">
+      <c r="BA51" s="5" t="n">
         <v>230</v>
-      </c>
-      <c r="BA51" s="5" t="n">
-        <v>420</v>
       </c>
       <c r="BB51" s="5" t="n">
         <v>110</v>
@@ -16094,7 +16094,7 @@
         <v>0.53</v>
       </c>
       <c r="AF52" s="5" t="n">
-        <v>20630</v>
+        <v>20600</v>
       </c>
       <c r="AG52" s="5" t="n">
         <v>10711</v>
@@ -16145,19 +16145,19 @@
         <v>92</v>
       </c>
       <c r="AW52" s="5" t="n">
+        <v>11930</v>
+      </c>
+      <c r="AX52" s="5" t="n">
+        <v>20090</v>
+      </c>
+      <c r="AY52" s="5" t="n">
         <v>13860</v>
       </c>
-      <c r="AX52" s="5" t="n">
-        <v>11930</v>
-      </c>
-      <c r="AY52" s="5" t="n">
+      <c r="AZ52" s="5" t="n">
         <v>6040</v>
       </c>
-      <c r="AZ52" s="5" t="n">
+      <c r="BA52" s="5" t="n">
         <v>24030</v>
-      </c>
-      <c r="BA52" s="5" t="n">
-        <v>20090</v>
       </c>
       <c r="BB52" s="5" t="n">
         <v>10780</v>
@@ -16355,7 +16355,7 @@
         <v>0.41</v>
       </c>
       <c r="AF53" s="5" t="n">
-        <v>4620</v>
+        <v>4630</v>
       </c>
       <c r="AG53" s="5" t="n">
         <v>2712</v>
@@ -16406,19 +16406,19 @@
         <v>105</v>
       </c>
       <c r="AW53" s="5" t="n">
+        <v>6300</v>
+      </c>
+      <c r="AX53" s="5" t="n">
+        <v>11320</v>
+      </c>
+      <c r="AY53" s="5" t="n">
         <v>8610</v>
       </c>
-      <c r="AX53" s="5" t="n">
-        <v>6300</v>
-      </c>
-      <c r="AY53" s="5" t="n">
+      <c r="AZ53" s="5" t="n">
         <v>3570</v>
       </c>
-      <c r="AZ53" s="5" t="n">
+      <c r="BA53" s="5" t="n">
         <v>15660</v>
-      </c>
-      <c r="BA53" s="5" t="n">
-        <v>11320</v>
       </c>
       <c r="BB53" s="5" t="n">
         <v>6400</v>
@@ -16616,7 +16616,7 @@
         <v>0.41</v>
       </c>
       <c r="AF54" s="5" t="n">
-        <v>7560</v>
+        <v>7550</v>
       </c>
       <c r="AG54" s="5" t="n">
         <v>3708</v>
@@ -16667,19 +16667,19 @@
         <v>105</v>
       </c>
       <c r="AW54" s="5" t="n">
+        <v>8160</v>
+      </c>
+      <c r="AX54" s="5" t="n">
+        <v>12660</v>
+      </c>
+      <c r="AY54" s="5" t="n">
         <v>13060</v>
       </c>
-      <c r="AX54" s="5" t="n">
-        <v>8160</v>
-      </c>
-      <c r="AY54" s="5" t="n">
+      <c r="AZ54" s="5" t="n">
         <v>5400</v>
       </c>
-      <c r="AZ54" s="5" t="n">
+      <c r="BA54" s="5" t="n">
         <v>20740</v>
-      </c>
-      <c r="BA54" s="5" t="n">
-        <v>12660</v>
       </c>
       <c r="BB54" s="5" t="n">
         <v>8660</v>
@@ -16877,7 +16877,7 @@
         <v>0.39</v>
       </c>
       <c r="AF55" s="5" t="n">
-        <v>14280</v>
+        <v>14290</v>
       </c>
       <c r="AG55" s="5" t="n">
         <v>5156</v>
@@ -16928,19 +16928,19 @@
         <v>92</v>
       </c>
       <c r="AW55" s="5" t="n">
+        <v>12120</v>
+      </c>
+      <c r="AX55" s="5" t="n">
+        <v>19760</v>
+      </c>
+      <c r="AY55" s="5" t="n">
         <v>12970</v>
       </c>
-      <c r="AX55" s="5" t="n">
-        <v>12120</v>
-      </c>
-      <c r="AY55" s="5" t="n">
+      <c r="AZ55" s="5" t="n">
         <v>5740</v>
       </c>
-      <c r="AZ55" s="5" t="n">
+      <c r="BA55" s="5" t="n">
         <v>22290</v>
-      </c>
-      <c r="BA55" s="5" t="n">
-        <v>19760</v>
       </c>
       <c r="BB55" s="5" t="n">
         <v>10200</v>
@@ -17138,7 +17138,7 @@
         <v>0.42</v>
       </c>
       <c r="AF56" s="5" t="n">
-        <v>10240</v>
+        <v>10250</v>
       </c>
       <c r="AG56" s="5" t="n">
         <v>2087</v>
@@ -17189,19 +17189,19 @@
         <v>105</v>
       </c>
       <c r="AW56" s="5" t="n">
+        <v>4540</v>
+      </c>
+      <c r="AX56" s="5" t="n">
+        <v>7600</v>
+      </c>
+      <c r="AY56" s="5" t="n">
         <v>5860</v>
       </c>
-      <c r="AX56" s="5" t="n">
-        <v>4540</v>
-      </c>
-      <c r="AY56" s="5" t="n">
+      <c r="AZ56" s="5" t="n">
         <v>2720</v>
       </c>
-      <c r="AZ56" s="5" t="n">
+      <c r="BA56" s="5" t="n">
         <v>10490</v>
-      </c>
-      <c r="BA56" s="5" t="n">
-        <v>7600</v>
       </c>
       <c r="BB56" s="5" t="n">
         <v>4810</v>
@@ -17399,7 +17399,7 @@
         <v>0.5</v>
       </c>
       <c r="AF57" s="5" t="n">
-        <v>16190</v>
+        <v>16180</v>
       </c>
       <c r="AG57" s="5" t="n">
         <v>6847</v>
@@ -17450,19 +17450,19 @@
         <v>92</v>
       </c>
       <c r="AW57" s="5" t="n">
+        <v>10900</v>
+      </c>
+      <c r="AX57" s="5" t="n">
+        <v>16990</v>
+      </c>
+      <c r="AY57" s="5" t="n">
         <v>11700</v>
       </c>
-      <c r="AX57" s="5" t="n">
-        <v>10900</v>
-      </c>
-      <c r="AY57" s="5" t="n">
+      <c r="AZ57" s="5" t="n">
         <v>5240</v>
       </c>
-      <c r="AZ57" s="5" t="n">
+      <c r="BA57" s="5" t="n">
         <v>19180</v>
-      </c>
-      <c r="BA57" s="5" t="n">
-        <v>16990</v>
       </c>
       <c r="BB57" s="5" t="n">
         <v>8660</v>
@@ -17711,19 +17711,19 @@
         <v>105</v>
       </c>
       <c r="AW58" s="5" t="n">
+        <v>17920</v>
+      </c>
+      <c r="AX58" s="5" t="n">
+        <v>26750</v>
+      </c>
+      <c r="AY58" s="5" t="n">
         <v>23720</v>
       </c>
-      <c r="AX58" s="5" t="n">
-        <v>17920</v>
-      </c>
-      <c r="AY58" s="5" t="n">
+      <c r="AZ58" s="5" t="n">
         <v>9910</v>
       </c>
-      <c r="AZ58" s="5" t="n">
+      <c r="BA58" s="5" t="n">
         <v>36760</v>
-      </c>
-      <c r="BA58" s="5" t="n">
-        <v>26750</v>
       </c>
       <c r="BB58" s="5" t="n">
         <v>15490</v>
@@ -17972,19 +17972,19 @@
         <v>105</v>
       </c>
       <c r="AW59" s="5" t="n">
+        <v>8410</v>
+      </c>
+      <c r="AX59" s="5" t="n">
+        <v>13020</v>
+      </c>
+      <c r="AY59" s="5" t="n">
         <v>10860</v>
       </c>
-      <c r="AX59" s="5" t="n">
-        <v>8410</v>
-      </c>
-      <c r="AY59" s="5" t="n">
+      <c r="AZ59" s="5" t="n">
         <v>4750</v>
       </c>
-      <c r="AZ59" s="5" t="n">
+      <c r="BA59" s="5" t="n">
         <v>17430</v>
-      </c>
-      <c r="BA59" s="5" t="n">
-        <v>13020</v>
       </c>
       <c r="BB59" s="5" t="n">
         <v>7730</v>
@@ -18233,19 +18233,19 @@
         <v>105</v>
       </c>
       <c r="AW60" s="5" t="n">
+        <v>11700</v>
+      </c>
+      <c r="AX60" s="5" t="n">
+        <v>17680</v>
+      </c>
+      <c r="AY60" s="5" t="n">
         <v>12920</v>
       </c>
-      <c r="AX60" s="5" t="n">
-        <v>11700</v>
-      </c>
-      <c r="AY60" s="5" t="n">
+      <c r="AZ60" s="5" t="n">
         <v>5340</v>
       </c>
-      <c r="AZ60" s="5" t="n">
+      <c r="BA60" s="5" t="n">
         <v>21390</v>
-      </c>
-      <c r="BA60" s="5" t="n">
-        <v>17680</v>
       </c>
       <c r="BB60" s="5" t="n">
         <v>8930</v>
@@ -18494,19 +18494,19 @@
         <v>92</v>
       </c>
       <c r="AW61" s="5" t="n">
+        <v>10970</v>
+      </c>
+      <c r="AX61" s="5" t="n">
+        <v>17300</v>
+      </c>
+      <c r="AY61" s="5" t="n">
         <v>11410</v>
       </c>
-      <c r="AX61" s="5" t="n">
-        <v>10970</v>
-      </c>
-      <c r="AY61" s="5" t="n">
+      <c r="AZ61" s="5" t="n">
         <v>5340</v>
       </c>
-      <c r="AZ61" s="5" t="n">
+      <c r="BA61" s="5" t="n">
         <v>18170</v>
-      </c>
-      <c r="BA61" s="5" t="n">
-        <v>17300</v>
       </c>
       <c r="BB61" s="5" t="n">
         <v>8630</v>
@@ -18755,19 +18755,19 @@
         <v>92</v>
       </c>
       <c r="AW62" s="5" t="n">
+        <v>10150</v>
+      </c>
+      <c r="AX62" s="5" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AY62" s="5" t="n">
         <v>10020</v>
       </c>
-      <c r="AX62" s="5" t="n">
-        <v>10150</v>
-      </c>
-      <c r="AY62" s="5" t="n">
+      <c r="AZ62" s="5" t="n">
         <v>4520</v>
       </c>
-      <c r="AZ62" s="5" t="n">
+      <c r="BA62" s="5" t="n">
         <v>16260</v>
-      </c>
-      <c r="BA62" s="5" t="n">
-        <v>15800</v>
       </c>
       <c r="BB62" s="5" t="n">
         <v>7460</v>
@@ -19016,19 +19016,19 @@
         <v>92</v>
       </c>
       <c r="AW63" s="5" t="n">
+        <v>28580</v>
+      </c>
+      <c r="AX63" s="5" t="n">
+        <v>47920</v>
+      </c>
+      <c r="AY63" s="5" t="n">
         <v>28330</v>
       </c>
-      <c r="AX63" s="5" t="n">
-        <v>28580</v>
-      </c>
-      <c r="AY63" s="5" t="n">
+      <c r="AZ63" s="5" t="n">
         <v>12390</v>
       </c>
-      <c r="AZ63" s="5" t="n">
+      <c r="BA63" s="5" t="n">
         <v>50340</v>
-      </c>
-      <c r="BA63" s="5" t="n">
-        <v>47920</v>
       </c>
       <c r="BB63" s="5" t="n">
         <v>22140</v>
@@ -19226,7 +19226,7 @@
         <v>0.36</v>
       </c>
       <c r="AF64" s="5" t="n">
-        <v>27760</v>
+        <v>27770</v>
       </c>
       <c r="AG64" s="5" t="n">
         <v>14947</v>
@@ -19277,19 +19277,19 @@
         <v>92</v>
       </c>
       <c r="AW64" s="5" t="n">
+        <v>20070</v>
+      </c>
+      <c r="AX64" s="5" t="n">
+        <v>34630</v>
+      </c>
+      <c r="AY64" s="5" t="n">
         <v>21140</v>
       </c>
-      <c r="AX64" s="5" t="n">
-        <v>20070</v>
-      </c>
-      <c r="AY64" s="5" t="n">
+      <c r="AZ64" s="5" t="n">
         <v>9360</v>
       </c>
-      <c r="AZ64" s="5" t="n">
+      <c r="BA64" s="5" t="n">
         <v>37580</v>
-      </c>
-      <c r="BA64" s="5" t="n">
-        <v>34630</v>
       </c>
       <c r="BB64" s="5" t="n">
         <v>16990</v>
@@ -19538,19 +19538,19 @@
         <v>96</v>
       </c>
       <c r="AW65" s="5" t="n">
+        <v>7460</v>
+      </c>
+      <c r="AX65" s="5" t="n">
+        <v>11970</v>
+      </c>
+      <c r="AY65" s="5" t="n">
         <v>11920</v>
       </c>
-      <c r="AX65" s="5" t="n">
-        <v>7460</v>
-      </c>
-      <c r="AY65" s="5" t="n">
+      <c r="AZ65" s="5" t="n">
         <v>4550</v>
       </c>
-      <c r="AZ65" s="5" t="n">
+      <c r="BA65" s="5" t="n">
         <v>19760</v>
-      </c>
-      <c r="BA65" s="5" t="n">
-        <v>11970</v>
       </c>
       <c r="BB65" s="5" t="n">
         <v>7290</v>
@@ -19799,19 +19799,19 @@
         <v>105</v>
       </c>
       <c r="AW66" s="5" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AX66" s="5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AY66" s="5" t="n">
         <v>3970</v>
       </c>
-      <c r="AX66" s="5" t="n">
-        <v>2980</v>
-      </c>
-      <c r="AY66" s="5" t="n">
+      <c r="AZ66" s="5" t="n">
         <v>1700</v>
       </c>
-      <c r="AZ66" s="5" t="n">
+      <c r="BA66" s="5" t="n">
         <v>8140</v>
-      </c>
-      <c r="BA66" s="5" t="n">
-        <v>7000</v>
       </c>
       <c r="BB66" s="5" t="n">
         <v>3480</v>
@@ -20060,19 +20060,19 @@
         <v>96</v>
       </c>
       <c r="AW67" s="5" t="n">
+        <v>2750</v>
+      </c>
+      <c r="AX67" s="5" t="n">
+        <v>18850</v>
+      </c>
+      <c r="AY67" s="5" t="n">
         <v>3900</v>
       </c>
-      <c r="AX67" s="5" t="n">
-        <v>2750</v>
-      </c>
-      <c r="AY67" s="5" t="n">
+      <c r="AZ67" s="5" t="n">
         <v>1710</v>
       </c>
-      <c r="AZ67" s="5" t="n">
+      <c r="BA67" s="5" t="n">
         <v>25250</v>
-      </c>
-      <c r="BA67" s="5" t="n">
-        <v>18850</v>
       </c>
       <c r="BB67" s="5" t="n">
         <v>10730</v>
@@ -20270,7 +20270,7 @@
         <v>0.41</v>
       </c>
       <c r="AF68" s="5" t="n">
-        <v>8150</v>
+        <v>8130</v>
       </c>
       <c r="AG68" s="5" t="n">
         <v>2666</v>
@@ -20321,19 +20321,19 @@
         <v>105</v>
       </c>
       <c r="AW68" s="5" t="n">
+        <v>10840</v>
+      </c>
+      <c r="AX68" s="5" t="n">
+        <v>20400</v>
+      </c>
+      <c r="AY68" s="5" t="n">
         <v>12860</v>
       </c>
-      <c r="AX68" s="5" t="n">
-        <v>10840</v>
-      </c>
-      <c r="AY68" s="5" t="n">
+      <c r="AZ68" s="5" t="n">
         <v>5660</v>
       </c>
-      <c r="AZ68" s="5" t="n">
+      <c r="BA68" s="5" t="n">
         <v>24190</v>
-      </c>
-      <c r="BA68" s="5" t="n">
-        <v>20400</v>
       </c>
       <c r="BB68" s="5" t="n">
         <v>10610</v>
@@ -20582,19 +20582,19 @@
         <v>105</v>
       </c>
       <c r="AW69" s="5" t="n">
+        <v>6060</v>
+      </c>
+      <c r="AX69" s="5" t="n">
+        <v>9920</v>
+      </c>
+      <c r="AY69" s="5" t="n">
         <v>7500</v>
       </c>
-      <c r="AX69" s="5" t="n">
-        <v>6060</v>
-      </c>
-      <c r="AY69" s="5" t="n">
+      <c r="AZ69" s="5" t="n">
         <v>3100</v>
       </c>
-      <c r="AZ69" s="5" t="n">
+      <c r="BA69" s="5" t="n">
         <v>13430</v>
-      </c>
-      <c r="BA69" s="5" t="n">
-        <v>9920</v>
       </c>
       <c r="BB69" s="5" t="n">
         <v>5570</v>
@@ -20843,19 +20843,19 @@
         <v>105</v>
       </c>
       <c r="AW70" s="5" t="n">
+        <v>2610</v>
+      </c>
+      <c r="AX70" s="5" t="n">
+        <v>4300</v>
+      </c>
+      <c r="AY70" s="5" t="n">
         <v>3160</v>
       </c>
-      <c r="AX70" s="5" t="n">
-        <v>2610</v>
-      </c>
-      <c r="AY70" s="5" t="n">
+      <c r="AZ70" s="5" t="n">
         <v>1440</v>
       </c>
-      <c r="AZ70" s="5" t="n">
+      <c r="BA70" s="5" t="n">
         <v>5380</v>
-      </c>
-      <c r="BA70" s="5" t="n">
-        <v>4300</v>
       </c>
       <c r="BB70" s="5" t="n">
         <v>2500</v>
@@ -21053,7 +21053,7 @@
         <v>0.24</v>
       </c>
       <c r="AF71" s="5" t="n">
-        <v>2560</v>
+        <v>2550</v>
       </c>
       <c r="AG71" s="5" t="n">
         <v>626</v>
@@ -21104,19 +21104,19 @@
         <v>92</v>
       </c>
       <c r="AW71" s="5" t="n">
+        <v>1090</v>
+      </c>
+      <c r="AX71" s="5" t="n">
+        <v>1920</v>
+      </c>
+      <c r="AY71" s="5" t="n">
         <v>1120</v>
       </c>
-      <c r="AX71" s="5" t="n">
-        <v>1090</v>
-      </c>
-      <c r="AY71" s="5" t="n">
+      <c r="AZ71" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="AZ71" s="5" t="n">
+      <c r="BA71" s="5" t="n">
         <v>2200</v>
-      </c>
-      <c r="BA71" s="5" t="n">
-        <v>1920</v>
       </c>
       <c r="BB71" s="5" t="n">
         <v>1040</v>
@@ -21365,19 +21365,19 @@
         <v>96</v>
       </c>
       <c r="AW72" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AX72" s="5" t="n">
+        <v>3510</v>
+      </c>
+      <c r="AY72" s="5" t="n">
         <v>2310</v>
       </c>
-      <c r="AX72" s="5" t="n">
-        <v>2010</v>
-      </c>
-      <c r="AY72" s="5" t="n">
+      <c r="AZ72" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="AZ72" s="5" t="n">
+      <c r="BA72" s="5" t="n">
         <v>4070</v>
-      </c>
-      <c r="BA72" s="5" t="n">
-        <v>3510</v>
       </c>
       <c r="BB72" s="5" t="n">
         <v>2080</v>
@@ -21626,19 +21626,19 @@
         <v>92</v>
       </c>
       <c r="AW73" s="5" t="n">
+        <v>2550</v>
+      </c>
+      <c r="AX73" s="5" t="n">
+        <v>4430</v>
+      </c>
+      <c r="AY73" s="5" t="n">
         <v>2210</v>
       </c>
-      <c r="AX73" s="5" t="n">
-        <v>2550</v>
-      </c>
-      <c r="AY73" s="5" t="n">
+      <c r="AZ73" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="AZ73" s="5" t="n">
+      <c r="BA73" s="5" t="n">
         <v>3850</v>
-      </c>
-      <c r="BA73" s="5" t="n">
-        <v>4430</v>
       </c>
       <c r="BB73" s="5" t="n">
         <v>1820</v>
@@ -21887,19 +21887,19 @@
         <v>96</v>
       </c>
       <c r="AW74" s="5" t="n">
+        <v>2340</v>
+      </c>
+      <c r="AX74" s="5" t="n">
+        <v>6120</v>
+      </c>
+      <c r="AY74" s="5" t="n">
         <v>2710</v>
       </c>
-      <c r="AX74" s="5" t="n">
-        <v>2340</v>
-      </c>
-      <c r="AY74" s="5" t="n">
+      <c r="AZ74" s="5" t="n">
         <v>1250</v>
       </c>
-      <c r="AZ74" s="5" t="n">
+      <c r="BA74" s="5" t="n">
         <v>8270</v>
-      </c>
-      <c r="BA74" s="5" t="n">
-        <v>6120</v>
       </c>
       <c r="BB74" s="5" t="n">
         <v>3820</v>
@@ -22148,19 +22148,19 @@
         <v>92</v>
       </c>
       <c r="AW75" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="AX75" s="5" t="n">
+        <v>3900</v>
+      </c>
+      <c r="AY75" s="5" t="n">
         <v>2560</v>
       </c>
-      <c r="AX75" s="5" t="n">
-        <v>2710</v>
-      </c>
-      <c r="AY75" s="5" t="n">
+      <c r="AZ75" s="5" t="n">
         <v>1240</v>
       </c>
-      <c r="AZ75" s="5" t="n">
+      <c r="BA75" s="5" t="n">
         <v>3880</v>
-      </c>
-      <c r="BA75" s="5" t="n">
-        <v>3900</v>
       </c>
       <c r="BB75" s="5" t="n">
         <v>1870</v>
@@ -22409,19 +22409,19 @@
         <v>92</v>
       </c>
       <c r="AW76" s="5" t="n">
+        <v>1340</v>
+      </c>
+      <c r="AX76" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AY76" s="5" t="n">
         <v>1760</v>
       </c>
-      <c r="AX76" s="5" t="n">
-        <v>1340</v>
-      </c>
-      <c r="AY76" s="5" t="n">
+      <c r="AZ76" s="5" t="n">
         <v>820</v>
       </c>
-      <c r="AZ76" s="5" t="n">
+      <c r="BA76" s="5" t="n">
         <v>3020</v>
-      </c>
-      <c r="BA76" s="5" t="n">
-        <v>2200</v>
       </c>
       <c r="BB76" s="5" t="n">
         <v>1430</v>
@@ -22670,19 +22670,19 @@
         <v>105</v>
       </c>
       <c r="AW77" s="5" t="n">
+        <v>2640</v>
+      </c>
+      <c r="AX77" s="5" t="n">
+        <v>4510</v>
+      </c>
+      <c r="AY77" s="5" t="n">
         <v>2610</v>
       </c>
-      <c r="AX77" s="5" t="n">
-        <v>2640</v>
-      </c>
-      <c r="AY77" s="5" t="n">
+      <c r="AZ77" s="5" t="n">
         <v>1080</v>
       </c>
-      <c r="AZ77" s="5" t="n">
+      <c r="BA77" s="5" t="n">
         <v>5140</v>
-      </c>
-      <c r="BA77" s="5" t="n">
-        <v>4510</v>
       </c>
       <c r="BB77" s="5" t="n">
         <v>2170</v>
@@ -22880,7 +22880,7 @@
         <v>0.48</v>
       </c>
       <c r="AF78" s="5" t="n">
-        <v>8260</v>
+        <v>8250</v>
       </c>
       <c r="AG78" s="5" t="n">
         <v>2840</v>
@@ -22931,19 +22931,19 @@
         <v>92</v>
       </c>
       <c r="AW78" s="5" t="n">
+        <v>7560</v>
+      </c>
+      <c r="AX78" s="5" t="n">
+        <v>10470</v>
+      </c>
+      <c r="AY78" s="5" t="n">
         <v>8180</v>
       </c>
-      <c r="AX78" s="5" t="n">
-        <v>7560</v>
-      </c>
-      <c r="AY78" s="5" t="n">
+      <c r="AZ78" s="5" t="n">
         <v>3770</v>
       </c>
-      <c r="AZ78" s="5" t="n">
+      <c r="BA78" s="5" t="n">
         <v>11600</v>
-      </c>
-      <c r="BA78" s="5" t="n">
-        <v>10470</v>
       </c>
       <c r="BB78" s="5" t="n">
         <v>5380</v>
@@ -23192,19 +23192,19 @@
         <v>96</v>
       </c>
       <c r="AW79" s="5" t="n">
+        <v>2320</v>
+      </c>
+      <c r="AX79" s="5" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AY79" s="5" t="n">
         <v>3190</v>
       </c>
-      <c r="AX79" s="5" t="n">
-        <v>2320</v>
-      </c>
-      <c r="AY79" s="5" t="n">
+      <c r="AZ79" s="5" t="n">
         <v>1260</v>
       </c>
-      <c r="AZ79" s="5" t="n">
+      <c r="BA79" s="5" t="n">
         <v>6840</v>
-      </c>
-      <c r="BA79" s="5" t="n">
-        <v>4750</v>
       </c>
       <c r="BB79" s="5" t="n">
         <v>2700</v>
@@ -23402,7 +23402,7 @@
         <v>0.44</v>
       </c>
       <c r="AF80" s="5" t="n">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="AG80" s="5" t="n">
         <v>2431</v>
@@ -23453,19 +23453,19 @@
         <v>92</v>
       </c>
       <c r="AW80" s="5" t="n">
+        <v>2900</v>
+      </c>
+      <c r="AX80" s="5" t="n">
+        <v>4840</v>
+      </c>
+      <c r="AY80" s="5" t="n">
         <v>2560</v>
       </c>
-      <c r="AX80" s="5" t="n">
-        <v>2900</v>
-      </c>
-      <c r="AY80" s="5" t="n">
+      <c r="AZ80" s="5" t="n">
         <v>1070</v>
       </c>
-      <c r="AZ80" s="5" t="n">
+      <c r="BA80" s="5" t="n">
         <v>4990</v>
-      </c>
-      <c r="BA80" s="5" t="n">
-        <v>4840</v>
       </c>
       <c r="BB80" s="5" t="n">
         <v>2120</v>
@@ -23714,19 +23714,19 @@
         <v>92</v>
       </c>
       <c r="AW81" s="5" t="n">
+        <v>4020</v>
+      </c>
+      <c r="AX81" s="5" t="n">
+        <v>6540</v>
+      </c>
+      <c r="AY81" s="5" t="n">
         <v>3480</v>
       </c>
-      <c r="AX81" s="5" t="n">
-        <v>4020</v>
-      </c>
-      <c r="AY81" s="5" t="n">
+      <c r="AZ81" s="5" t="n">
         <v>1590</v>
       </c>
-      <c r="AZ81" s="5" t="n">
+      <c r="BA81" s="5" t="n">
         <v>5820</v>
-      </c>
-      <c r="BA81" s="5" t="n">
-        <v>6540</v>
       </c>
       <c r="BB81" s="5" t="n">
         <v>2670</v>
@@ -23924,7 +23924,7 @@
         <v>0.45</v>
       </c>
       <c r="AF82" s="5" t="n">
-        <v>6350</v>
+        <v>6360</v>
       </c>
       <c r="AG82" s="5" t="n">
         <v>3570</v>
@@ -23975,19 +23975,19 @@
         <v>92</v>
       </c>
       <c r="AW82" s="5" t="n">
+        <v>4220</v>
+      </c>
+      <c r="AX82" s="5" t="n">
+        <v>5930</v>
+      </c>
+      <c r="AY82" s="5" t="n">
         <v>3240</v>
       </c>
-      <c r="AX82" s="5" t="n">
-        <v>4220</v>
-      </c>
-      <c r="AY82" s="5" t="n">
+      <c r="AZ82" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="AZ82" s="5" t="n">
+      <c r="BA82" s="5" t="n">
         <v>4630</v>
-      </c>
-      <c r="BA82" s="5" t="n">
-        <v>5930</v>
       </c>
       <c r="BB82" s="5" t="n">
         <v>2170</v>
@@ -24236,19 +24236,19 @@
         <v>92</v>
       </c>
       <c r="AW83" s="5" t="n">
+        <v>4790</v>
+      </c>
+      <c r="AX83" s="5" t="n">
+        <v>7410</v>
+      </c>
+      <c r="AY83" s="5" t="n">
         <v>3870</v>
       </c>
-      <c r="AX83" s="5" t="n">
-        <v>4790</v>
-      </c>
-      <c r="AY83" s="5" t="n">
+      <c r="AZ83" s="5" t="n">
         <v>1890</v>
       </c>
-      <c r="AZ83" s="5" t="n">
+      <c r="BA83" s="5" t="n">
         <v>6960</v>
-      </c>
-      <c r="BA83" s="5" t="n">
-        <v>7410</v>
       </c>
       <c r="BB83" s="5" t="n">
         <v>3340</v>
@@ -24446,7 +24446,7 @@
         <v>0.32</v>
       </c>
       <c r="AF84" s="5" t="n">
-        <v>4400</v>
+        <v>4410</v>
       </c>
       <c r="AG84" s="5" t="n">
         <v>3289</v>
@@ -24497,19 +24497,19 @@
         <v>92</v>
       </c>
       <c r="AW84" s="5" t="n">
+        <v>2360</v>
+      </c>
+      <c r="AX84" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="AY84" s="5" t="n">
         <v>1740</v>
       </c>
-      <c r="AX84" s="5" t="n">
-        <v>2360</v>
-      </c>
-      <c r="AY84" s="5" t="n">
+      <c r="AZ84" s="5" t="n">
         <v>780</v>
       </c>
-      <c r="AZ84" s="5" t="n">
+      <c r="BA84" s="5" t="n">
         <v>2730</v>
-      </c>
-      <c r="BA84" s="5" t="n">
-        <v>3400</v>
       </c>
       <c r="BB84" s="5" t="n">
         <v>1230</v>
@@ -24707,7 +24707,7 @@
         <v>0.39</v>
       </c>
       <c r="AF85" s="5" t="n">
-        <v>3960</v>
+        <v>3950</v>
       </c>
       <c r="AG85" s="5" t="n">
         <v>1422</v>
@@ -24758,19 +24758,19 @@
         <v>92</v>
       </c>
       <c r="AW85" s="5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="AX85" s="5" t="n">
+        <v>3230</v>
+      </c>
+      <c r="AY85" s="5" t="n">
         <v>2200</v>
       </c>
-      <c r="AX85" s="5" t="n">
-        <v>2180</v>
-      </c>
-      <c r="AY85" s="5" t="n">
+      <c r="AZ85" s="5" t="n">
         <v>1030</v>
       </c>
-      <c r="AZ85" s="5" t="n">
+      <c r="BA85" s="5" t="n">
         <v>3300</v>
-      </c>
-      <c r="BA85" s="5" t="n">
-        <v>3230</v>
       </c>
       <c r="BB85" s="5" t="n">
         <v>1580</v>
@@ -25019,19 +25019,19 @@
         <v>105</v>
       </c>
       <c r="AW86" s="5" t="n">
+        <v>1970</v>
+      </c>
+      <c r="AX86" s="5" t="n">
+        <v>3850</v>
+      </c>
+      <c r="AY86" s="5" t="n">
         <v>2430</v>
       </c>
-      <c r="AX86" s="5" t="n">
-        <v>1970</v>
-      </c>
-      <c r="AY86" s="5" t="n">
+      <c r="AZ86" s="5" t="n">
         <v>1210</v>
       </c>
-      <c r="AZ86" s="5" t="n">
+      <c r="BA86" s="5" t="n">
         <v>5040</v>
-      </c>
-      <c r="BA86" s="5" t="n">
-        <v>3850</v>
       </c>
       <c r="BB86" s="5" t="n">
         <v>2480</v>
@@ -25280,19 +25280,19 @@
         <v>105</v>
       </c>
       <c r="AW87" s="5" t="n">
+        <v>12210</v>
+      </c>
+      <c r="AX87" s="5" t="n">
+        <v>14930</v>
+      </c>
+      <c r="AY87" s="5" t="n">
         <v>13460</v>
       </c>
-      <c r="AX87" s="5" t="n">
-        <v>12210</v>
-      </c>
-      <c r="AY87" s="5" t="n">
+      <c r="AZ87" s="5" t="n">
         <v>6890</v>
       </c>
-      <c r="AZ87" s="5" t="n">
+      <c r="BA87" s="5" t="n">
         <v>16620</v>
-      </c>
-      <c r="BA87" s="5" t="n">
-        <v>14930</v>
       </c>
       <c r="BB87" s="5" t="n">
         <v>8480</v>
@@ -25541,19 +25541,19 @@
         <v>92</v>
       </c>
       <c r="AW88" s="5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="AX88" s="5" t="n">
+        <v>4970</v>
+      </c>
+      <c r="AY88" s="5" t="n">
         <v>2700</v>
       </c>
-      <c r="AX88" s="5" t="n">
-        <v>2590</v>
-      </c>
-      <c r="AY88" s="5" t="n">
+      <c r="AZ88" s="5" t="n">
         <v>1160</v>
       </c>
-      <c r="AZ88" s="5" t="n">
+      <c r="BA88" s="5" t="n">
         <v>5220</v>
-      </c>
-      <c r="BA88" s="5" t="n">
-        <v>4970</v>
       </c>
       <c r="BB88" s="5" t="n">
         <v>2360</v>
@@ -25802,19 +25802,19 @@
         <v>92</v>
       </c>
       <c r="AW89" s="5" t="n">
+        <v>5230</v>
+      </c>
+      <c r="AX89" s="5" t="n">
+        <v>7020</v>
+      </c>
+      <c r="AY89" s="5" t="n">
         <v>5250</v>
       </c>
-      <c r="AX89" s="5" t="n">
-        <v>5230</v>
-      </c>
-      <c r="AY89" s="5" t="n">
+      <c r="AZ89" s="5" t="n">
         <v>2400</v>
       </c>
-      <c r="AZ89" s="5" t="n">
+      <c r="BA89" s="5" t="n">
         <v>7490</v>
-      </c>
-      <c r="BA89" s="5" t="n">
-        <v>7020</v>
       </c>
       <c r="BB89" s="5" t="n">
         <v>3490</v>
@@ -26012,7 +26012,7 @@
         <v>0.55</v>
       </c>
       <c r="AF90" s="5" t="n">
-        <v>6540</v>
+        <v>6550</v>
       </c>
       <c r="AG90" s="5" t="n">
         <v>3824</v>
@@ -26063,19 +26063,19 @@
         <v>92</v>
       </c>
       <c r="AW90" s="5" t="n">
+        <v>6160</v>
+      </c>
+      <c r="AX90" s="5" t="n">
+        <v>7760</v>
+      </c>
+      <c r="AY90" s="5" t="n">
         <v>6880</v>
       </c>
-      <c r="AX90" s="5" t="n">
-        <v>6160</v>
-      </c>
-      <c r="AY90" s="5" t="n">
+      <c r="AZ90" s="5" t="n">
         <v>2880</v>
       </c>
-      <c r="AZ90" s="5" t="n">
+      <c r="BA90" s="5" t="n">
         <v>9150</v>
-      </c>
-      <c r="BA90" s="5" t="n">
-        <v>7760</v>
       </c>
       <c r="BB90" s="5" t="n">
         <v>3880</v>
@@ -26324,19 +26324,19 @@
         <v>105</v>
       </c>
       <c r="AW91" s="5" t="n">
+        <v>14820</v>
+      </c>
+      <c r="AX91" s="5" t="n">
+        <v>19830</v>
+      </c>
+      <c r="AY91" s="5" t="n">
         <v>26260</v>
       </c>
-      <c r="AX91" s="5" t="n">
-        <v>14820</v>
-      </c>
-      <c r="AY91" s="5" t="n">
+      <c r="AZ91" s="5" t="n">
         <v>11040</v>
       </c>
-      <c r="AZ91" s="5" t="n">
+      <c r="BA91" s="5" t="n">
         <v>35710</v>
-      </c>
-      <c r="BA91" s="5" t="n">
-        <v>19830</v>
       </c>
       <c r="BB91" s="5" t="n">
         <v>14970</v>
@@ -26534,7 +26534,7 @@
         <v>0.41</v>
       </c>
       <c r="AF92" s="5" t="n">
-        <v>4710</v>
+        <v>4700</v>
       </c>
       <c r="AG92" s="5" t="n">
         <v>2725</v>
@@ -26585,19 +26585,19 @@
         <v>96</v>
       </c>
       <c r="AW92" s="5" t="n">
+        <v>3820</v>
+      </c>
+      <c r="AX92" s="5" t="n">
+        <v>6050</v>
+      </c>
+      <c r="AY92" s="5" t="n">
         <v>4020</v>
       </c>
-      <c r="AX92" s="5" t="n">
-        <v>3820</v>
-      </c>
-      <c r="AY92" s="5" t="n">
+      <c r="AZ92" s="5" t="n">
         <v>1670</v>
       </c>
-      <c r="AZ92" s="5" t="n">
+      <c r="BA92" s="5" t="n">
         <v>6650</v>
-      </c>
-      <c r="BA92" s="5" t="n">
-        <v>6050</v>
       </c>
       <c r="BB92" s="5" t="n">
         <v>2880</v>
@@ -26846,19 +26846,19 @@
         <v>92</v>
       </c>
       <c r="AW93" s="5" t="n">
+        <v>3660</v>
+      </c>
+      <c r="AX93" s="5" t="n">
+        <v>5050</v>
+      </c>
+      <c r="AY93" s="5" t="n">
         <v>5510</v>
       </c>
-      <c r="AX93" s="5" t="n">
-        <v>3660</v>
-      </c>
-      <c r="AY93" s="5" t="n">
+      <c r="AZ93" s="5" t="n">
         <v>2330</v>
       </c>
-      <c r="AZ93" s="5" t="n">
+      <c r="BA93" s="5" t="n">
         <v>7710</v>
-      </c>
-      <c r="BA93" s="5" t="n">
-        <v>5050</v>
       </c>
       <c r="BB93" s="5" t="n">
         <v>3300</v>
@@ -27107,19 +27107,19 @@
         <v>105</v>
       </c>
       <c r="AW94" s="5" t="n">
+        <v>6390</v>
+      </c>
+      <c r="AX94" s="5" t="n">
+        <v>9360</v>
+      </c>
+      <c r="AY94" s="5" t="n">
         <v>11210</v>
       </c>
-      <c r="AX94" s="5" t="n">
-        <v>6390</v>
-      </c>
-      <c r="AY94" s="5" t="n">
+      <c r="AZ94" s="5" t="n">
         <v>4770</v>
       </c>
-      <c r="AZ94" s="5" t="n">
+      <c r="BA94" s="5" t="n">
         <v>16730</v>
-      </c>
-      <c r="BA94" s="5" t="n">
-        <v>9360</v>
       </c>
       <c r="BB94" s="5" t="n">
         <v>7190</v>
@@ -27317,7 +27317,7 @@
         <v>0.3</v>
       </c>
       <c r="AF95" s="5" t="n">
-        <v>4990</v>
+        <v>4980</v>
       </c>
       <c r="AG95" s="5" t="n">
         <v>1921</v>
@@ -27368,19 +27368,19 @@
         <v>105</v>
       </c>
       <c r="AW95" s="5" t="n">
+        <v>4520</v>
+      </c>
+      <c r="AX95" s="5" t="n">
+        <v>8390</v>
+      </c>
+      <c r="AY95" s="5" t="n">
         <v>5600</v>
       </c>
-      <c r="AX95" s="5" t="n">
-        <v>4520</v>
-      </c>
-      <c r="AY95" s="5" t="n">
+      <c r="AZ95" s="5" t="n">
         <v>2400</v>
       </c>
-      <c r="AZ95" s="5" t="n">
+      <c r="BA95" s="5" t="n">
         <v>10440</v>
-      </c>
-      <c r="BA95" s="5" t="n">
-        <v>8390</v>
       </c>
       <c r="BB95" s="5" t="n">
         <v>4680</v>
@@ -27578,7 +27578,7 @@
         <v>0.36</v>
       </c>
       <c r="AF96" s="5" t="n">
-        <v>7650</v>
+        <v>7630</v>
       </c>
       <c r="AG96" s="5" t="n">
         <v>2150</v>
@@ -27629,19 +27629,19 @@
         <v>96</v>
       </c>
       <c r="AW96" s="5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="AX96" s="5" t="n">
+        <v>4430</v>
+      </c>
+      <c r="AY96" s="5" t="n">
         <v>2760</v>
       </c>
-      <c r="AX96" s="5" t="n">
-        <v>2590</v>
-      </c>
-      <c r="AY96" s="5" t="n">
+      <c r="AZ96" s="5" t="n">
         <v>1080</v>
       </c>
-      <c r="AZ96" s="5" t="n">
+      <c r="BA96" s="5" t="n">
         <v>5060</v>
-      </c>
-      <c r="BA96" s="5" t="n">
-        <v>4430</v>
       </c>
       <c r="BB96" s="5" t="n">
         <v>2120</v>
@@ -27890,19 +27890,19 @@
         <v>92</v>
       </c>
       <c r="AW97" s="5" t="n">
+        <v>6370</v>
+      </c>
+      <c r="AX97" s="5" t="n">
+        <v>9310</v>
+      </c>
+      <c r="AY97" s="5" t="n">
         <v>10020</v>
       </c>
-      <c r="AX97" s="5" t="n">
-        <v>6370</v>
-      </c>
-      <c r="AY97" s="5" t="n">
+      <c r="AZ97" s="5" t="n">
         <v>4150</v>
       </c>
-      <c r="AZ97" s="5" t="n">
+      <c r="BA97" s="5" t="n">
         <v>14840</v>
-      </c>
-      <c r="BA97" s="5" t="n">
-        <v>9310</v>
       </c>
       <c r="BB97" s="5" t="n">
         <v>6170</v>
@@ -28151,19 +28151,19 @@
         <v>105</v>
       </c>
       <c r="AW98" s="5" t="n">
+        <v>8810</v>
+      </c>
+      <c r="AX98" s="5" t="n">
+        <v>10600</v>
+      </c>
+      <c r="AY98" s="5" t="n">
         <v>11850</v>
       </c>
-      <c r="AX98" s="5" t="n">
-        <v>8810</v>
-      </c>
-      <c r="AY98" s="5" t="n">
+      <c r="AZ98" s="5" t="n">
         <v>4850</v>
       </c>
-      <c r="AZ98" s="5" t="n">
+      <c r="BA98" s="5" t="n">
         <v>13710</v>
-      </c>
-      <c r="BA98" s="5" t="n">
-        <v>10600</v>
       </c>
       <c r="BB98" s="5" t="n">
         <v>5630</v>
@@ -28361,7 +28361,7 @@
         <v>0.31</v>
       </c>
       <c r="AF99" s="5" t="n">
-        <v>2480</v>
+        <v>2530</v>
       </c>
       <c r="AG99" s="5" t="n">
         <v>2435</v>
@@ -28412,19 +28412,19 @@
         <v>92</v>
       </c>
       <c r="AW99" s="5" t="n">
+        <v>4820</v>
+      </c>
+      <c r="AX99" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="AY99" s="5" t="n">
         <v>4670</v>
       </c>
-      <c r="AX99" s="5" t="n">
-        <v>4820</v>
-      </c>
-      <c r="AY99" s="5" t="n">
+      <c r="AZ99" s="5" t="n">
         <v>1880</v>
       </c>
-      <c r="AZ99" s="5" t="n">
+      <c r="BA99" s="5" t="n">
         <v>6560</v>
-      </c>
-      <c r="BA99" s="5" t="n">
-        <v>7010</v>
       </c>
       <c r="BB99" s="5" t="n">
         <v>2680</v>
@@ -28622,7 +28622,7 @@
         <v>0.27</v>
       </c>
       <c r="AF100" s="5" t="n">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="AG100" s="5" t="n">
         <v>226</v>
@@ -28673,19 +28673,19 @@
         <v>92</v>
       </c>
       <c r="AW100" s="5" t="n">
+        <v>6980</v>
+      </c>
+      <c r="AX100" s="5" t="n">
+        <v>9510</v>
+      </c>
+      <c r="AY100" s="5" t="n">
         <v>10880</v>
       </c>
-      <c r="AX100" s="5" t="n">
-        <v>6980</v>
-      </c>
-      <c r="AY100" s="5" t="n">
+      <c r="AZ100" s="5" t="n">
         <v>4610</v>
       </c>
-      <c r="AZ100" s="5" t="n">
+      <c r="BA100" s="5" t="n">
         <v>14780</v>
-      </c>
-      <c r="BA100" s="5" t="n">
-        <v>9510</v>
       </c>
       <c r="BB100" s="5" t="n">
         <v>6290</v>
@@ -28934,19 +28934,19 @@
         <v>96</v>
       </c>
       <c r="AW101" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AX101" s="5" t="n">
+        <v>8100</v>
+      </c>
+      <c r="AY101" s="5" t="n">
         <v>3370</v>
       </c>
-      <c r="AX101" s="5" t="n">
-        <v>4100</v>
-      </c>
-      <c r="AY101" s="5" t="n">
+      <c r="AZ101" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="AZ101" s="5" t="n">
+      <c r="BA101" s="5" t="n">
         <v>7410</v>
-      </c>
-      <c r="BA101" s="5" t="n">
-        <v>8100</v>
       </c>
       <c r="BB101" s="5" t="n">
         <v>3740</v>
@@ -29144,7 +29144,7 @@
         <v>0.48</v>
       </c>
       <c r="AF102" s="5" t="n">
-        <v>3700</v>
+        <v>3710</v>
       </c>
       <c r="AG102" s="5" t="n">
         <v>3711</v>
@@ -29195,19 +29195,19 @@
         <v>92</v>
       </c>
       <c r="AW102" s="5" t="n">
+        <v>2980</v>
+      </c>
+      <c r="AX102" s="5" t="n">
+        <v>4210</v>
+      </c>
+      <c r="AY102" s="5" t="n">
         <v>3270</v>
       </c>
-      <c r="AX102" s="5" t="n">
-        <v>2980</v>
-      </c>
-      <c r="AY102" s="5" t="n">
+      <c r="AZ102" s="5" t="n">
         <v>1300</v>
       </c>
-      <c r="AZ102" s="5" t="n">
+      <c r="BA102" s="5" t="n">
         <v>4620</v>
-      </c>
-      <c r="BA102" s="5" t="n">
-        <v>4210</v>
       </c>
       <c r="BB102" s="5" t="n">
         <v>1830</v>
@@ -29405,7 +29405,7 @@
         <v>0.56</v>
       </c>
       <c r="AF103" s="5" t="n">
-        <v>3440</v>
+        <v>3420</v>
       </c>
       <c r="AG103" s="5" t="n">
         <v>805</v>
@@ -29456,19 +29456,19 @@
         <v>96</v>
       </c>
       <c r="AW103" s="5" t="n">
+        <v>5370</v>
+      </c>
+      <c r="AX103" s="5" t="n">
+        <v>9800</v>
+      </c>
+      <c r="AY103" s="5" t="n">
         <v>6870</v>
       </c>
-      <c r="AX103" s="5" t="n">
-        <v>5370</v>
-      </c>
-      <c r="AY103" s="5" t="n">
+      <c r="AZ103" s="5" t="n">
         <v>3330</v>
       </c>
-      <c r="AZ103" s="5" t="n">
+      <c r="BA103" s="5" t="n">
         <v>12490</v>
-      </c>
-      <c r="BA103" s="5" t="n">
-        <v>9800</v>
       </c>
       <c r="BB103" s="5" t="n">
         <v>6160</v>
@@ -29666,7 +29666,7 @@
         <v>0.46</v>
       </c>
       <c r="AF104" s="5" t="n">
-        <v>3780</v>
+        <v>3760</v>
       </c>
       <c r="AG104" s="5" t="n">
         <v>3485</v>
@@ -29717,19 +29717,19 @@
         <v>92</v>
       </c>
       <c r="AW104" s="5" t="n">
+        <v>3080</v>
+      </c>
+      <c r="AX104" s="5" t="n">
+        <v>5030</v>
+      </c>
+      <c r="AY104" s="5" t="n">
         <v>3110</v>
       </c>
-      <c r="AX104" s="5" t="n">
-        <v>3080</v>
-      </c>
-      <c r="AY104" s="5" t="n">
+      <c r="AZ104" s="5" t="n">
         <v>1430</v>
       </c>
-      <c r="AZ104" s="5" t="n">
+      <c r="BA104" s="5" t="n">
         <v>5470</v>
-      </c>
-      <c r="BA104" s="5" t="n">
-        <v>5030</v>
       </c>
       <c r="BB104" s="5" t="n">
         <v>2540</v>
@@ -29978,19 +29978,19 @@
         <v>92</v>
       </c>
       <c r="AW105" s="5" t="n">
+        <v>2670</v>
+      </c>
+      <c r="AX105" s="5" t="n">
+        <v>3740</v>
+      </c>
+      <c r="AY105" s="5" t="n">
         <v>2950</v>
       </c>
-      <c r="AX105" s="5" t="n">
-        <v>2670</v>
-      </c>
-      <c r="AY105" s="5" t="n">
+      <c r="AZ105" s="5" t="n">
         <v>1190</v>
       </c>
-      <c r="AZ105" s="5" t="n">
+      <c r="BA105" s="5" t="n">
         <v>4180</v>
-      </c>
-      <c r="BA105" s="5" t="n">
-        <v>3740</v>
       </c>
       <c r="BB105" s="5" t="n">
         <v>1720</v>
@@ -30239,19 +30239,19 @@
         <v>96</v>
       </c>
       <c r="AW106" s="5" t="n">
+        <v>5030</v>
+      </c>
+      <c r="AX106" s="5" t="n">
+        <v>10210</v>
+      </c>
+      <c r="AY106" s="5" t="n">
         <v>7840</v>
       </c>
-      <c r="AX106" s="5" t="n">
-        <v>5030</v>
-      </c>
-      <c r="AY106" s="5" t="n">
+      <c r="AZ106" s="5" t="n">
         <v>3350</v>
       </c>
-      <c r="AZ106" s="5" t="n">
+      <c r="BA106" s="5" t="n">
         <v>15810</v>
-      </c>
-      <c r="BA106" s="5" t="n">
-        <v>10210</v>
       </c>
       <c r="BB106" s="5" t="n">
         <v>6800</v>
@@ -30500,19 +30500,19 @@
         <v>92</v>
       </c>
       <c r="AW107" s="5" t="n">
+        <v>3380</v>
+      </c>
+      <c r="AX107" s="5" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AY107" s="5" t="n">
         <v>3580</v>
       </c>
-      <c r="AX107" s="5" t="n">
-        <v>3380</v>
-      </c>
-      <c r="AY107" s="5" t="n">
+      <c r="AZ107" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="AZ107" s="5" t="n">
+      <c r="BA107" s="5" t="n">
         <v>5830</v>
-      </c>
-      <c r="BA107" s="5" t="n">
-        <v>5300</v>
       </c>
       <c r="BB107" s="5" t="n">
         <v>2510</v>
@@ -30710,7 +30710,7 @@
         <v>0.44</v>
       </c>
       <c r="AF108" s="5" t="n">
-        <v>3590</v>
+        <v>3620</v>
       </c>
       <c r="AG108" s="5" t="n">
         <v>1831</v>
@@ -30761,19 +30761,19 @@
         <v>92</v>
       </c>
       <c r="AW108" s="5" t="n">
+        <v>3980</v>
+      </c>
+      <c r="AX108" s="5" t="n">
+        <v>6140</v>
+      </c>
+      <c r="AY108" s="5" t="n">
         <v>4410</v>
       </c>
-      <c r="AX108" s="5" t="n">
-        <v>3980</v>
-      </c>
-      <c r="AY108" s="5" t="n">
+      <c r="AZ108" s="5" t="n">
         <v>1940</v>
       </c>
-      <c r="AZ108" s="5" t="n">
+      <c r="BA108" s="5" t="n">
         <v>7230</v>
-      </c>
-      <c r="BA108" s="5" t="n">
-        <v>6140</v>
       </c>
       <c r="BB108" s="5" t="n">
         <v>3210</v>
@@ -30971,7 +30971,7 @@
         <v>0.46</v>
       </c>
       <c r="AF109" s="5" t="n">
-        <v>4840</v>
+        <v>4850</v>
       </c>
       <c r="AG109" s="5" t="n">
         <v>2742</v>
@@ -31022,19 +31022,19 @@
         <v>105</v>
       </c>
       <c r="AW109" s="5" t="n">
+        <v>3680</v>
+      </c>
+      <c r="AX109" s="5" t="n">
+        <v>5770</v>
+      </c>
+      <c r="AY109" s="5" t="n">
         <v>5070</v>
       </c>
-      <c r="AX109" s="5" t="n">
-        <v>3680</v>
-      </c>
-      <c r="AY109" s="5" t="n">
+      <c r="AZ109" s="5" t="n">
         <v>2150</v>
       </c>
-      <c r="AZ109" s="5" t="n">
+      <c r="BA109" s="5" t="n">
         <v>8450</v>
-      </c>
-      <c r="BA109" s="5" t="n">
-        <v>5770</v>
       </c>
       <c r="BB109" s="5" t="n">
         <v>3620</v>
@@ -31232,7 +31232,7 @@
         <v>0.4</v>
       </c>
       <c r="AF110" s="5" t="n">
-        <v>5740</v>
+        <v>5750</v>
       </c>
       <c r="AG110" s="5" t="n">
         <v>1919</v>
@@ -31283,19 +31283,19 @@
         <v>92</v>
       </c>
       <c r="AW110" s="5" t="n">
+        <v>1660</v>
+      </c>
+      <c r="AX110" s="5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="AY110" s="5" t="n">
         <v>2070</v>
       </c>
-      <c r="AX110" s="5" t="n">
-        <v>1660</v>
-      </c>
-      <c r="AY110" s="5" t="n">
+      <c r="AZ110" s="5" t="n">
         <v>910</v>
       </c>
-      <c r="AZ110" s="5" t="n">
+      <c r="BA110" s="5" t="n">
         <v>3670</v>
-      </c>
-      <c r="BA110" s="5" t="n">
-        <v>2780</v>
       </c>
       <c r="BB110" s="5" t="n">
         <v>1650</v>
@@ -31493,7 +31493,7 @@
         <v>0.36</v>
       </c>
       <c r="AF111" s="5" t="n">
-        <v>4780</v>
+        <v>4770</v>
       </c>
       <c r="AG111" s="5" t="n">
         <v>530</v>
@@ -31544,19 +31544,19 @@
         <v>105</v>
       </c>
       <c r="AW111" s="5" t="n">
+        <v>1970</v>
+      </c>
+      <c r="AX111" s="5" t="n">
+        <v>3160</v>
+      </c>
+      <c r="AY111" s="5" t="n">
         <v>3210</v>
       </c>
-      <c r="AX111" s="5" t="n">
-        <v>1970</v>
-      </c>
-      <c r="AY111" s="5" t="n">
+      <c r="AZ111" s="5" t="n">
         <v>1430</v>
       </c>
-      <c r="AZ111" s="5" t="n">
+      <c r="BA111" s="5" t="n">
         <v>5330</v>
-      </c>
-      <c r="BA111" s="5" t="n">
-        <v>3160</v>
       </c>
       <c r="BB111" s="5" t="n">
         <v>2370</v>
@@ -31805,19 +31805,19 @@
         <v>105</v>
       </c>
       <c r="AW112" s="5" t="n">
+        <v>2520</v>
+      </c>
+      <c r="AX112" s="5" t="n">
+        <v>3690</v>
+      </c>
+      <c r="AY112" s="5" t="n">
         <v>3610</v>
       </c>
-      <c r="AX112" s="5" t="n">
-        <v>2520</v>
-      </c>
-      <c r="AY112" s="5" t="n">
+      <c r="AZ112" s="5" t="n">
         <v>1620</v>
       </c>
-      <c r="AZ112" s="5" t="n">
+      <c r="BA112" s="5" t="n">
         <v>5410</v>
-      </c>
-      <c r="BA112" s="5" t="n">
-        <v>3690</v>
       </c>
       <c r="BB112" s="5" t="n">
         <v>2450</v>
@@ -32015,7 +32015,7 @@
         <v>0.28</v>
       </c>
       <c r="AF113" s="5" t="n">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="AG113" s="5" t="n">
         <v>558</v>
@@ -32066,19 +32066,19 @@
         <v>92</v>
       </c>
       <c r="AW113" s="5" t="n">
+        <v>930</v>
+      </c>
+      <c r="AX113" s="5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="AY113" s="5" t="n">
         <v>1220</v>
       </c>
-      <c r="AX113" s="5" t="n">
-        <v>930</v>
-      </c>
-      <c r="AY113" s="5" t="n">
+      <c r="AZ113" s="5" t="n">
         <v>630</v>
       </c>
-      <c r="AZ113" s="5" t="n">
+      <c r="BA113" s="5" t="n">
         <v>2650</v>
-      </c>
-      <c r="BA113" s="5" t="n">
-        <v>1820</v>
       </c>
       <c r="BB113" s="5" t="n">
         <v>1230</v>
@@ -32276,7 +32276,7 @@
         <v>0.38</v>
       </c>
       <c r="AF114" s="5" t="n">
-        <v>3180</v>
+        <v>3170</v>
       </c>
       <c r="AG114" s="5" t="n">
         <v>701</v>
@@ -32327,19 +32327,19 @@
         <v>92</v>
       </c>
       <c r="AW114" s="5" t="n">
+        <v>2380</v>
+      </c>
+      <c r="AX114" s="5" t="n">
+        <v>3470</v>
+      </c>
+      <c r="AY114" s="5" t="n">
         <v>3690</v>
       </c>
-      <c r="AX114" s="5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="AY114" s="5" t="n">
+      <c r="AZ114" s="5" t="n">
         <v>1580</v>
       </c>
-      <c r="AZ114" s="5" t="n">
+      <c r="BA114" s="5" t="n">
         <v>5550</v>
-      </c>
-      <c r="BA114" s="5" t="n">
-        <v>3470</v>
       </c>
       <c r="BB114" s="5" t="n">
         <v>2370</v>
@@ -32588,19 +32588,19 @@
         <v>96</v>
       </c>
       <c r="AW115" s="5" t="n">
+        <v>3740</v>
+      </c>
+      <c r="AX115" s="5" t="n">
+        <v>6030</v>
+      </c>
+      <c r="AY115" s="5" t="n">
         <v>6430</v>
       </c>
-      <c r="AX115" s="5" t="n">
-        <v>3740</v>
-      </c>
-      <c r="AY115" s="5" t="n">
+      <c r="AZ115" s="5" t="n">
         <v>2830</v>
       </c>
-      <c r="AZ115" s="5" t="n">
+      <c r="BA115" s="5" t="n">
         <v>10360</v>
-      </c>
-      <c r="BA115" s="5" t="n">
-        <v>6030</v>
       </c>
       <c r="BB115" s="5" t="n">
         <v>4620</v>
@@ -32849,19 +32849,19 @@
         <v>92</v>
       </c>
       <c r="AW116" s="5" t="n">
+        <v>4060</v>
+      </c>
+      <c r="AX116" s="5" t="n">
+        <v>6180</v>
+      </c>
+      <c r="AY116" s="5" t="n">
         <v>5420</v>
       </c>
-      <c r="AX116" s="5" t="n">
-        <v>4060</v>
-      </c>
-      <c r="AY116" s="5" t="n">
+      <c r="AZ116" s="5" t="n">
         <v>2380</v>
       </c>
-      <c r="AZ116" s="5" t="n">
+      <c r="BA116" s="5" t="n">
         <v>8350</v>
-      </c>
-      <c r="BA116" s="5" t="n">
-        <v>6180</v>
       </c>
       <c r="BB116" s="5" t="n">
         <v>3720</v>
@@ -33110,19 +33110,19 @@
         <v>96</v>
       </c>
       <c r="AW117" s="5" t="n">
+        <v>1240</v>
+      </c>
+      <c r="AX117" s="5" t="n">
+        <v>2710</v>
+      </c>
+      <c r="AY117" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="AX117" s="5" t="n">
-        <v>1240</v>
-      </c>
-      <c r="AY117" s="5" t="n">
+      <c r="AZ117" s="5" t="n">
         <v>650</v>
       </c>
-      <c r="AZ117" s="5" t="n">
+      <c r="BA117" s="5" t="n">
         <v>3650</v>
-      </c>
-      <c r="BA117" s="5" t="n">
-        <v>2710</v>
       </c>
       <c r="BB117" s="5" t="n">
         <v>1550</v>
@@ -33371,19 +33371,19 @@
         <v>92</v>
       </c>
       <c r="AW118" s="5" t="n">
+        <v>2160</v>
+      </c>
+      <c r="AX118" s="5" t="n">
+        <v>3640</v>
+      </c>
+      <c r="AY118" s="5" t="n">
         <v>2860</v>
       </c>
-      <c r="AX118" s="5" t="n">
-        <v>2160</v>
-      </c>
-      <c r="AY118" s="5" t="n">
+      <c r="AZ118" s="5" t="n">
         <v>1260</v>
       </c>
-      <c r="AZ118" s="5" t="n">
+      <c r="BA118" s="5" t="n">
         <v>4940</v>
-      </c>
-      <c r="BA118" s="5" t="n">
-        <v>3640</v>
       </c>
       <c r="BB118" s="5" t="n">
         <v>2230</v>
@@ -33581,7 +33581,7 @@
         <v>0.68</v>
       </c>
       <c r="AF119" s="5" t="n">
-        <v>5520</v>
+        <v>5540</v>
       </c>
       <c r="AG119" s="5" t="n">
         <v>2728</v>
@@ -33632,19 +33632,19 @@
         <v>92</v>
       </c>
       <c r="AW119" s="5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="AX119" s="5" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AY119" s="5" t="n">
         <v>2850</v>
       </c>
-      <c r="AX119" s="5" t="n">
-        <v>2180</v>
-      </c>
-      <c r="AY119" s="5" t="n">
+      <c r="AZ119" s="5" t="n">
         <v>1180</v>
       </c>
-      <c r="AZ119" s="5" t="n">
+      <c r="BA119" s="5" t="n">
         <v>4760</v>
-      </c>
-      <c r="BA119" s="5" t="n">
-        <v>3700</v>
       </c>
       <c r="BB119" s="5" t="n">
         <v>2060</v>
@@ -33893,19 +33893,19 @@
         <v>105</v>
       </c>
       <c r="AW120" s="5" t="n">
+        <v>2140</v>
+      </c>
+      <c r="AX120" s="5" t="n">
+        <v>4590</v>
+      </c>
+      <c r="AY120" s="5" t="n">
         <v>3680</v>
       </c>
-      <c r="AX120" s="5" t="n">
-        <v>2140</v>
-      </c>
-      <c r="AY120" s="5" t="n">
+      <c r="AZ120" s="5" t="n">
         <v>1490</v>
       </c>
-      <c r="AZ120" s="5" t="n">
+      <c r="BA120" s="5" t="n">
         <v>8250</v>
-      </c>
-      <c r="BA120" s="5" t="n">
-        <v>4590</v>
       </c>
       <c r="BB120" s="5" t="n">
         <v>3430</v>
@@ -34154,19 +34154,19 @@
         <v>92</v>
       </c>
       <c r="AW121" s="5" t="n">
+        <v>3540</v>
+      </c>
+      <c r="AX121" s="5" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AY121" s="5" t="n">
         <v>5830</v>
       </c>
-      <c r="AX121" s="5" t="n">
-        <v>3540</v>
-      </c>
-      <c r="AY121" s="5" t="n">
+      <c r="AZ121" s="5" t="n">
         <v>2330</v>
       </c>
-      <c r="AZ121" s="5" t="n">
+      <c r="BA121" s="5" t="n">
         <v>9420</v>
-      </c>
-      <c r="BA121" s="5" t="n">
-        <v>5510</v>
       </c>
       <c r="BB121" s="5" t="n">
         <v>3770</v>
@@ -34415,19 +34415,19 @@
         <v>105</v>
       </c>
       <c r="AW122" s="5" t="n">
+        <v>4370</v>
+      </c>
+      <c r="AX122" s="5" t="n">
+        <v>6720</v>
+      </c>
+      <c r="AY122" s="5" t="n">
         <v>8140</v>
       </c>
-      <c r="AX122" s="5" t="n">
-        <v>4370</v>
-      </c>
-      <c r="AY122" s="5" t="n">
+      <c r="AZ122" s="5" t="n">
         <v>3280</v>
       </c>
-      <c r="AZ122" s="5" t="n">
+      <c r="BA122" s="5" t="n">
         <v>12540</v>
-      </c>
-      <c r="BA122" s="5" t="n">
-        <v>6720</v>
       </c>
       <c r="BB122" s="5" t="n">
         <v>5070</v>
@@ -34676,19 +34676,19 @@
         <v>105</v>
       </c>
       <c r="AW123" s="5" t="n">
+        <v>7940</v>
+      </c>
+      <c r="AX123" s="5" t="n">
+        <v>11570</v>
+      </c>
+      <c r="AY123" s="5" t="n">
         <v>10540</v>
       </c>
-      <c r="AX123" s="5" t="n">
-        <v>7940</v>
-      </c>
-      <c r="AY123" s="5" t="n">
+      <c r="AZ123" s="5" t="n">
         <v>4940</v>
       </c>
-      <c r="AZ123" s="5" t="n">
+      <c r="BA123" s="5" t="n">
         <v>16020</v>
-      </c>
-      <c r="BA123" s="5" t="n">
-        <v>11570</v>
       </c>
       <c r="BB123" s="5" t="n">
         <v>7430</v>
@@ -34937,19 +34937,19 @@
         <v>105</v>
       </c>
       <c r="AW124" s="5" t="n">
+        <v>2040</v>
+      </c>
+      <c r="AX124" s="5" t="n">
+        <v>3480</v>
+      </c>
+      <c r="AY124" s="5" t="n">
         <v>3700</v>
       </c>
-      <c r="AX124" s="5" t="n">
-        <v>2040</v>
-      </c>
-      <c r="AY124" s="5" t="n">
+      <c r="AZ124" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="AZ124" s="5" t="n">
+      <c r="BA124" s="5" t="n">
         <v>6300</v>
-      </c>
-      <c r="BA124" s="5" t="n">
-        <v>3480</v>
       </c>
       <c r="BB124" s="5" t="n">
         <v>2590</v>
@@ -35198,19 +35198,19 @@
         <v>96</v>
       </c>
       <c r="AW125" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AX125" s="5" t="n">
+        <v>2630</v>
+      </c>
+      <c r="AY125" s="5" t="n">
         <v>1960</v>
       </c>
-      <c r="AX125" s="5" t="n">
-        <v>1190</v>
-      </c>
-      <c r="AY125" s="5" t="n">
+      <c r="AZ125" s="5" t="n">
         <v>770</v>
       </c>
-      <c r="AZ125" s="5" t="n">
+      <c r="BA125" s="5" t="n">
         <v>4290</v>
-      </c>
-      <c r="BA125" s="5" t="n">
-        <v>2630</v>
       </c>
       <c r="BB125" s="5" t="n">
         <v>1770</v>
@@ -35408,7 +35408,7 @@
         <v>0.25</v>
       </c>
       <c r="AF126" s="5" t="n">
-        <v>4360</v>
+        <v>4350</v>
       </c>
       <c r="AG126" s="5" t="n">
         <v>2142</v>
@@ -35459,19 +35459,19 @@
         <v>92</v>
       </c>
       <c r="AW126" s="5" t="n">
+        <v>7200</v>
+      </c>
+      <c r="AX126" s="5" t="n">
+        <v>9060</v>
+      </c>
+      <c r="AY126" s="5" t="n">
         <v>7070</v>
       </c>
-      <c r="AX126" s="5" t="n">
-        <v>7200</v>
-      </c>
-      <c r="AY126" s="5" t="n">
+      <c r="AZ126" s="5" t="n">
         <v>2870</v>
       </c>
-      <c r="AZ126" s="5" t="n">
+      <c r="BA126" s="5" t="n">
         <v>9630</v>
-      </c>
-      <c r="BA126" s="5" t="n">
-        <v>9060</v>
       </c>
       <c r="BB126" s="5" t="n">
         <v>3920</v>
@@ -35669,7 +35669,7 @@
         <v>0.39</v>
       </c>
       <c r="AF127" s="5" t="n">
-        <v>3960</v>
+        <v>3970</v>
       </c>
       <c r="AG127" s="5" t="n">
         <v>1296</v>
@@ -35720,19 +35720,19 @@
         <v>105</v>
       </c>
       <c r="AW127" s="5" t="n">
+        <v>7050</v>
+      </c>
+      <c r="AX127" s="5" t="n">
+        <v>10830</v>
+      </c>
+      <c r="AY127" s="5" t="n">
         <v>9000</v>
       </c>
-      <c r="AX127" s="5" t="n">
-        <v>7050</v>
-      </c>
-      <c r="AY127" s="5" t="n">
+      <c r="AZ127" s="5" t="n">
         <v>4210</v>
       </c>
-      <c r="AZ127" s="5" t="n">
+      <c r="BA127" s="5" t="n">
         <v>13850</v>
-      </c>
-      <c r="BA127" s="5" t="n">
-        <v>10830</v>
       </c>
       <c r="BB127" s="5" t="n">
         <v>6360</v>
@@ -35981,19 +35981,19 @@
         <v>105</v>
       </c>
       <c r="AW128" s="5" t="n">
+        <v>1530</v>
+      </c>
+      <c r="AX128" s="5" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AY128" s="5" t="n">
         <v>1900</v>
       </c>
-      <c r="AX128" s="5" t="n">
-        <v>1530</v>
-      </c>
-      <c r="AY128" s="5" t="n">
+      <c r="AZ128" s="5" t="n">
         <v>800</v>
       </c>
-      <c r="AZ128" s="5" t="n">
+      <c r="BA128" s="5" t="n">
         <v>4100</v>
-      </c>
-      <c r="BA128" s="5" t="n">
-        <v>3150</v>
       </c>
       <c r="BB128" s="5" t="n">
         <v>1720</v>
@@ -36242,19 +36242,19 @@
         <v>92</v>
       </c>
       <c r="AW129" s="5" t="n">
+        <v>2280</v>
+      </c>
+      <c r="AX129" s="5" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AY129" s="5" t="n">
         <v>2440</v>
       </c>
-      <c r="AX129" s="5" t="n">
-        <v>2280</v>
-      </c>
-      <c r="AY129" s="5" t="n">
+      <c r="AZ129" s="5" t="n">
         <v>1120</v>
       </c>
-      <c r="AZ129" s="5" t="n">
+      <c r="BA129" s="5" t="n">
         <v>5360</v>
-      </c>
-      <c r="BA129" s="5" t="n">
-        <v>4980</v>
       </c>
       <c r="BB129" s="5" t="n">
         <v>2540</v>
@@ -36503,19 +36503,19 @@
         <v>105</v>
       </c>
       <c r="AW130" s="5" t="n">
+        <v>1310</v>
+      </c>
+      <c r="AX130" s="5" t="n">
+        <v>2890</v>
+      </c>
+      <c r="AY130" s="5" t="n">
         <v>2150</v>
       </c>
-      <c r="AX130" s="5" t="n">
-        <v>1310</v>
-      </c>
-      <c r="AY130" s="5" t="n">
+      <c r="AZ130" s="5" t="n">
         <v>850</v>
       </c>
-      <c r="AZ130" s="5" t="n">
+      <c r="BA130" s="5" t="n">
         <v>4970</v>
-      </c>
-      <c r="BA130" s="5" t="n">
-        <v>2890</v>
       </c>
       <c r="BB130" s="5" t="n">
         <v>1990</v>
@@ -36713,7 +36713,7 @@
         <v>0.45</v>
       </c>
       <c r="AF131" s="5" t="n">
-        <v>4660</v>
+        <v>4640</v>
       </c>
       <c r="AG131" s="5" t="n">
         <v>1954</v>
@@ -36764,19 +36764,19 @@
         <v>105</v>
       </c>
       <c r="AW131" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="AX131" s="5" t="n">
+        <v>8260</v>
+      </c>
+      <c r="AY131" s="5" t="n">
         <v>5570</v>
       </c>
-      <c r="AX131" s="5" t="n">
-        <v>5200</v>
-      </c>
-      <c r="AY131" s="5" t="n">
+      <c r="AZ131" s="5" t="n">
         <v>2300</v>
       </c>
-      <c r="AZ131" s="5" t="n">
+      <c r="BA131" s="5" t="n">
         <v>9680</v>
-      </c>
-      <c r="BA131" s="5" t="n">
-        <v>8260</v>
       </c>
       <c r="BB131" s="5" t="n">
         <v>4040</v>
@@ -36974,7 +36974,7 @@
         <v>0.23</v>
       </c>
       <c r="AF132" s="5" t="n">
-        <v>3110</v>
+        <v>3100</v>
       </c>
       <c r="AG132" s="5" t="n">
         <v>1724</v>
@@ -37025,19 +37025,19 @@
         <v>92</v>
       </c>
       <c r="AW132" s="5" t="n">
+        <v>3260</v>
+      </c>
+      <c r="AX132" s="5" t="n">
+        <v>5030</v>
+      </c>
+      <c r="AY132" s="5" t="n">
         <v>4450</v>
       </c>
-      <c r="AX132" s="5" t="n">
-        <v>3260</v>
-      </c>
-      <c r="AY132" s="5" t="n">
+      <c r="AZ132" s="5" t="n">
         <v>1830</v>
       </c>
-      <c r="AZ132" s="5" t="n">
+      <c r="BA132" s="5" t="n">
         <v>7350</v>
-      </c>
-      <c r="BA132" s="5" t="n">
-        <v>5030</v>
       </c>
       <c r="BB132" s="5" t="n">
         <v>3030</v>
@@ -37235,7 +37235,7 @@
         <v>0.34</v>
       </c>
       <c r="AF133" s="5" t="n">
-        <v>3540</v>
+        <v>3550</v>
       </c>
       <c r="AG133" s="5" t="n">
         <v>995</v>
@@ -37286,19 +37286,19 @@
         <v>92</v>
       </c>
       <c r="AW133" s="5" t="n">
+        <v>3280</v>
+      </c>
+      <c r="AX133" s="5" t="n">
+        <v>6430</v>
+      </c>
+      <c r="AY133" s="5" t="n">
         <v>3960</v>
       </c>
-      <c r="AX133" s="5" t="n">
-        <v>3280</v>
-      </c>
-      <c r="AY133" s="5" t="n">
+      <c r="AZ133" s="5" t="n">
         <v>1760</v>
       </c>
-      <c r="AZ133" s="5" t="n">
+      <c r="BA133" s="5" t="n">
         <v>7520</v>
-      </c>
-      <c r="BA133" s="5" t="n">
-        <v>6430</v>
       </c>
       <c r="BB133" s="5" t="n">
         <v>3480</v>
@@ -37547,19 +37547,19 @@
         <v>105</v>
       </c>
       <c r="AW134" s="5" t="n">
+        <v>4780</v>
+      </c>
+      <c r="AX134" s="5" t="n">
+        <v>8030</v>
+      </c>
+      <c r="AY134" s="5" t="n">
         <v>5580</v>
       </c>
-      <c r="AX134" s="5" t="n">
-        <v>4780</v>
-      </c>
-      <c r="AY134" s="5" t="n">
+      <c r="AZ134" s="5" t="n">
         <v>2120</v>
       </c>
-      <c r="AZ134" s="5" t="n">
+      <c r="BA134" s="5" t="n">
         <v>9990</v>
-      </c>
-      <c r="BA134" s="5" t="n">
-        <v>8030</v>
       </c>
       <c r="BB134" s="5" t="n">
         <v>3950</v>
@@ -37808,19 +37808,19 @@
         <v>96</v>
       </c>
       <c r="AW135" s="5" t="n">
+        <v>2220</v>
+      </c>
+      <c r="AX135" s="5" t="n">
+        <v>4960</v>
+      </c>
+      <c r="AY135" s="5" t="n">
         <v>2620</v>
       </c>
-      <c r="AX135" s="5" t="n">
-        <v>2220</v>
-      </c>
-      <c r="AY135" s="5" t="n">
+      <c r="AZ135" s="5" t="n">
         <v>1240</v>
       </c>
-      <c r="AZ135" s="5" t="n">
+      <c r="BA135" s="5" t="n">
         <v>6110</v>
-      </c>
-      <c r="BA135" s="5" t="n">
-        <v>4960</v>
       </c>
       <c r="BB135" s="5" t="n">
         <v>2920</v>
@@ -38018,7 +38018,7 @@
         <v>0.33</v>
       </c>
       <c r="AF136" s="5" t="n">
-        <v>3180</v>
+        <v>3200</v>
       </c>
       <c r="AG136" s="5" t="n">
         <v>1322</v>
@@ -38069,19 +38069,19 @@
         <v>105</v>
       </c>
       <c r="AW136" s="5" t="n">
+        <v>3590</v>
+      </c>
+      <c r="AX136" s="5" t="n">
+        <v>6590</v>
+      </c>
+      <c r="AY136" s="5" t="n">
         <v>5350</v>
       </c>
-      <c r="AX136" s="5" t="n">
-        <v>3590</v>
-      </c>
-      <c r="AY136" s="5" t="n">
+      <c r="AZ136" s="5" t="n">
         <v>2210</v>
       </c>
-      <c r="AZ136" s="5" t="n">
+      <c r="BA136" s="5" t="n">
         <v>9610</v>
-      </c>
-      <c r="BA136" s="5" t="n">
-        <v>6590</v>
       </c>
       <c r="BB136" s="5" t="n">
         <v>4110</v>
@@ -38330,19 +38330,19 @@
         <v>92</v>
       </c>
       <c r="AW137" s="5" t="n">
+        <v>5710</v>
+      </c>
+      <c r="AX137" s="5" t="n">
+        <v>7360</v>
+      </c>
+      <c r="AY137" s="5" t="n">
         <v>6660</v>
       </c>
-      <c r="AX137" s="5" t="n">
-        <v>5710</v>
-      </c>
-      <c r="AY137" s="5" t="n">
+      <c r="AZ137" s="5" t="n">
         <v>2800</v>
       </c>
-      <c r="AZ137" s="5" t="n">
+      <c r="BA137" s="5" t="n">
         <v>8720</v>
-      </c>
-      <c r="BA137" s="5" t="n">
-        <v>7360</v>
       </c>
       <c r="BB137" s="5" t="n">
         <v>3720</v>
@@ -38591,19 +38591,19 @@
         <v>92</v>
       </c>
       <c r="AW138" s="5" t="n">
+        <v>2460</v>
+      </c>
+      <c r="AX138" s="5" t="n">
+        <v>4330</v>
+      </c>
+      <c r="AY138" s="5" t="n">
         <v>2990</v>
       </c>
-      <c r="AX138" s="5" t="n">
-        <v>2460</v>
-      </c>
-      <c r="AY138" s="5" t="n">
+      <c r="AZ138" s="5" t="n">
         <v>1340</v>
       </c>
-      <c r="AZ138" s="5" t="n">
+      <c r="BA138" s="5" t="n">
         <v>5160</v>
-      </c>
-      <c r="BA138" s="5" t="n">
-        <v>4330</v>
       </c>
       <c r="BB138" s="5" t="n">
         <v>2290</v>
@@ -38801,7 +38801,7 @@
         <v>0.34</v>
       </c>
       <c r="AF139" s="5" t="n">
-        <v>3560</v>
+        <v>3550</v>
       </c>
       <c r="AG139" s="5" t="n">
         <v>703</v>
@@ -38852,19 +38852,19 @@
         <v>92</v>
       </c>
       <c r="AW139" s="5" t="n">
+        <v>2840</v>
+      </c>
+      <c r="AX139" s="5" t="n">
+        <v>4690</v>
+      </c>
+      <c r="AY139" s="5" t="n">
         <v>3810</v>
       </c>
-      <c r="AX139" s="5" t="n">
-        <v>2840</v>
-      </c>
-      <c r="AY139" s="5" t="n">
+      <c r="AZ139" s="5" t="n">
         <v>1530</v>
       </c>
-      <c r="AZ139" s="5" t="n">
+      <c r="BA139" s="5" t="n">
         <v>6690</v>
-      </c>
-      <c r="BA139" s="5" t="n">
-        <v>4690</v>
       </c>
       <c r="BB139" s="5" t="n">
         <v>2760</v>
@@ -39116,16 +39116,16 @@
         <v>2200</v>
       </c>
       <c r="AX140" s="5" t="n">
+        <v>3950</v>
+      </c>
+      <c r="AY140" s="5" t="n">
         <v>2200</v>
       </c>
-      <c r="AY140" s="5" t="n">
+      <c r="AZ140" s="5" t="n">
         <v>960</v>
       </c>
-      <c r="AZ140" s="5" t="n">
+      <c r="BA140" s="5" t="n">
         <v>4420</v>
-      </c>
-      <c r="BA140" s="5" t="n">
-        <v>3950</v>
       </c>
       <c r="BB140" s="5" t="n">
         <v>1990</v>
@@ -39374,19 +39374,19 @@
         <v>105</v>
       </c>
       <c r="AW141" s="5" t="n">
+        <v>1250</v>
+      </c>
+      <c r="AX141" s="5" t="n">
+        <v>2610</v>
+      </c>
+      <c r="AY141" s="5" t="n">
         <v>1160</v>
       </c>
-      <c r="AX141" s="5" t="n">
-        <v>1250</v>
-      </c>
-      <c r="AY141" s="5" t="n">
+      <c r="AZ141" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="AZ141" s="5" t="n">
+      <c r="BA141" s="5" t="n">
         <v>2360</v>
-      </c>
-      <c r="BA141" s="5" t="n">
-        <v>2610</v>
       </c>
       <c r="BB141" s="5" t="n">
         <v>1060</v>
@@ -39584,7 +39584,7 @@
         <v>0.69</v>
       </c>
       <c r="AF142" s="5" t="n">
-        <v>3680</v>
+        <v>3670</v>
       </c>
       <c r="AG142" s="5" t="n">
         <v>582</v>
@@ -39635,19 +39635,19 @@
         <v>92</v>
       </c>
       <c r="AW142" s="5" t="n">
+        <v>3880</v>
+      </c>
+      <c r="AX142" s="5" t="n">
+        <v>6940</v>
+      </c>
+      <c r="AY142" s="5" t="n">
         <v>3820</v>
       </c>
-      <c r="AX142" s="5" t="n">
-        <v>3880</v>
-      </c>
-      <c r="AY142" s="5" t="n">
+      <c r="AZ142" s="5" t="n">
         <v>1690</v>
       </c>
-      <c r="AZ142" s="5" t="n">
+      <c r="BA142" s="5" t="n">
         <v>7670</v>
-      </c>
-      <c r="BA142" s="5" t="n">
-        <v>6940</v>
       </c>
       <c r="BB142" s="5" t="n">
         <v>3300</v>
@@ -39845,7 +39845,7 @@
         <v>0.3</v>
       </c>
       <c r="AF143" s="5" t="n">
-        <v>2120</v>
+        <v>2110</v>
       </c>
       <c r="AG143" s="5" t="n">
         <v>1128</v>
@@ -39896,19 +39896,19 @@
         <v>92</v>
       </c>
       <c r="AW143" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AX143" s="5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AY143" s="5" t="n">
         <v>2400</v>
       </c>
-      <c r="AX143" s="5" t="n">
-        <v>2200</v>
-      </c>
-      <c r="AY143" s="5" t="n">
+      <c r="AZ143" s="5" t="n">
         <v>1090</v>
       </c>
-      <c r="AZ143" s="5" t="n">
+      <c r="BA143" s="5" t="n">
         <v>4120</v>
-      </c>
-      <c r="BA143" s="5" t="n">
-        <v>3600</v>
       </c>
       <c r="BB143" s="5" t="n">
         <v>1850</v>
@@ -40157,19 +40157,19 @@
         <v>105</v>
       </c>
       <c r="AW144" s="5" t="n">
+        <v>4410</v>
+      </c>
+      <c r="AX144" s="5" t="n">
+        <v>9400</v>
+      </c>
+      <c r="AY144" s="5" t="n">
         <v>5610</v>
       </c>
-      <c r="AX144" s="5" t="n">
-        <v>4410</v>
-      </c>
-      <c r="AY144" s="5" t="n">
+      <c r="AZ144" s="5" t="n">
         <v>2420</v>
       </c>
-      <c r="AZ144" s="5" t="n">
+      <c r="BA144" s="5" t="n">
         <v>12470</v>
-      </c>
-      <c r="BA144" s="5" t="n">
-        <v>9400</v>
       </c>
       <c r="BB144" s="5" t="n">
         <v>5490</v>
@@ -40418,19 +40418,19 @@
         <v>92</v>
       </c>
       <c r="AW145" s="5" t="n">
+        <v>2870</v>
+      </c>
+      <c r="AX145" s="5" t="n">
+        <v>4360</v>
+      </c>
+      <c r="AY145" s="5" t="n">
         <v>3720</v>
       </c>
-      <c r="AX145" s="5" t="n">
-        <v>2870</v>
-      </c>
-      <c r="AY145" s="5" t="n">
+      <c r="AZ145" s="5" t="n">
         <v>1630</v>
       </c>
-      <c r="AZ145" s="5" t="n">
+      <c r="BA145" s="5" t="n">
         <v>5710</v>
-      </c>
-      <c r="BA145" s="5" t="n">
-        <v>4360</v>
       </c>
       <c r="BB145" s="5" t="n">
         <v>2550</v>
@@ -40679,19 +40679,19 @@
         <v>92</v>
       </c>
       <c r="AW146" s="5" t="n">
+        <v>1950</v>
+      </c>
+      <c r="AX146" s="5" t="n">
+        <v>3260</v>
+      </c>
+      <c r="AY146" s="5" t="n">
         <v>2220</v>
       </c>
-      <c r="AX146" s="5" t="n">
-        <v>1950</v>
-      </c>
-      <c r="AY146" s="5" t="n">
+      <c r="AZ146" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="AZ146" s="5" t="n">
+      <c r="BA146" s="5" t="n">
         <v>3720</v>
-      </c>
-      <c r="BA146" s="5" t="n">
-        <v>3260</v>
       </c>
       <c r="BB146" s="5" t="n">
         <v>1720</v>
@@ -40889,7 +40889,7 @@
         <v>0.3</v>
       </c>
       <c r="AF147" s="5" t="n">
-        <v>2840</v>
+        <v>2830</v>
       </c>
       <c r="AG147" s="5" t="n">
         <v>644</v>
@@ -40940,19 +40940,19 @@
         <v>96</v>
       </c>
       <c r="AW147" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AX147" s="5" t="n">
+        <v>7460</v>
+      </c>
+      <c r="AY147" s="5" t="n">
         <v>4890</v>
       </c>
-      <c r="AX147" s="5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="AY147" s="5" t="n">
+      <c r="AZ147" s="5" t="n">
         <v>2290</v>
       </c>
-      <c r="AZ147" s="5" t="n">
+      <c r="BA147" s="5" t="n">
         <v>11100</v>
-      </c>
-      <c r="BA147" s="5" t="n">
-        <v>7460</v>
       </c>
       <c r="BB147" s="5" t="n">
         <v>5200</v>
@@ -41201,19 +41201,19 @@
         <v>105</v>
       </c>
       <c r="AW148" s="5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="AX148" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="AY148" s="5" t="n">
         <v>2760</v>
       </c>
-      <c r="AX148" s="5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="AY148" s="5" t="n">
+      <c r="AZ148" s="5" t="n">
         <v>1170</v>
       </c>
-      <c r="AZ148" s="5" t="n">
+      <c r="BA148" s="5" t="n">
         <v>5260</v>
-      </c>
-      <c r="BA148" s="5" t="n">
-        <v>4100</v>
       </c>
       <c r="BB148" s="5" t="n">
         <v>2240</v>
@@ -41411,7 +41411,7 @@
         <v>0.25</v>
       </c>
       <c r="AF149" s="5" t="n">
-        <v>2340</v>
+        <v>2350</v>
       </c>
       <c r="AG149" s="5" t="n">
         <v>439</v>
@@ -41462,19 +41462,19 @@
         <v>92</v>
       </c>
       <c r="AW149" s="5" t="n">
+        <v>4860</v>
+      </c>
+      <c r="AX149" s="5" t="n">
+        <v>8380</v>
+      </c>
+      <c r="AY149" s="5" t="n">
         <v>5270</v>
       </c>
-      <c r="AX149" s="5" t="n">
-        <v>4860</v>
-      </c>
-      <c r="AY149" s="5" t="n">
+      <c r="AZ149" s="5" t="n">
         <v>2490</v>
       </c>
-      <c r="AZ149" s="5" t="n">
+      <c r="BA149" s="5" t="n">
         <v>9710</v>
-      </c>
-      <c r="BA149" s="5" t="n">
-        <v>8380</v>
       </c>
       <c r="BB149" s="5" t="n">
         <v>4610</v>
@@ -41672,7 +41672,7 @@
         <v>0.29</v>
       </c>
       <c r="AF150" s="5" t="n">
-        <v>2820</v>
+        <v>2810</v>
       </c>
       <c r="AG150" s="5" t="n">
         <v>505</v>
@@ -41723,19 +41723,19 @@
         <v>96</v>
       </c>
       <c r="AW150" s="5" t="n">
+        <v>1790</v>
+      </c>
+      <c r="AX150" s="5" t="n">
+        <v>3190</v>
+      </c>
+      <c r="AY150" s="5" t="n">
         <v>2990</v>
       </c>
-      <c r="AX150" s="5" t="n">
-        <v>1790</v>
-      </c>
-      <c r="AY150" s="5" t="n">
+      <c r="AZ150" s="5" t="n">
         <v>1290</v>
       </c>
-      <c r="AZ150" s="5" t="n">
+      <c r="BA150" s="5" t="n">
         <v>5510</v>
-      </c>
-      <c r="BA150" s="5" t="n">
-        <v>3190</v>
       </c>
       <c r="BB150" s="5" t="n">
         <v>2380</v>
@@ -41984,19 +41984,19 @@
         <v>105</v>
       </c>
       <c r="AW151" s="5" t="n">
+        <v>5410</v>
+      </c>
+      <c r="AX151" s="5" t="n">
+        <v>10780</v>
+      </c>
+      <c r="AY151" s="5" t="n">
         <v>7800</v>
       </c>
-      <c r="AX151" s="5" t="n">
-        <v>5410</v>
-      </c>
-      <c r="AY151" s="5" t="n">
+      <c r="AZ151" s="5" t="n">
         <v>3160</v>
       </c>
-      <c r="AZ151" s="5" t="n">
+      <c r="BA151" s="5" t="n">
         <v>15900</v>
-      </c>
-      <c r="BA151" s="5" t="n">
-        <v>10780</v>
       </c>
       <c r="BB151" s="5" t="n">
         <v>6590</v>
@@ -42245,19 +42245,19 @@
         <v>96</v>
       </c>
       <c r="AW152" s="5" t="n">
+        <v>5210</v>
+      </c>
+      <c r="AX152" s="5" t="n">
+        <v>7490</v>
+      </c>
+      <c r="AY152" s="5" t="n">
         <v>6350</v>
       </c>
-      <c r="AX152" s="5" t="n">
-        <v>5210</v>
-      </c>
-      <c r="AY152" s="5" t="n">
+      <c r="AZ152" s="5" t="n">
         <v>2650</v>
       </c>
-      <c r="AZ152" s="5" t="n">
+      <c r="BA152" s="5" t="n">
         <v>9190</v>
-      </c>
-      <c r="BA152" s="5" t="n">
-        <v>7490</v>
       </c>
       <c r="BB152" s="5" t="n">
         <v>3890</v>
@@ -42455,7 +42455,7 @@
         <v>0.39</v>
       </c>
       <c r="AF153" s="5" t="n">
-        <v>3490</v>
+        <v>3500</v>
       </c>
       <c r="AG153" s="5" t="n">
         <v>1071</v>
@@ -42506,19 +42506,19 @@
         <v>105</v>
       </c>
       <c r="AW153" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AX153" s="5" t="n">
+        <v>3510</v>
+      </c>
+      <c r="AY153" s="5" t="n">
         <v>2660</v>
       </c>
-      <c r="AX153" s="5" t="n">
-        <v>2100</v>
-      </c>
-      <c r="AY153" s="5" t="n">
+      <c r="AZ153" s="5" t="n">
         <v>1140</v>
       </c>
-      <c r="AZ153" s="5" t="n">
+      <c r="BA153" s="5" t="n">
         <v>4930</v>
-      </c>
-      <c r="BA153" s="5" t="n">
-        <v>3510</v>
       </c>
       <c r="BB153" s="5" t="n">
         <v>2120</v>
@@ -42767,19 +42767,19 @@
         <v>105</v>
       </c>
       <c r="AW154" s="5" t="n">
+        <v>2230</v>
+      </c>
+      <c r="AX154" s="5" t="n">
+        <v>3490</v>
+      </c>
+      <c r="AY154" s="5" t="n">
         <v>2330</v>
       </c>
-      <c r="AX154" s="5" t="n">
-        <v>2230</v>
-      </c>
-      <c r="AY154" s="5" t="n">
+      <c r="AZ154" s="5" t="n">
         <v>1020</v>
       </c>
-      <c r="AZ154" s="5" t="n">
+      <c r="BA154" s="5" t="n">
         <v>3920</v>
-      </c>
-      <c r="BA154" s="5" t="n">
-        <v>3490</v>
       </c>
       <c r="BB154" s="5" t="n">
         <v>1740</v>
@@ -43028,19 +43028,19 @@
         <v>105</v>
       </c>
       <c r="AW155" s="5" t="n">
+        <v>2520</v>
+      </c>
+      <c r="AX155" s="5" t="n">
+        <v>4160</v>
+      </c>
+      <c r="AY155" s="5" t="n">
         <v>3090</v>
       </c>
-      <c r="AX155" s="5" t="n">
-        <v>2520</v>
-      </c>
-      <c r="AY155" s="5" t="n">
+      <c r="AZ155" s="5" t="n">
         <v>1370</v>
       </c>
-      <c r="AZ155" s="5" t="n">
+      <c r="BA155" s="5" t="n">
         <v>5420</v>
-      </c>
-      <c r="BA155" s="5" t="n">
-        <v>4160</v>
       </c>
       <c r="BB155" s="5" t="n">
         <v>2430</v>
@@ -43289,19 +43289,19 @@
         <v>96</v>
       </c>
       <c r="AW156" s="5" t="n">
+        <v>960</v>
+      </c>
+      <c r="AX156" s="5" t="n">
+        <v>1710</v>
+      </c>
+      <c r="AY156" s="5" t="n">
         <v>1780</v>
       </c>
-      <c r="AX156" s="5" t="n">
-        <v>960</v>
-      </c>
-      <c r="AY156" s="5" t="n">
+      <c r="AZ156" s="5" t="n">
         <v>740</v>
       </c>
-      <c r="AZ156" s="5" t="n">
+      <c r="BA156" s="5" t="n">
         <v>3280</v>
-      </c>
-      <c r="BA156" s="5" t="n">
-        <v>1710</v>
       </c>
       <c r="BB156" s="5" t="n">
         <v>1350</v>
@@ -43550,19 +43550,19 @@
         <v>96</v>
       </c>
       <c r="AW157" s="5" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AX157" s="5" t="n">
+        <v>4680</v>
+      </c>
+      <c r="AY157" s="5" t="n">
         <v>1110</v>
       </c>
-      <c r="AX157" s="5" t="n">
-        <v>1150</v>
-      </c>
-      <c r="AY157" s="5" t="n">
+      <c r="AZ157" s="5" t="n">
         <v>420</v>
       </c>
-      <c r="AZ157" s="5" t="n">
+      <c r="BA157" s="5" t="n">
         <v>5720</v>
-      </c>
-      <c r="BA157" s="5" t="n">
-        <v>4680</v>
       </c>
       <c r="BB157" s="5" t="n">
         <v>2340</v>
@@ -43811,19 +43811,19 @@
         <v>92</v>
       </c>
       <c r="AW158" s="5" t="n">
+        <v>45740</v>
+      </c>
+      <c r="AX158" s="5" t="n">
+        <v>52820</v>
+      </c>
+      <c r="AY158" s="5" t="n">
         <v>29510</v>
       </c>
-      <c r="AX158" s="5" t="n">
-        <v>45740</v>
-      </c>
-      <c r="AY158" s="5" t="n">
+      <c r="AZ158" s="5" t="n">
         <v>13830</v>
       </c>
-      <c r="AZ158" s="5" t="n">
+      <c r="BA158" s="5" t="n">
         <v>36530</v>
-      </c>
-      <c r="BA158" s="5" t="n">
-        <v>52820</v>
       </c>
       <c r="BB158" s="5" t="n">
         <v>17050</v>
@@ -44072,19 +44072,19 @@
         <v>105</v>
       </c>
       <c r="AW159" s="5" t="n">
+        <v>3660</v>
+      </c>
+      <c r="AX159" s="5" t="n">
+        <v>10690</v>
+      </c>
+      <c r="AY159" s="5" t="n">
         <v>5200</v>
       </c>
-      <c r="AX159" s="5" t="n">
-        <v>3660</v>
-      </c>
-      <c r="AY159" s="5" t="n">
+      <c r="AZ159" s="5" t="n">
         <v>2110</v>
       </c>
-      <c r="AZ159" s="5" t="n">
+      <c r="BA159" s="5" t="n">
         <v>13560</v>
-      </c>
-      <c r="BA159" s="5" t="n">
-        <v>10690</v>
       </c>
       <c r="BB159" s="5" t="n">
         <v>5400</v>
@@ -44333,19 +44333,19 @@
         <v>105</v>
       </c>
       <c r="AW160" s="5" t="n">
+        <v>3900</v>
+      </c>
+      <c r="AX160" s="5" t="n">
+        <v>6470</v>
+      </c>
+      <c r="AY160" s="5" t="n">
         <v>4370</v>
       </c>
-      <c r="AX160" s="5" t="n">
-        <v>3900</v>
-      </c>
-      <c r="AY160" s="5" t="n">
+      <c r="AZ160" s="5" t="n">
         <v>1880</v>
       </c>
-      <c r="AZ160" s="5" t="n">
+      <c r="BA160" s="5" t="n">
         <v>7650</v>
-      </c>
-      <c r="BA160" s="5" t="n">
-        <v>6470</v>
       </c>
       <c r="BB160" s="5" t="n">
         <v>3340</v>
@@ -44594,19 +44594,19 @@
         <v>96</v>
       </c>
       <c r="AW161" s="5" t="n">
+        <v>810</v>
+      </c>
+      <c r="AX161" s="5" t="n">
+        <v>22010</v>
+      </c>
+      <c r="AY161" s="5" t="n">
         <v>800</v>
       </c>
-      <c r="AX161" s="5" t="n">
-        <v>810</v>
-      </c>
-      <c r="AY161" s="5" t="n">
+      <c r="AZ161" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="AZ161" s="5" t="n">
+      <c r="BA161" s="5" t="n">
         <v>35280</v>
-      </c>
-      <c r="BA161" s="5" t="n">
-        <v>22010</v>
       </c>
       <c r="BB161" s="5" t="n">
         <v>14840</v>
@@ -44855,19 +44855,19 @@
         <v>105</v>
       </c>
       <c r="AW162" s="5" t="n">
+        <v>3680</v>
+      </c>
+      <c r="AX162" s="5" t="n">
+        <v>7060</v>
+      </c>
+      <c r="AY162" s="5" t="n">
         <v>4540</v>
       </c>
-      <c r="AX162" s="5" t="n">
-        <v>3680</v>
-      </c>
-      <c r="AY162" s="5" t="n">
+      <c r="AZ162" s="5" t="n">
         <v>2060</v>
       </c>
-      <c r="AZ162" s="5" t="n">
+      <c r="BA162" s="5" t="n">
         <v>8810</v>
-      </c>
-      <c r="BA162" s="5" t="n">
-        <v>7060</v>
       </c>
       <c r="BB162" s="5" t="n">
         <v>4080</v>
@@ -45116,19 +45116,19 @@
         <v>92</v>
       </c>
       <c r="AW163" s="5" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AX163" s="5" t="n">
+        <v>6860</v>
+      </c>
+      <c r="AY163" s="5" t="n">
         <v>5640</v>
       </c>
-      <c r="AX163" s="5" t="n">
-        <v>4480</v>
-      </c>
-      <c r="AY163" s="5" t="n">
+      <c r="AZ163" s="5" t="n">
         <v>2640</v>
       </c>
-      <c r="AZ163" s="5" t="n">
+      <c r="BA163" s="5" t="n">
         <v>8910</v>
-      </c>
-      <c r="BA163" s="5" t="n">
-        <v>6860</v>
       </c>
       <c r="BB163" s="5" t="n">
         <v>4200</v>
@@ -45326,7 +45326,7 @@
         <v>0.23</v>
       </c>
       <c r="AF164" s="5" t="n">
-        <v>7360</v>
+        <v>7340</v>
       </c>
       <c r="AG164" s="5" t="n">
         <v>8123</v>
@@ -45377,19 +45377,19 @@
         <v>92</v>
       </c>
       <c r="AW164" s="5" t="n">
+        <v>6100</v>
+      </c>
+      <c r="AX164" s="5" t="n">
+        <v>8990</v>
+      </c>
+      <c r="AY164" s="5" t="n">
         <v>5960</v>
       </c>
-      <c r="AX164" s="5" t="n">
-        <v>6100</v>
-      </c>
-      <c r="AY164" s="5" t="n">
+      <c r="AZ164" s="5" t="n">
         <v>2520</v>
       </c>
-      <c r="AZ164" s="5" t="n">
+      <c r="BA164" s="5" t="n">
         <v>9430</v>
-      </c>
-      <c r="BA164" s="5" t="n">
-        <v>8990</v>
       </c>
       <c r="BB164" s="5" t="n">
         <v>3990</v>
@@ -45587,7 +45587,7 @@
         <v>0.42</v>
       </c>
       <c r="AF165" s="5" t="n">
-        <v>5710</v>
+        <v>5720</v>
       </c>
       <c r="AG165" s="5" t="n">
         <v>2830</v>
@@ -45638,19 +45638,19 @@
         <v>105</v>
       </c>
       <c r="AW165" s="5" t="n">
+        <v>2220</v>
+      </c>
+      <c r="AX165" s="5" t="n">
+        <v>3690</v>
+      </c>
+      <c r="AY165" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="AX165" s="5" t="n">
-        <v>2220</v>
-      </c>
-      <c r="AY165" s="5" t="n">
+      <c r="AZ165" s="5" t="n">
         <v>880</v>
       </c>
-      <c r="AZ165" s="5" t="n">
+      <c r="BA165" s="5" t="n">
         <v>3970</v>
-      </c>
-      <c r="BA165" s="5" t="n">
-        <v>3690</v>
       </c>
       <c r="BB165" s="5" t="n">
         <v>1750</v>
@@ -45899,19 +45899,19 @@
         <v>92</v>
       </c>
       <c r="AW166" s="5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="AX166" s="5" t="n">
+        <v>4760</v>
+      </c>
+      <c r="AY166" s="5" t="n">
         <v>2320</v>
       </c>
-      <c r="AX166" s="5" t="n">
-        <v>2180</v>
-      </c>
-      <c r="AY166" s="5" t="n">
+      <c r="AZ166" s="5" t="n">
         <v>1080</v>
       </c>
-      <c r="AZ166" s="5" t="n">
+      <c r="BA166" s="5" t="n">
         <v>5390</v>
-      </c>
-      <c r="BA166" s="5" t="n">
-        <v>4760</v>
       </c>
       <c r="BB166" s="5" t="n">
         <v>2490</v>
@@ -46109,7 +46109,7 @@
         <v>0.43</v>
       </c>
       <c r="AF167" s="5" t="n">
-        <v>6280</v>
+        <v>6290</v>
       </c>
       <c r="AG167" s="5" t="n">
         <v>9224</v>
@@ -46160,19 +46160,19 @@
         <v>92</v>
       </c>
       <c r="AW167" s="5" t="n">
+        <v>3170</v>
+      </c>
+      <c r="AX167" s="5" t="n">
+        <v>15520</v>
+      </c>
+      <c r="AY167" s="5" t="n">
         <v>2980</v>
       </c>
-      <c r="AX167" s="5" t="n">
-        <v>3170</v>
-      </c>
-      <c r="AY167" s="5" t="n">
+      <c r="AZ167" s="5" t="n">
         <v>1350</v>
       </c>
-      <c r="AZ167" s="5" t="n">
+      <c r="BA167" s="5" t="n">
         <v>17220</v>
-      </c>
-      <c r="BA167" s="5" t="n">
-        <v>15520</v>
       </c>
       <c r="BB167" s="5" t="n">
         <v>7330</v>
@@ -46421,19 +46421,19 @@
         <v>92</v>
       </c>
       <c r="AW168" s="5" t="n">
+        <v>3050</v>
+      </c>
+      <c r="AX168" s="5" t="n">
+        <v>4880</v>
+      </c>
+      <c r="AY168" s="5" t="n">
         <v>2590</v>
       </c>
-      <c r="AX168" s="5" t="n">
-        <v>3050</v>
-      </c>
-      <c r="AY168" s="5" t="n">
+      <c r="AZ168" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="AZ168" s="5" t="n">
+      <c r="BA168" s="5" t="n">
         <v>4380</v>
-      </c>
-      <c r="BA168" s="5" t="n">
-        <v>4880</v>
       </c>
       <c r="BB168" s="5" t="n">
         <v>1880</v>
@@ -46631,7 +46631,7 @@
         <v>0.47</v>
       </c>
       <c r="AF169" s="5" t="n">
-        <v>3650</v>
+        <v>3640</v>
       </c>
       <c r="AG169" s="5" t="n">
         <v>846</v>
@@ -46682,19 +46682,19 @@
         <v>96</v>
       </c>
       <c r="AW169" s="5" t="n">
+        <v>3290</v>
+      </c>
+      <c r="AX169" s="5" t="n">
+        <v>6100</v>
+      </c>
+      <c r="AY169" s="5" t="n">
         <v>3340</v>
       </c>
-      <c r="AX169" s="5" t="n">
-        <v>3290</v>
-      </c>
-      <c r="AY169" s="5" t="n">
+      <c r="AZ169" s="5" t="n">
         <v>1670</v>
       </c>
-      <c r="AZ169" s="5" t="n">
+      <c r="BA169" s="5" t="n">
         <v>6680</v>
-      </c>
-      <c r="BA169" s="5" t="n">
-        <v>6100</v>
       </c>
       <c r="BB169" s="5" t="n">
         <v>3280</v>
@@ -46892,7 +46892,7 @@
         <v>0.35</v>
       </c>
       <c r="AF170" s="5" t="n">
-        <v>8550</v>
+        <v>8540</v>
       </c>
       <c r="AG170" s="5" t="n">
         <v>6511</v>
@@ -46943,19 +46943,19 @@
         <v>105</v>
       </c>
       <c r="AW170" s="5" t="n">
+        <v>7640</v>
+      </c>
+      <c r="AX170" s="5" t="n">
+        <v>10300</v>
+      </c>
+      <c r="AY170" s="5" t="n">
         <v>7780</v>
       </c>
-      <c r="AX170" s="5" t="n">
-        <v>7640</v>
-      </c>
-      <c r="AY170" s="5" t="n">
+      <c r="AZ170" s="5" t="n">
         <v>3340</v>
       </c>
-      <c r="AZ170" s="5" t="n">
+      <c r="BA170" s="5" t="n">
         <v>11070</v>
-      </c>
-      <c r="BA170" s="5" t="n">
-        <v>10300</v>
       </c>
       <c r="BB170" s="5" t="n">
         <v>4760</v>
@@ -47204,19 +47204,19 @@
         <v>105</v>
       </c>
       <c r="AW171" s="5" t="n">
+        <v>1810</v>
+      </c>
+      <c r="AX171" s="5" t="n">
+        <v>3420</v>
+      </c>
+      <c r="AY171" s="5" t="n">
         <v>2500</v>
       </c>
-      <c r="AX171" s="5" t="n">
-        <v>1810</v>
-      </c>
-      <c r="AY171" s="5" t="n">
+      <c r="AZ171" s="5" t="n">
         <v>1140</v>
       </c>
-      <c r="AZ171" s="5" t="n">
+      <c r="BA171" s="5" t="n">
         <v>5100</v>
-      </c>
-      <c r="BA171" s="5" t="n">
-        <v>3420</v>
       </c>
       <c r="BB171" s="5" t="n">
         <v>2310</v>
@@ -47414,7 +47414,7 @@
         <v>0.23</v>
       </c>
       <c r="AF172" s="5" t="n">
-        <v>5580</v>
+        <v>5570</v>
       </c>
       <c r="AG172" s="5" t="n">
         <v>3089</v>
@@ -47465,19 +47465,19 @@
         <v>92</v>
       </c>
       <c r="AW172" s="5" t="n">
+        <v>3940</v>
+      </c>
+      <c r="AX172" s="5" t="n">
+        <v>7140</v>
+      </c>
+      <c r="AY172" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="AX172" s="5" t="n">
-        <v>3940</v>
-      </c>
-      <c r="AY172" s="5" t="n">
+      <c r="AZ172" s="5" t="n">
         <v>1720</v>
       </c>
-      <c r="AZ172" s="5" t="n">
+      <c r="BA172" s="5" t="n">
         <v>7010</v>
-      </c>
-      <c r="BA172" s="5" t="n">
-        <v>7140</v>
       </c>
       <c r="BB172" s="5" t="n">
         <v>3200</v>
@@ -47675,7 +47675,7 @@
         <v>0.34</v>
       </c>
       <c r="AF173" s="5" t="n">
-        <v>3120</v>
+        <v>3130</v>
       </c>
       <c r="AG173" s="5" t="n">
         <v>399</v>
@@ -47726,19 +47726,19 @@
         <v>96</v>
       </c>
       <c r="AW173" s="5" t="n">
+        <v>1790</v>
+      </c>
+      <c r="AX173" s="5" t="n">
+        <v>3560</v>
+      </c>
+      <c r="AY173" s="5" t="n">
         <v>2670</v>
       </c>
-      <c r="AX173" s="5" t="n">
-        <v>1790</v>
-      </c>
-      <c r="AY173" s="5" t="n">
+      <c r="AZ173" s="5" t="n">
         <v>1270</v>
       </c>
-      <c r="AZ173" s="5" t="n">
+      <c r="BA173" s="5" t="n">
         <v>5530</v>
-      </c>
-      <c r="BA173" s="5" t="n">
-        <v>3560</v>
       </c>
       <c r="BB173" s="5" t="n">
         <v>2600</v>
@@ -47987,19 +47987,19 @@
         <v>105</v>
       </c>
       <c r="AW174" s="5" t="n">
+        <v>1940</v>
+      </c>
+      <c r="AX174" s="5" t="n">
+        <v>5930</v>
+      </c>
+      <c r="AY174" s="5" t="n">
         <v>2740</v>
       </c>
-      <c r="AX174" s="5" t="n">
-        <v>1940</v>
-      </c>
-      <c r="AY174" s="5" t="n">
+      <c r="AZ174" s="5" t="n">
         <v>1240</v>
       </c>
-      <c r="AZ174" s="5" t="n">
+      <c r="BA174" s="5" t="n">
         <v>8640</v>
-      </c>
-      <c r="BA174" s="5" t="n">
-        <v>5930</v>
       </c>
       <c r="BB174" s="5" t="n">
         <v>4090</v>
@@ -48248,19 +48248,19 @@
         <v>96</v>
       </c>
       <c r="AW175" s="5" t="n">
+        <v>1020</v>
+      </c>
+      <c r="AX175" s="5" t="n">
+        <v>2480</v>
+      </c>
+      <c r="AY175" s="5" t="n">
         <v>1230</v>
       </c>
-      <c r="AX175" s="5" t="n">
-        <v>1020</v>
-      </c>
-      <c r="AY175" s="5" t="n">
+      <c r="AZ175" s="5" t="n">
         <v>570</v>
       </c>
-      <c r="AZ175" s="5" t="n">
+      <c r="BA175" s="5" t="n">
         <v>3090</v>
-      </c>
-      <c r="BA175" s="5" t="n">
-        <v>2480</v>
       </c>
       <c r="BB175" s="5" t="n">
         <v>1460</v>
@@ -48509,19 +48509,19 @@
         <v>92</v>
       </c>
       <c r="AW176" s="5" t="n">
+        <v>4660</v>
+      </c>
+      <c r="AX176" s="5" t="n">
+        <v>7830</v>
+      </c>
+      <c r="AY176" s="5" t="n">
         <v>5500</v>
       </c>
-      <c r="AX176" s="5" t="n">
-        <v>4660</v>
-      </c>
-      <c r="AY176" s="5" t="n">
+      <c r="AZ176" s="5" t="n">
         <v>2350</v>
       </c>
-      <c r="AZ176" s="5" t="n">
+      <c r="BA176" s="5" t="n">
         <v>9800</v>
-      </c>
-      <c r="BA176" s="5" t="n">
-        <v>7830</v>
       </c>
       <c r="BB176" s="5" t="n">
         <v>4380</v>
@@ -48770,19 +48770,19 @@
         <v>105</v>
       </c>
       <c r="AW177" s="5" t="n">
+        <v>3750</v>
+      </c>
+      <c r="AX177" s="5" t="n">
+        <v>6910</v>
+      </c>
+      <c r="AY177" s="5" t="n">
         <v>4420</v>
       </c>
-      <c r="AX177" s="5" t="n">
-        <v>3750</v>
-      </c>
-      <c r="AY177" s="5" t="n">
+      <c r="AZ177" s="5" t="n">
         <v>1900</v>
       </c>
-      <c r="AZ177" s="5" t="n">
+      <c r="BA177" s="5" t="n">
         <v>8690</v>
-      </c>
-      <c r="BA177" s="5" t="n">
-        <v>6910</v>
       </c>
       <c r="BB177" s="5" t="n">
         <v>3780</v>
@@ -49031,19 +49031,19 @@
         <v>96</v>
       </c>
       <c r="AW178" s="5" t="n">
+        <v>3920</v>
+      </c>
+      <c r="AX178" s="5" t="n">
+        <v>6910</v>
+      </c>
+      <c r="AY178" s="5" t="n">
         <v>4270</v>
       </c>
-      <c r="AX178" s="5" t="n">
-        <v>3920</v>
-      </c>
-      <c r="AY178" s="5" t="n">
+      <c r="AZ178" s="5" t="n">
         <v>1750</v>
       </c>
-      <c r="AZ178" s="5" t="n">
+      <c r="BA178" s="5" t="n">
         <v>8330</v>
-      </c>
-      <c r="BA178" s="5" t="n">
-        <v>6910</v>
       </c>
       <c r="BB178" s="5" t="n">
         <v>3420</v>
@@ -49292,19 +49292,19 @@
         <v>96</v>
       </c>
       <c r="AW179" s="5" t="n">
+        <v>6610</v>
+      </c>
+      <c r="AX179" s="5" t="n">
+        <v>10520</v>
+      </c>
+      <c r="AY179" s="5" t="n">
         <v>10600</v>
       </c>
-      <c r="AX179" s="5" t="n">
-        <v>6610</v>
-      </c>
-      <c r="AY179" s="5" t="n">
+      <c r="AZ179" s="5" t="n">
         <v>3890</v>
       </c>
-      <c r="AZ179" s="5" t="n">
+      <c r="BA179" s="5" t="n">
         <v>16580</v>
-      </c>
-      <c r="BA179" s="5" t="n">
-        <v>10520</v>
       </c>
       <c r="BB179" s="5" t="n">
         <v>6050</v>
@@ -49502,7 +49502,7 @@
         <v>0.57</v>
       </c>
       <c r="AF180" s="5" t="n">
-        <v>5000</v>
+        <v>4990</v>
       </c>
       <c r="AG180" s="5" t="n">
         <v>3574</v>
@@ -49553,19 +49553,19 @@
         <v>92</v>
       </c>
       <c r="AW180" s="5" t="n">
+        <v>3580</v>
+      </c>
+      <c r="AX180" s="5" t="n">
+        <v>5870</v>
+      </c>
+      <c r="AY180" s="5" t="n">
         <v>5050</v>
       </c>
-      <c r="AX180" s="5" t="n">
-        <v>3580</v>
-      </c>
-      <c r="AY180" s="5" t="n">
+      <c r="AZ180" s="5" t="n">
         <v>2190</v>
       </c>
-      <c r="AZ180" s="5" t="n">
+      <c r="BA180" s="5" t="n">
         <v>8420</v>
-      </c>
-      <c r="BA180" s="5" t="n">
-        <v>5870</v>
       </c>
       <c r="BB180" s="5" t="n">
         <v>3720</v>
@@ -49763,7 +49763,7 @@
         <v>0.54</v>
       </c>
       <c r="AF181" s="5" t="n">
-        <v>4300</v>
+        <v>4310</v>
       </c>
       <c r="AG181" s="5" t="n">
         <v>3953</v>
@@ -49814,19 +49814,19 @@
         <v>105</v>
       </c>
       <c r="AW181" s="5" t="n">
+        <v>3290</v>
+      </c>
+      <c r="AX181" s="5" t="n">
+        <v>5590</v>
+      </c>
+      <c r="AY181" s="5" t="n">
         <v>4670</v>
       </c>
-      <c r="AX181" s="5" t="n">
-        <v>3290</v>
-      </c>
-      <c r="AY181" s="5" t="n">
+      <c r="AZ181" s="5" t="n">
         <v>1970</v>
       </c>
-      <c r="AZ181" s="5" t="n">
+      <c r="BA181" s="5" t="n">
         <v>8310</v>
-      </c>
-      <c r="BA181" s="5" t="n">
-        <v>5590</v>
       </c>
       <c r="BB181" s="5" t="n">
         <v>3540</v>
@@ -50024,7 +50024,7 @@
         <v>0.59</v>
       </c>
       <c r="AF182" s="5" t="n">
-        <v>4380</v>
+        <v>4370</v>
       </c>
       <c r="AG182" s="5" t="n">
         <v>4171</v>
@@ -50075,19 +50075,19 @@
         <v>96</v>
       </c>
       <c r="AW182" s="5" t="n">
+        <v>2110</v>
+      </c>
+      <c r="AX182" s="5" t="n">
+        <v>3320</v>
+      </c>
+      <c r="AY182" s="5" t="n">
         <v>2270</v>
       </c>
-      <c r="AX182" s="5" t="n">
-        <v>2110</v>
-      </c>
-      <c r="AY182" s="5" t="n">
+      <c r="AZ182" s="5" t="n">
         <v>970</v>
       </c>
-      <c r="AZ182" s="5" t="n">
+      <c r="BA182" s="5" t="n">
         <v>3900</v>
-      </c>
-      <c r="BA182" s="5" t="n">
-        <v>3320</v>
       </c>
       <c r="BB182" s="5" t="n">
         <v>1680</v>
@@ -50336,19 +50336,19 @@
         <v>92</v>
       </c>
       <c r="AW183" s="5" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AX183" s="5" t="n">
+        <v>3150</v>
+      </c>
+      <c r="AY183" s="5" t="n">
         <v>1950</v>
       </c>
-      <c r="AX183" s="5" t="n">
-        <v>1630</v>
-      </c>
-      <c r="AY183" s="5" t="n">
+      <c r="AZ183" s="5" t="n">
         <v>890</v>
       </c>
-      <c r="AZ183" s="5" t="n">
+      <c r="BA183" s="5" t="n">
         <v>4280</v>
-      </c>
-      <c r="BA183" s="5" t="n">
-        <v>3150</v>
       </c>
       <c r="BB183" s="5" t="n">
         <v>1960</v>
@@ -50597,19 +50597,19 @@
         <v>96</v>
       </c>
       <c r="AW184" s="5" t="n">
+        <v>3220</v>
+      </c>
+      <c r="AX184" s="5" t="n">
+        <v>6480</v>
+      </c>
+      <c r="AY184" s="5" t="n">
         <v>4540</v>
       </c>
-      <c r="AX184" s="5" t="n">
-        <v>3220</v>
-      </c>
-      <c r="AY184" s="5" t="n">
+      <c r="AZ184" s="5" t="n">
         <v>1860</v>
       </c>
-      <c r="AZ184" s="5" t="n">
+      <c r="BA184" s="5" t="n">
         <v>9370</v>
-      </c>
-      <c r="BA184" s="5" t="n">
-        <v>6480</v>
       </c>
       <c r="BB184" s="5" t="n">
         <v>3860</v>
@@ -50858,19 +50858,19 @@
         <v>105</v>
       </c>
       <c r="AW185" s="5" t="n">
+        <v>1960</v>
+      </c>
+      <c r="AX185" s="5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AY185" s="5" t="n">
         <v>2100</v>
       </c>
-      <c r="AX185" s="5" t="n">
-        <v>1960</v>
-      </c>
-      <c r="AY185" s="5" t="n">
+      <c r="AZ185" s="5" t="n">
         <v>930</v>
       </c>
-      <c r="AZ185" s="5" t="n">
+      <c r="BA185" s="5" t="n">
         <v>4440</v>
-      </c>
-      <c r="BA185" s="5" t="n">
-        <v>3600</v>
       </c>
       <c r="BB185" s="5" t="n">
         <v>1980</v>
@@ -51068,7 +51068,7 @@
         <v>0.26</v>
       </c>
       <c r="AF186" s="5" t="n">
-        <v>3200</v>
+        <v>3210</v>
       </c>
       <c r="AG186" s="5" t="n">
         <v>693</v>
@@ -51119,19 +51119,19 @@
         <v>105</v>
       </c>
       <c r="AW186" s="5" t="n">
+        <v>5060</v>
+      </c>
+      <c r="AX186" s="5" t="n">
+        <v>7460</v>
+      </c>
+      <c r="AY186" s="5" t="n">
         <v>7880</v>
       </c>
-      <c r="AX186" s="5" t="n">
-        <v>5060</v>
-      </c>
-      <c r="AY186" s="5" t="n">
+      <c r="AZ186" s="5" t="n">
         <v>3520</v>
       </c>
-      <c r="AZ186" s="5" t="n">
+      <c r="BA186" s="5" t="n">
         <v>11070</v>
-      </c>
-      <c r="BA186" s="5" t="n">
-        <v>7460</v>
       </c>
       <c r="BB186" s="5" t="n">
         <v>4970</v>
@@ -51329,7 +51329,7 @@
         <v>0.35</v>
       </c>
       <c r="AF187" s="5" t="n">
-        <v>2580</v>
+        <v>2590</v>
       </c>
       <c r="AG187" s="5" t="n">
         <v>1033</v>
@@ -51380,19 +51380,19 @@
         <v>105</v>
       </c>
       <c r="AW187" s="5" t="n">
+        <v>2610</v>
+      </c>
+      <c r="AX187" s="5" t="n">
+        <v>4430</v>
+      </c>
+      <c r="AY187" s="5" t="n">
         <v>3480</v>
       </c>
-      <c r="AX187" s="5" t="n">
-        <v>2610</v>
-      </c>
-      <c r="AY187" s="5" t="n">
+      <c r="AZ187" s="5" t="n">
         <v>1490</v>
       </c>
-      <c r="AZ187" s="5" t="n">
+      <c r="BA187" s="5" t="n">
         <v>6610</v>
-      </c>
-      <c r="BA187" s="5" t="n">
-        <v>4430</v>
       </c>
       <c r="BB187" s="5" t="n">
         <v>2730</v>
@@ -51590,7 +51590,7 @@
         <v>0.27</v>
       </c>
       <c r="AF188" s="5" t="n">
-        <v>4600</v>
+        <v>4590</v>
       </c>
       <c r="AG188" s="5" t="n">
         <v>1305</v>
@@ -51641,19 +51641,19 @@
         <v>92</v>
       </c>
       <c r="AW188" s="5" t="n">
+        <v>3780</v>
+      </c>
+      <c r="AX188" s="5" t="n">
+        <v>6240</v>
+      </c>
+      <c r="AY188" s="5" t="n">
         <v>4120</v>
       </c>
-      <c r="AX188" s="5" t="n">
-        <v>3780</v>
-      </c>
-      <c r="AY188" s="5" t="n">
+      <c r="AZ188" s="5" t="n">
         <v>1780</v>
       </c>
-      <c r="AZ188" s="5" t="n">
+      <c r="BA188" s="5" t="n">
         <v>7470</v>
-      </c>
-      <c r="BA188" s="5" t="n">
-        <v>6240</v>
       </c>
       <c r="BB188" s="5" t="n">
         <v>3300</v>
@@ -51851,7 +51851,7 @@
         <v>0.33</v>
       </c>
       <c r="AF189" s="5" t="n">
-        <v>2740</v>
+        <v>2750</v>
       </c>
       <c r="AG189" s="5" t="n">
         <v>784</v>
@@ -51902,19 +51902,19 @@
         <v>92</v>
       </c>
       <c r="AW189" s="5" t="n">
+        <v>1870</v>
+      </c>
+      <c r="AX189" s="5" t="n">
+        <v>3090</v>
+      </c>
+      <c r="AY189" s="5" t="n">
         <v>2190</v>
       </c>
-      <c r="AX189" s="5" t="n">
-        <v>1870</v>
-      </c>
-      <c r="AY189" s="5" t="n">
+      <c r="AZ189" s="5" t="n">
         <v>910</v>
       </c>
-      <c r="AZ189" s="5" t="n">
+      <c r="BA189" s="5" t="n">
         <v>3960</v>
-      </c>
-      <c r="BA189" s="5" t="n">
-        <v>3090</v>
       </c>
       <c r="BB189" s="5" t="n">
         <v>1680</v>
@@ -52163,19 +52163,19 @@
         <v>96</v>
       </c>
       <c r="AW190" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="AX190" s="5" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AY190" s="5" t="n">
         <v>1330</v>
       </c>
-      <c r="AX190" s="5" t="n">
-        <v>790</v>
-      </c>
-      <c r="AY190" s="5" t="n">
+      <c r="AZ190" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="AZ190" s="5" t="n">
+      <c r="BA190" s="5" t="n">
         <v>3190</v>
-      </c>
-      <c r="BA190" s="5" t="n">
-        <v>1990</v>
       </c>
       <c r="BB190" s="5" t="n">
         <v>1440</v>
@@ -52424,19 +52424,19 @@
         <v>105</v>
       </c>
       <c r="AW191" s="5" t="n">
+        <v>5120</v>
+      </c>
+      <c r="AX191" s="5" t="n">
+        <v>7110</v>
+      </c>
+      <c r="AY191" s="5" t="n">
         <v>6830</v>
       </c>
-      <c r="AX191" s="5" t="n">
-        <v>5120</v>
-      </c>
-      <c r="AY191" s="5" t="n">
+      <c r="AZ191" s="5" t="n">
         <v>3010</v>
       </c>
-      <c r="AZ191" s="5" t="n">
+      <c r="BA191" s="5" t="n">
         <v>9430</v>
-      </c>
-      <c r="BA191" s="5" t="n">
-        <v>7110</v>
       </c>
       <c r="BB191" s="5" t="n">
         <v>4200</v>
@@ -52634,7 +52634,7 @@
         <v>0.25</v>
       </c>
       <c r="AF192" s="5" t="n">
-        <v>3360</v>
+        <v>3370</v>
       </c>
       <c r="AG192" s="5" t="n">
         <v>1177</v>
@@ -52685,19 +52685,19 @@
         <v>96</v>
       </c>
       <c r="AW192" s="5" t="n">
+        <v>7690</v>
+      </c>
+      <c r="AX192" s="5" t="n">
+        <v>12240</v>
+      </c>
+      <c r="AY192" s="5" t="n">
         <v>9890</v>
       </c>
-      <c r="AX192" s="5" t="n">
-        <v>7690</v>
-      </c>
-      <c r="AY192" s="5" t="n">
+      <c r="AZ192" s="5" t="n">
         <v>4580</v>
       </c>
-      <c r="AZ192" s="5" t="n">
+      <c r="BA192" s="5" t="n">
         <v>16320</v>
-      </c>
-      <c r="BA192" s="5" t="n">
-        <v>12240</v>
       </c>
       <c r="BB192" s="5" t="n">
         <v>7510</v>
@@ -52895,7 +52895,7 @@
         <v>0.48</v>
       </c>
       <c r="AF193" s="5" t="n">
-        <v>6090</v>
+        <v>6140</v>
       </c>
       <c r="AG193" s="5" t="n">
         <v>7532</v>
@@ -52946,19 +52946,19 @@
         <v>105</v>
       </c>
       <c r="AW193" s="5" t="n">
+        <v>7660</v>
+      </c>
+      <c r="AX193" s="5" t="n">
+        <v>10480</v>
+      </c>
+      <c r="AY193" s="5" t="n">
         <v>7600</v>
       </c>
-      <c r="AX193" s="5" t="n">
-        <v>7660</v>
-      </c>
-      <c r="AY193" s="5" t="n">
+      <c r="AZ193" s="5" t="n">
         <v>3240</v>
       </c>
-      <c r="AZ193" s="5" t="n">
+      <c r="BA193" s="5" t="n">
         <v>10760</v>
-      </c>
-      <c r="BA193" s="5" t="n">
-        <v>10480</v>
       </c>
       <c r="BB193" s="5" t="n">
         <v>4610</v>
@@ -53156,7 +53156,7 @@
         <v>0.36</v>
       </c>
       <c r="AF194" s="5" t="n">
-        <v>2630</v>
+        <v>2620</v>
       </c>
       <c r="AG194" s="5" t="n">
         <v>1064</v>
@@ -53207,19 +53207,19 @@
         <v>105</v>
       </c>
       <c r="AW194" s="5" t="n">
+        <v>2920</v>
+      </c>
+      <c r="AX194" s="5" t="n">
+        <v>7470</v>
+      </c>
+      <c r="AY194" s="5" t="n">
         <v>4650</v>
       </c>
-      <c r="AX194" s="5" t="n">
-        <v>2920</v>
-      </c>
-      <c r="AY194" s="5" t="n">
+      <c r="AZ194" s="5" t="n">
         <v>1860</v>
       </c>
-      <c r="AZ194" s="5" t="n">
+      <c r="BA194" s="5" t="n">
         <v>12510</v>
-      </c>
-      <c r="BA194" s="5" t="n">
-        <v>7470</v>
       </c>
       <c r="BB194" s="5" t="n">
         <v>5000</v>
@@ -53468,19 +53468,19 @@
         <v>92</v>
       </c>
       <c r="AW195" s="5" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AX195" s="5" t="n">
+        <v>3210</v>
+      </c>
+      <c r="AY195" s="5" t="n">
         <v>2850</v>
       </c>
-      <c r="AX195" s="5" t="n">
-        <v>1650</v>
-      </c>
-      <c r="AY195" s="5" t="n">
+      <c r="AZ195" s="5" t="n">
         <v>1180</v>
       </c>
-      <c r="AZ195" s="5" t="n">
+      <c r="BA195" s="5" t="n">
         <v>5740</v>
-      </c>
-      <c r="BA195" s="5" t="n">
-        <v>3210</v>
       </c>
       <c r="BB195" s="5" t="n">
         <v>2400</v>
@@ -53729,19 +53729,19 @@
         <v>92</v>
       </c>
       <c r="AW196" s="5" t="n">
+        <v>3370</v>
+      </c>
+      <c r="AX196" s="5" t="n">
+        <v>5890</v>
+      </c>
+      <c r="AY196" s="5" t="n">
         <v>4980</v>
       </c>
-      <c r="AX196" s="5" t="n">
-        <v>3370</v>
-      </c>
-      <c r="AY196" s="5" t="n">
+      <c r="AZ196" s="5" t="n">
         <v>2030</v>
       </c>
-      <c r="AZ196" s="5" t="n">
+      <c r="BA196" s="5" t="n">
         <v>8310</v>
-      </c>
-      <c r="BA196" s="5" t="n">
-        <v>5890</v>
       </c>
       <c r="BB196" s="5" t="n">
         <v>3390</v>
@@ -53990,19 +53990,19 @@
         <v>92</v>
       </c>
       <c r="AW197" s="5" t="n">
+        <v>3210</v>
+      </c>
+      <c r="AX197" s="5" t="n">
+        <v>4720</v>
+      </c>
+      <c r="AY197" s="5" t="n">
         <v>4840</v>
       </c>
-      <c r="AX197" s="5" t="n">
-        <v>3210</v>
-      </c>
-      <c r="AY197" s="5" t="n">
+      <c r="AZ197" s="5" t="n">
         <v>2050</v>
       </c>
-      <c r="AZ197" s="5" t="n">
+      <c r="BA197" s="5" t="n">
         <v>7410</v>
-      </c>
-      <c r="BA197" s="5" t="n">
-        <v>4720</v>
       </c>
       <c r="BB197" s="5" t="n">
         <v>3170</v>
@@ -54251,19 +54251,19 @@
         <v>92</v>
       </c>
       <c r="AW198" s="5" t="n">
+        <v>2920</v>
+      </c>
+      <c r="AX198" s="5" t="n">
+        <v>4990</v>
+      </c>
+      <c r="AY198" s="5" t="n">
         <v>4700</v>
       </c>
-      <c r="AX198" s="5" t="n">
-        <v>2920</v>
-      </c>
-      <c r="AY198" s="5" t="n">
+      <c r="AZ198" s="5" t="n">
         <v>1920</v>
       </c>
-      <c r="AZ198" s="5" t="n">
+      <c r="BA198" s="5" t="n">
         <v>8180</v>
-      </c>
-      <c r="BA198" s="5" t="n">
-        <v>4990</v>
       </c>
       <c r="BB198" s="5" t="n">
         <v>3360</v>
@@ -54461,7 +54461,7 @@
         <v>0.47</v>
       </c>
       <c r="AF199" s="5" t="n">
-        <v>1620</v>
+        <v>1630</v>
       </c>
       <c r="AG199" s="5" t="n">
         <v>892</v>
@@ -54512,19 +54512,19 @@
         <v>105</v>
       </c>
       <c r="AW199" s="5" t="n">
+        <v>5470</v>
+      </c>
+      <c r="AX199" s="5" t="n">
+        <v>10730</v>
+      </c>
+      <c r="AY199" s="5" t="n">
         <v>8700</v>
       </c>
-      <c r="AX199" s="5" t="n">
-        <v>5470</v>
-      </c>
-      <c r="AY199" s="5" t="n">
+      <c r="AZ199" s="5" t="n">
         <v>3550</v>
       </c>
-      <c r="AZ199" s="5" t="n">
+      <c r="BA199" s="5" t="n">
         <v>17060</v>
-      </c>
-      <c r="BA199" s="5" t="n">
-        <v>10730</v>
       </c>
       <c r="BB199" s="5" t="n">
         <v>7130</v>
@@ -54773,19 +54773,19 @@
         <v>96</v>
       </c>
       <c r="AW200" s="5" t="n">
+        <v>2050</v>
+      </c>
+      <c r="AX200" s="5" t="n">
+        <v>5230</v>
+      </c>
+      <c r="AY200" s="5" t="n">
         <v>2700</v>
       </c>
-      <c r="AX200" s="5" t="n">
-        <v>2050</v>
-      </c>
-      <c r="AY200" s="5" t="n">
+      <c r="AZ200" s="5" t="n">
         <v>1170</v>
       </c>
-      <c r="AZ200" s="5" t="n">
+      <c r="BA200" s="5" t="n">
         <v>7960</v>
-      </c>
-      <c r="BA200" s="5" t="n">
-        <v>5230</v>
       </c>
       <c r="BB200" s="5" t="n">
         <v>3430</v>
@@ -55034,19 +55034,19 @@
         <v>92</v>
       </c>
       <c r="AW201" s="5" t="n">
+        <v>1730</v>
+      </c>
+      <c r="AX201" s="5" t="n">
+        <v>2880</v>
+      </c>
+      <c r="AY201" s="5" t="n">
         <v>2040</v>
       </c>
-      <c r="AX201" s="5" t="n">
-        <v>1730</v>
-      </c>
-      <c r="AY201" s="5" t="n">
+      <c r="AZ201" s="5" t="n">
         <v>850</v>
       </c>
-      <c r="AZ201" s="5" t="n">
+      <c r="BA201" s="5" t="n">
         <v>3570</v>
-      </c>
-      <c r="BA201" s="5" t="n">
-        <v>2880</v>
       </c>
       <c r="BB201" s="5" t="n">
         <v>1490</v>
@@ -55295,19 +55295,19 @@
         <v>92</v>
       </c>
       <c r="AW202" s="5" t="n">
+        <v>2840</v>
+      </c>
+      <c r="AX202" s="5" t="n">
+        <v>4330</v>
+      </c>
+      <c r="AY202" s="5" t="n">
         <v>4040</v>
       </c>
-      <c r="AX202" s="5" t="n">
-        <v>2840</v>
-      </c>
-      <c r="AY202" s="5" t="n">
+      <c r="AZ202" s="5" t="n">
         <v>1660</v>
       </c>
-      <c r="AZ202" s="5" t="n">
+      <c r="BA202" s="5" t="n">
         <v>6140</v>
-      </c>
-      <c r="BA202" s="5" t="n">
-        <v>4330</v>
       </c>
       <c r="BB202" s="5" t="n">
         <v>2540</v>
@@ -55505,7 +55505,7 @@
         <v>0.42</v>
       </c>
       <c r="AF203" s="5" t="n">
-        <v>4210</v>
+        <v>4190</v>
       </c>
       <c r="AG203" s="5" t="n">
         <v>2059</v>
@@ -55556,19 +55556,19 @@
         <v>92</v>
       </c>
       <c r="AW203" s="5" t="n">
+        <v>3020</v>
+      </c>
+      <c r="AX203" s="5" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AY203" s="5" t="n">
         <v>3890</v>
       </c>
-      <c r="AX203" s="5" t="n">
-        <v>3020</v>
-      </c>
-      <c r="AY203" s="5" t="n">
+      <c r="AZ203" s="5" t="n">
         <v>1660</v>
       </c>
-      <c r="AZ203" s="5" t="n">
+      <c r="BA203" s="5" t="n">
         <v>6110</v>
-      </c>
-      <c r="BA203" s="5" t="n">
-        <v>4750</v>
       </c>
       <c r="BB203" s="5" t="n">
         <v>2680</v>
@@ -55817,19 +55817,19 @@
         <v>105</v>
       </c>
       <c r="AW204" s="5" t="n">
+        <v>1870</v>
+      </c>
+      <c r="AX204" s="5" t="n">
+        <v>4320</v>
+      </c>
+      <c r="AY204" s="5" t="n">
         <v>2300</v>
       </c>
-      <c r="AX204" s="5" t="n">
-        <v>1870</v>
-      </c>
-      <c r="AY204" s="5" t="n">
+      <c r="AZ204" s="5" t="n">
         <v>980</v>
       </c>
-      <c r="AZ204" s="5" t="n">
+      <c r="BA204" s="5" t="n">
         <v>5870</v>
-      </c>
-      <c r="BA204" s="5" t="n">
-        <v>4320</v>
       </c>
       <c r="BB204" s="5" t="n">
         <v>2440</v>
@@ -56078,19 +56078,19 @@
         <v>92</v>
       </c>
       <c r="AW205" s="5" t="n">
+        <v>1370</v>
+      </c>
+      <c r="AX205" s="5" t="n">
+        <v>2390</v>
+      </c>
+      <c r="AY205" s="5" t="n">
         <v>1540</v>
       </c>
-      <c r="AX205" s="5" t="n">
-        <v>1370</v>
-      </c>
-      <c r="AY205" s="5" t="n">
+      <c r="AZ205" s="5" t="n">
         <v>630</v>
       </c>
-      <c r="AZ205" s="5" t="n">
+      <c r="BA205" s="5" t="n">
         <v>2810</v>
-      </c>
-      <c r="BA205" s="5" t="n">
-        <v>2390</v>
       </c>
       <c r="BB205" s="5" t="n">
         <v>1240</v>
@@ -56288,7 +56288,7 @@
         <v>0.15</v>
       </c>
       <c r="AF206" s="5" t="n">
-        <v>2570</v>
+        <v>2580</v>
       </c>
       <c r="AG206" s="5" t="n">
         <v>436</v>
@@ -56339,19 +56339,19 @@
         <v>96</v>
       </c>
       <c r="AW206" s="5" t="n">
+        <v>2310</v>
+      </c>
+      <c r="AX206" s="5" t="n">
+        <v>4210</v>
+      </c>
+      <c r="AY206" s="5" t="n">
         <v>3570</v>
       </c>
-      <c r="AX206" s="5" t="n">
-        <v>2310</v>
-      </c>
-      <c r="AY206" s="5" t="n">
+      <c r="AZ206" s="5" t="n">
         <v>1520</v>
       </c>
-      <c r="AZ206" s="5" t="n">
+      <c r="BA206" s="5" t="n">
         <v>6590</v>
-      </c>
-      <c r="BA206" s="5" t="n">
-        <v>4210</v>
       </c>
       <c r="BB206" s="5" t="n">
         <v>2880</v>
@@ -56600,19 +56600,19 @@
         <v>105</v>
       </c>
       <c r="AW207" s="5" t="n">
+        <v>3360</v>
+      </c>
+      <c r="AX207" s="5" t="n">
+        <v>5210</v>
+      </c>
+      <c r="AY207" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="AX207" s="5" t="n">
-        <v>3360</v>
-      </c>
-      <c r="AY207" s="5" t="n">
+      <c r="AZ207" s="5" t="n">
         <v>1740</v>
       </c>
-      <c r="AZ207" s="5" t="n">
+      <c r="BA207" s="5" t="n">
         <v>6420</v>
-      </c>
-      <c r="BA207" s="5" t="n">
-        <v>5210</v>
       </c>
       <c r="BB207" s="5" t="n">
         <v>2820</v>
@@ -56861,19 +56861,19 @@
         <v>105</v>
       </c>
       <c r="AW208" s="5" t="n">
+        <v>8650</v>
+      </c>
+      <c r="AX208" s="5" t="n">
+        <v>12570</v>
+      </c>
+      <c r="AY208" s="5" t="n">
         <v>8580</v>
       </c>
-      <c r="AX208" s="5" t="n">
-        <v>8650</v>
-      </c>
-      <c r="AY208" s="5" t="n">
+      <c r="AZ208" s="5" t="n">
         <v>3840</v>
       </c>
-      <c r="AZ208" s="5" t="n">
+      <c r="BA208" s="5" t="n">
         <v>13450</v>
-      </c>
-      <c r="BA208" s="5" t="n">
-        <v>12570</v>
       </c>
       <c r="BB208" s="5" t="n">
         <v>6140</v>
@@ -57071,7 +57071,7 @@
         <v>0.54</v>
       </c>
       <c r="AF209" s="5" t="n">
-        <v>4090</v>
+        <v>4100</v>
       </c>
       <c r="AG209" s="5" t="n">
         <v>1534</v>
@@ -57122,19 +57122,19 @@
         <v>105</v>
       </c>
       <c r="AW209" s="5" t="n">
+        <v>3440</v>
+      </c>
+      <c r="AX209" s="5" t="n">
+        <v>6310</v>
+      </c>
+      <c r="AY209" s="5" t="n">
         <v>4420</v>
       </c>
-      <c r="AX209" s="5" t="n">
-        <v>3440</v>
-      </c>
-      <c r="AY209" s="5" t="n">
+      <c r="AZ209" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="AZ209" s="5" t="n">
+      <c r="BA209" s="5" t="n">
         <v>9220</v>
-      </c>
-      <c r="BA209" s="5" t="n">
-        <v>6310</v>
       </c>
       <c r="BB209" s="5" t="n">
         <v>3780</v>
@@ -57383,19 +57383,19 @@
         <v>105</v>
       </c>
       <c r="AW210" s="5" t="n">
+        <v>1370</v>
+      </c>
+      <c r="AX210" s="5" t="n">
+        <v>2580</v>
+      </c>
+      <c r="AY210" s="5" t="n">
         <v>1610</v>
       </c>
-      <c r="AX210" s="5" t="n">
-        <v>1370</v>
-      </c>
-      <c r="AY210" s="5" t="n">
+      <c r="AZ210" s="5" t="n">
         <v>710</v>
       </c>
-      <c r="AZ210" s="5" t="n">
+      <c r="BA210" s="5" t="n">
         <v>3090</v>
-      </c>
-      <c r="BA210" s="5" t="n">
-        <v>2580</v>
       </c>
       <c r="BB210" s="5" t="n">
         <v>1390</v>
@@ -57593,7 +57593,7 @@
         <v>0.34</v>
       </c>
       <c r="AF211" s="5" t="n">
-        <v>4440</v>
+        <v>4430</v>
       </c>
       <c r="AG211" s="5" t="n">
         <v>2021</v>
@@ -57644,19 +57644,19 @@
         <v>96</v>
       </c>
       <c r="AW211" s="5" t="n">
+        <v>3410</v>
+      </c>
+      <c r="AX211" s="5" t="n">
+        <v>5940</v>
+      </c>
+      <c r="AY211" s="5" t="n">
         <v>4300</v>
       </c>
-      <c r="AX211" s="5" t="n">
-        <v>3410</v>
-      </c>
-      <c r="AY211" s="5" t="n">
+      <c r="AZ211" s="5" t="n">
         <v>2060</v>
       </c>
-      <c r="AZ211" s="5" t="n">
+      <c r="BA211" s="5" t="n">
         <v>7970</v>
-      </c>
-      <c r="BA211" s="5" t="n">
-        <v>5940</v>
       </c>
       <c r="BB211" s="5" t="n">
         <v>3770</v>
@@ -57905,19 +57905,19 @@
         <v>92</v>
       </c>
       <c r="AW212" s="5" t="n">
+        <v>4460</v>
+      </c>
+      <c r="AX212" s="5" t="n">
+        <v>7800</v>
+      </c>
+      <c r="AY212" s="5" t="n">
         <v>4380</v>
       </c>
-      <c r="AX212" s="5" t="n">
-        <v>4460</v>
-      </c>
-      <c r="AY212" s="5" t="n">
+      <c r="AZ212" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="AZ212" s="5" t="n">
+      <c r="BA212" s="5" t="n">
         <v>8360</v>
-      </c>
-      <c r="BA212" s="5" t="n">
-        <v>7800</v>
       </c>
       <c r="BB212" s="5" t="n">
         <v>3740</v>
@@ -58166,19 +58166,19 @@
         <v>96</v>
       </c>
       <c r="AW213" s="5" t="n">
+        <v>3670</v>
+      </c>
+      <c r="AX213" s="5" t="n">
+        <v>6150</v>
+      </c>
+      <c r="AY213" s="5" t="n">
         <v>5640</v>
       </c>
-      <c r="AX213" s="5" t="n">
-        <v>3670</v>
-      </c>
-      <c r="AY213" s="5" t="n">
+      <c r="AZ213" s="5" t="n">
         <v>2250</v>
       </c>
-      <c r="AZ213" s="5" t="n">
+      <c r="BA213" s="5" t="n">
         <v>9560</v>
-      </c>
-      <c r="BA213" s="5" t="n">
-        <v>6150</v>
       </c>
       <c r="BB213" s="5" t="n">
         <v>3830</v>
@@ -58427,19 +58427,19 @@
         <v>105</v>
       </c>
       <c r="AW214" s="5" t="n">
+        <v>4910</v>
+      </c>
+      <c r="AX214" s="5" t="n">
+        <v>6900</v>
+      </c>
+      <c r="AY214" s="5" t="n">
         <v>6160</v>
       </c>
-      <c r="AX214" s="5" t="n">
-        <v>4910</v>
-      </c>
-      <c r="AY214" s="5" t="n">
+      <c r="AZ214" s="5" t="n">
         <v>2660</v>
       </c>
-      <c r="AZ214" s="5" t="n">
+      <c r="BA214" s="5" t="n">
         <v>9130</v>
-      </c>
-      <c r="BA214" s="5" t="n">
-        <v>6900</v>
       </c>
       <c r="BB214" s="5" t="n">
         <v>3930</v>
@@ -58688,19 +58688,19 @@
         <v>105</v>
       </c>
       <c r="AW215" s="5" t="n">
+        <v>4080</v>
+      </c>
+      <c r="AX215" s="5" t="n">
+        <v>5930</v>
+      </c>
+      <c r="AY215" s="5" t="n">
         <v>5290</v>
       </c>
-      <c r="AX215" s="5" t="n">
-        <v>4080</v>
-      </c>
-      <c r="AY215" s="5" t="n">
+      <c r="AZ215" s="5" t="n">
         <v>2200</v>
       </c>
-      <c r="AZ215" s="5" t="n">
+      <c r="BA215" s="5" t="n">
         <v>7860</v>
-      </c>
-      <c r="BA215" s="5" t="n">
-        <v>5930</v>
       </c>
       <c r="BB215" s="5" t="n">
         <v>3320</v>
@@ -58898,7 +58898,7 @@
         <v>0.39</v>
       </c>
       <c r="AF216" s="5" t="n">
-        <v>2360</v>
+        <v>2370</v>
       </c>
       <c r="AG216" s="5" t="n">
         <v>260</v>
@@ -58949,19 +58949,19 @@
         <v>96</v>
       </c>
       <c r="AW216" s="5" t="n">
+        <v>4040</v>
+      </c>
+      <c r="AX216" s="5" t="n">
+        <v>6090</v>
+      </c>
+      <c r="AY216" s="5" t="n">
         <v>4300</v>
       </c>
-      <c r="AX216" s="5" t="n">
-        <v>4040</v>
-      </c>
-      <c r="AY216" s="5" t="n">
+      <c r="AZ216" s="5" t="n">
         <v>2170</v>
       </c>
-      <c r="AZ216" s="5" t="n">
+      <c r="BA216" s="5" t="n">
         <v>7180</v>
-      </c>
-      <c r="BA216" s="5" t="n">
-        <v>6090</v>
       </c>
       <c r="BB216" s="5" t="n">
         <v>3460</v>
@@ -59210,19 +59210,19 @@
         <v>105</v>
       </c>
       <c r="AW217" s="5" t="n">
+        <v>1960</v>
+      </c>
+      <c r="AX217" s="5" t="n">
+        <v>3230</v>
+      </c>
+      <c r="AY217" s="5" t="n">
         <v>2280</v>
       </c>
-      <c r="AX217" s="5" t="n">
-        <v>1960</v>
-      </c>
-      <c r="AY217" s="5" t="n">
+      <c r="AZ217" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="AZ217" s="5" t="n">
+      <c r="BA217" s="5" t="n">
         <v>4080</v>
-      </c>
-      <c r="BA217" s="5" t="n">
-        <v>3230</v>
       </c>
       <c r="BB217" s="5" t="n">
         <v>1790</v>
@@ -59471,19 +59471,19 @@
         <v>92</v>
       </c>
       <c r="AW218" s="5" t="n">
+        <v>3960</v>
+      </c>
+      <c r="AX218" s="5" t="n">
+        <v>5730</v>
+      </c>
+      <c r="AY218" s="5" t="n">
         <v>4120</v>
       </c>
-      <c r="AX218" s="5" t="n">
-        <v>3960</v>
-      </c>
-      <c r="AY218" s="5" t="n">
+      <c r="AZ218" s="5" t="n">
         <v>1820</v>
       </c>
-      <c r="AZ218" s="5" t="n">
+      <c r="BA218" s="5" t="n">
         <v>6340</v>
-      </c>
-      <c r="BA218" s="5" t="n">
-        <v>5730</v>
       </c>
       <c r="BB218" s="5" t="n">
         <v>2840</v>
@@ -59732,19 +59732,19 @@
         <v>105</v>
       </c>
       <c r="AW219" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AX219" s="5" t="n">
+        <v>4610</v>
+      </c>
+      <c r="AY219" s="5" t="n">
         <v>3490</v>
       </c>
-      <c r="AX219" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AY219" s="5" t="n">
+      <c r="AZ219" s="5" t="n">
         <v>1470</v>
       </c>
-      <c r="AZ219" s="5" t="n">
+      <c r="BA219" s="5" t="n">
         <v>6260</v>
-      </c>
-      <c r="BA219" s="5" t="n">
-        <v>4610</v>
       </c>
       <c r="BB219" s="5" t="n">
         <v>2650</v>
@@ -59993,19 +59993,19 @@
         <v>96</v>
       </c>
       <c r="AW220" s="5" t="n">
+        <v>1950</v>
+      </c>
+      <c r="AX220" s="5" t="n">
+        <v>4280</v>
+      </c>
+      <c r="AY220" s="5" t="n">
         <v>2800</v>
       </c>
-      <c r="AX220" s="5" t="n">
-        <v>1950</v>
-      </c>
-      <c r="AY220" s="5" t="n">
+      <c r="AZ220" s="5" t="n">
         <v>1280</v>
       </c>
-      <c r="AZ220" s="5" t="n">
+      <c r="BA220" s="5" t="n">
         <v>6260</v>
-      </c>
-      <c r="BA220" s="5" t="n">
-        <v>4280</v>
       </c>
       <c r="BB220" s="5" t="n">
         <v>2880</v>
@@ -60254,19 +60254,19 @@
         <v>105</v>
       </c>
       <c r="AW221" s="5" t="n">
+        <v>5530</v>
+      </c>
+      <c r="AX221" s="5" t="n">
+        <v>7910</v>
+      </c>
+      <c r="AY221" s="5" t="n">
         <v>5920</v>
       </c>
-      <c r="AX221" s="5" t="n">
-        <v>5530</v>
-      </c>
-      <c r="AY221" s="5" t="n">
+      <c r="AZ221" s="5" t="n">
         <v>2540</v>
       </c>
-      <c r="AZ221" s="5" t="n">
+      <c r="BA221" s="5" t="n">
         <v>8920</v>
-      </c>
-      <c r="BA221" s="5" t="n">
-        <v>7910</v>
       </c>
       <c r="BB221" s="5" t="n">
         <v>3890</v>
@@ -60515,19 +60515,19 @@
         <v>92</v>
       </c>
       <c r="AW222" s="5" t="n">
+        <v>2560</v>
+      </c>
+      <c r="AX222" s="5" t="n">
+        <v>4980</v>
+      </c>
+      <c r="AY222" s="5" t="n">
         <v>2030</v>
       </c>
-      <c r="AX222" s="5" t="n">
-        <v>2560</v>
-      </c>
-      <c r="AY222" s="5" t="n">
+      <c r="AZ222" s="5" t="n">
         <v>1010</v>
       </c>
-      <c r="AZ222" s="5" t="n">
+      <c r="BA222" s="5" t="n">
         <v>4540</v>
-      </c>
-      <c r="BA222" s="5" t="n">
-        <v>4980</v>
       </c>
       <c r="BB222" s="5" t="n">
         <v>2230</v>
@@ -60776,19 +60776,19 @@
         <v>105</v>
       </c>
       <c r="AW223" s="5" t="n">
+        <v>2370</v>
+      </c>
+      <c r="AX223" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="AY223" s="5" t="n">
         <v>3380</v>
       </c>
-      <c r="AX223" s="5" t="n">
-        <v>2370</v>
-      </c>
-      <c r="AY223" s="5" t="n">
+      <c r="AZ223" s="5" t="n">
         <v>1480</v>
       </c>
-      <c r="AZ223" s="5" t="n">
+      <c r="BA223" s="5" t="n">
         <v>6220</v>
-      </c>
-      <c r="BA223" s="5" t="n">
-        <v>4260</v>
       </c>
       <c r="BB223" s="5" t="n">
         <v>2690</v>
@@ -61037,19 +61037,19 @@
         <v>105</v>
       </c>
       <c r="AW224" s="5" t="n">
+        <v>1690</v>
+      </c>
+      <c r="AX224" s="5" t="n">
+        <v>3130</v>
+      </c>
+      <c r="AY224" s="5" t="n">
         <v>2700</v>
       </c>
-      <c r="AX224" s="5" t="n">
-        <v>1690</v>
-      </c>
-      <c r="AY224" s="5" t="n">
+      <c r="AZ224" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="AZ224" s="5" t="n">
+      <c r="BA224" s="5" t="n">
         <v>5130</v>
-      </c>
-      <c r="BA224" s="5" t="n">
-        <v>3130</v>
       </c>
       <c r="BB224" s="5" t="n">
         <v>2080</v>
@@ -61247,7 +61247,7 @@
         <v>0.37</v>
       </c>
       <c r="AF225" s="5" t="n">
-        <v>3850</v>
+        <v>3860</v>
       </c>
       <c r="AG225" s="5" t="n">
         <v>1731</v>
@@ -61298,19 +61298,19 @@
         <v>105</v>
       </c>
       <c r="AW225" s="5" t="n">
+        <v>6130</v>
+      </c>
+      <c r="AX225" s="5" t="n">
+        <v>9180</v>
+      </c>
+      <c r="AY225" s="5" t="n">
         <v>8830</v>
       </c>
-      <c r="AX225" s="5" t="n">
-        <v>6130</v>
-      </c>
-      <c r="AY225" s="5" t="n">
+      <c r="AZ225" s="5" t="n">
         <v>3780</v>
       </c>
-      <c r="AZ225" s="5" t="n">
+      <c r="BA225" s="5" t="n">
         <v>13600</v>
-      </c>
-      <c r="BA225" s="5" t="n">
-        <v>9180</v>
       </c>
       <c r="BB225" s="5" t="n">
         <v>5850</v>
@@ -61508,7 +61508,7 @@
         <v>0.35</v>
       </c>
       <c r="AF226" s="5" t="n">
-        <v>1730</v>
+        <v>1720</v>
       </c>
       <c r="AG226" s="5" t="n">
         <v>238</v>
@@ -61559,19 +61559,19 @@
         <v>96</v>
       </c>
       <c r="AW226" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="AX226" s="5" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AY226" s="5" t="n">
         <v>1160</v>
       </c>
-      <c r="AX226" s="5" t="n">
-        <v>790</v>
-      </c>
-      <c r="AY226" s="5" t="n">
+      <c r="AZ226" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="AZ226" s="5" t="n">
+      <c r="BA226" s="5" t="n">
         <v>2550</v>
-      </c>
-      <c r="BA226" s="5" t="n">
-        <v>1740</v>
       </c>
       <c r="BB226" s="5" t="n">
         <v>1050</v>
@@ -61769,7 +61769,7 @@
         <v>0.35</v>
       </c>
       <c r="AF227" s="5" t="n">
-        <v>11740</v>
+        <v>11720</v>
       </c>
       <c r="AG227" s="5" t="n">
         <v>7299</v>
@@ -61820,19 +61820,19 @@
         <v>92</v>
       </c>
       <c r="AW227" s="5" t="n">
+        <v>10900</v>
+      </c>
+      <c r="AX227" s="5" t="n">
+        <v>16460</v>
+      </c>
+      <c r="AY227" s="5" t="n">
         <v>9570</v>
       </c>
-      <c r="AX227" s="5" t="n">
-        <v>10900</v>
-      </c>
-      <c r="AY227" s="5" t="n">
+      <c r="AZ227" s="5" t="n">
         <v>4350</v>
       </c>
-      <c r="AZ227" s="5" t="n">
+      <c r="BA227" s="5" t="n">
         <v>15700</v>
-      </c>
-      <c r="BA227" s="5" t="n">
-        <v>16460</v>
       </c>
       <c r="BB227" s="5" t="n">
         <v>7100</v>
@@ -62030,7 +62030,7 @@
         <v>0.47</v>
       </c>
       <c r="AF228" s="5" t="n">
-        <v>7470</v>
+        <v>7440</v>
       </c>
       <c r="AG228" s="5" t="n">
         <v>5742</v>
@@ -62081,19 +62081,19 @@
         <v>92</v>
       </c>
       <c r="AW228" s="5" t="n">
+        <v>10480</v>
+      </c>
+      <c r="AX228" s="5" t="n">
+        <v>15470</v>
+      </c>
+      <c r="AY228" s="5" t="n">
         <v>13180</v>
       </c>
-      <c r="AX228" s="5" t="n">
-        <v>10480</v>
-      </c>
-      <c r="AY228" s="5" t="n">
+      <c r="AZ228" s="5" t="n">
         <v>6150</v>
       </c>
-      <c r="AZ228" s="5" t="n">
+      <c r="BA228" s="5" t="n">
         <v>19770</v>
-      </c>
-      <c r="BA228" s="5" t="n">
-        <v>15470</v>
       </c>
       <c r="BB228" s="5" t="n">
         <v>9210</v>
@@ -62291,7 +62291,7 @@
         <v>0.38</v>
       </c>
       <c r="AF229" s="5" t="n">
-        <v>4510</v>
+        <v>4500</v>
       </c>
       <c r="AG229" s="5" t="n">
         <v>1083</v>
@@ -62342,19 +62342,19 @@
         <v>105</v>
       </c>
       <c r="AW229" s="5" t="n">
+        <v>6140</v>
+      </c>
+      <c r="AX229" s="5" t="n">
+        <v>10270</v>
+      </c>
+      <c r="AY229" s="5" t="n">
         <v>9440</v>
       </c>
-      <c r="AX229" s="5" t="n">
-        <v>6140</v>
-      </c>
-      <c r="AY229" s="5" t="n">
+      <c r="AZ229" s="5" t="n">
         <v>4090</v>
       </c>
-      <c r="AZ229" s="5" t="n">
+      <c r="BA229" s="5" t="n">
         <v>15640</v>
-      </c>
-      <c r="BA229" s="5" t="n">
-        <v>10270</v>
       </c>
       <c r="BB229" s="5" t="n">
         <v>6810</v>
@@ -62552,7 +62552,7 @@
         <v>0.39</v>
       </c>
       <c r="AF230" s="5" t="n">
-        <v>2850</v>
+        <v>2860</v>
       </c>
       <c r="AG230" s="5" t="n">
         <v>325</v>
@@ -62603,19 +62603,19 @@
         <v>105</v>
       </c>
       <c r="AW230" s="5" t="n">
+        <v>3960</v>
+      </c>
+      <c r="AX230" s="5" t="n">
+        <v>7010</v>
+      </c>
+      <c r="AY230" s="5" t="n">
         <v>4930</v>
       </c>
-      <c r="AX230" s="5" t="n">
-        <v>3960</v>
-      </c>
-      <c r="AY230" s="5" t="n">
+      <c r="AZ230" s="5" t="n">
         <v>2250</v>
       </c>
-      <c r="AZ230" s="5" t="n">
+      <c r="BA230" s="5" t="n">
         <v>9490</v>
-      </c>
-      <c r="BA230" s="5" t="n">
-        <v>7010</v>
       </c>
       <c r="BB230" s="5" t="n">
         <v>4270</v>
@@ -62813,7 +62813,7 @@
         <v>0.54</v>
       </c>
       <c r="AF231" s="5" t="n">
-        <v>9600</v>
+        <v>9610</v>
       </c>
       <c r="AG231" s="5" t="n">
         <v>3506</v>
@@ -62864,19 +62864,19 @@
         <v>96</v>
       </c>
       <c r="AW231" s="5" t="n">
+        <v>9040</v>
+      </c>
+      <c r="AX231" s="5" t="n">
+        <v>25910</v>
+      </c>
+      <c r="AY231" s="5" t="n">
         <v>14180</v>
       </c>
-      <c r="AX231" s="5" t="n">
-        <v>9040</v>
-      </c>
-      <c r="AY231" s="5" t="n">
+      <c r="AZ231" s="5" t="n">
         <v>5660</v>
       </c>
-      <c r="AZ231" s="5" t="n">
+      <c r="BA231" s="5" t="n">
         <v>36180</v>
-      </c>
-      <c r="BA231" s="5" t="n">
-        <v>25910</v>
       </c>
       <c r="BB231" s="5" t="n">
         <v>14760</v>
@@ -63125,19 +63125,19 @@
         <v>92</v>
       </c>
       <c r="AW232" s="5" t="n">
+        <v>3270</v>
+      </c>
+      <c r="AX232" s="5" t="n">
+        <v>6680</v>
+      </c>
+      <c r="AY232" s="5" t="n">
         <v>5280</v>
       </c>
-      <c r="AX232" s="5" t="n">
-        <v>3270</v>
-      </c>
-      <c r="AY232" s="5" t="n">
+      <c r="AZ232" s="5" t="n">
         <v>2240</v>
       </c>
-      <c r="AZ232" s="5" t="n">
+      <c r="BA232" s="5" t="n">
         <v>10320</v>
-      </c>
-      <c r="BA232" s="5" t="n">
-        <v>6680</v>
       </c>
       <c r="BB232" s="5" t="n">
         <v>4360</v>
@@ -63386,19 +63386,19 @@
         <v>92</v>
       </c>
       <c r="AW233" s="5" t="n">
+        <v>3620</v>
+      </c>
+      <c r="AX233" s="5" t="n">
+        <v>6320</v>
+      </c>
+      <c r="AY233" s="5" t="n">
         <v>5520</v>
       </c>
-      <c r="AX233" s="5" t="n">
-        <v>3620</v>
-      </c>
-      <c r="AY233" s="5" t="n">
+      <c r="AZ233" s="5" t="n">
         <v>2380</v>
       </c>
-      <c r="AZ233" s="5" t="n">
+      <c r="BA233" s="5" t="n">
         <v>9760</v>
-      </c>
-      <c r="BA233" s="5" t="n">
-        <v>6320</v>
       </c>
       <c r="BB233" s="5" t="n">
         <v>4270</v>
@@ -63647,19 +63647,19 @@
         <v>96</v>
       </c>
       <c r="AW234" s="5" t="n">
+        <v>6200</v>
+      </c>
+      <c r="AX234" s="5" t="n">
+        <v>18210</v>
+      </c>
+      <c r="AY234" s="5" t="n">
         <v>8360</v>
       </c>
-      <c r="AX234" s="5" t="n">
-        <v>6200</v>
-      </c>
-      <c r="AY234" s="5" t="n">
+      <c r="AZ234" s="5" t="n">
         <v>3510</v>
       </c>
-      <c r="AZ234" s="5" t="n">
+      <c r="BA234" s="5" t="n">
         <v>21840</v>
-      </c>
-      <c r="BA234" s="5" t="n">
-        <v>18210</v>
       </c>
       <c r="BB234" s="5" t="n">
         <v>9250</v>
@@ -63908,19 +63908,19 @@
         <v>96</v>
       </c>
       <c r="AW235" s="5" t="n">
+        <v>5160</v>
+      </c>
+      <c r="AX235" s="5" t="n">
+        <v>11320</v>
+      </c>
+      <c r="AY235" s="5" t="n">
         <v>7530</v>
       </c>
-      <c r="AX235" s="5" t="n">
-        <v>5160</v>
-      </c>
-      <c r="AY235" s="5" t="n">
+      <c r="AZ235" s="5" t="n">
         <v>3290</v>
       </c>
-      <c r="AZ235" s="5" t="n">
+      <c r="BA235" s="5" t="n">
         <v>16680</v>
-      </c>
-      <c r="BA235" s="5" t="n">
-        <v>11320</v>
       </c>
       <c r="BB235" s="5" t="n">
         <v>7350</v>
@@ -64118,7 +64118,7 @@
         <v>0.32</v>
       </c>
       <c r="AF236" s="5" t="n">
-        <v>5160</v>
+        <v>5150</v>
       </c>
       <c r="AG236" s="5" t="n">
         <v>246</v>
@@ -64169,19 +64169,19 @@
         <v>92</v>
       </c>
       <c r="AW236" s="5" t="n">
+        <v>5780</v>
+      </c>
+      <c r="AX236" s="5" t="n">
+        <v>10820</v>
+      </c>
+      <c r="AY236" s="5" t="n">
         <v>6920</v>
       </c>
-      <c r="AX236" s="5" t="n">
-        <v>5780</v>
-      </c>
-      <c r="AY236" s="5" t="n">
+      <c r="AZ236" s="5" t="n">
         <v>3290</v>
       </c>
-      <c r="AZ236" s="5" t="n">
+      <c r="BA236" s="5" t="n">
         <v>12740</v>
-      </c>
-      <c r="BA236" s="5" t="n">
-        <v>10820</v>
       </c>
       <c r="BB236" s="5" t="n">
         <v>5970</v>
@@ -64430,19 +64430,19 @@
         <v>96</v>
       </c>
       <c r="AW237" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="AX237" s="5" t="n">
+        <v>6130</v>
+      </c>
+      <c r="AY237" s="5" t="n">
         <v>3190</v>
       </c>
-      <c r="AX237" s="5" t="n">
-        <v>2060</v>
-      </c>
-      <c r="AY237" s="5" t="n">
+      <c r="AZ237" s="5" t="n">
         <v>1400</v>
       </c>
-      <c r="AZ237" s="5" t="n">
+      <c r="BA237" s="5" t="n">
         <v>8880</v>
-      </c>
-      <c r="BA237" s="5" t="n">
-        <v>6130</v>
       </c>
       <c r="BB237" s="5" t="n">
         <v>3980</v>
@@ -64691,19 +64691,19 @@
         <v>105</v>
       </c>
       <c r="AW238" s="5" t="n">
+        <v>8060</v>
+      </c>
+      <c r="AX238" s="5" t="n">
+        <v>13800</v>
+      </c>
+      <c r="AY238" s="5" t="n">
         <v>12660</v>
       </c>
-      <c r="AX238" s="5" t="n">
-        <v>8060</v>
-      </c>
-      <c r="AY238" s="5" t="n">
+      <c r="AZ238" s="5" t="n">
         <v>5730</v>
       </c>
-      <c r="AZ238" s="5" t="n">
+      <c r="BA238" s="5" t="n">
         <v>22080</v>
-      </c>
-      <c r="BA238" s="5" t="n">
-        <v>13800</v>
       </c>
       <c r="BB238" s="5" t="n">
         <v>10040</v>
@@ -64901,7 +64901,7 @@
         <v>0.29</v>
       </c>
       <c r="AF239" s="5" t="n">
-        <v>4190</v>
+        <v>4220</v>
       </c>
       <c r="AG239" s="5" t="n">
         <v>271</v>
@@ -64952,19 +64952,19 @@
         <v>96</v>
       </c>
       <c r="AW239" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AX239" s="5" t="n">
+        <v>4660</v>
+      </c>
+      <c r="AY239" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="AX239" s="5" t="n">
-        <v>2400</v>
-      </c>
-      <c r="AY239" s="5" t="n">
+      <c r="AZ239" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="AZ239" s="5" t="n">
+      <c r="BA239" s="5" t="n">
         <v>7450</v>
-      </c>
-      <c r="BA239" s="5" t="n">
-        <v>4660</v>
       </c>
       <c r="BB239" s="5" t="n">
         <v>3280</v>
@@ -65213,19 +65213,19 @@
         <v>96</v>
       </c>
       <c r="AW240" s="5" t="n">
+        <v>8380</v>
+      </c>
+      <c r="AX240" s="5" t="n">
+        <v>19840</v>
+      </c>
+      <c r="AY240" s="5" t="n">
         <v>10040</v>
       </c>
-      <c r="AX240" s="5" t="n">
-        <v>8380</v>
-      </c>
-      <c r="AY240" s="5" t="n">
+      <c r="AZ240" s="5" t="n">
         <v>4770</v>
       </c>
-      <c r="AZ240" s="5" t="n">
+      <c r="BA240" s="5" t="n">
         <v>24180</v>
-      </c>
-      <c r="BA240" s="5" t="n">
-        <v>19840</v>
       </c>
       <c r="BB240" s="5" t="n">
         <v>11420</v>
@@ -65474,19 +65474,19 @@
         <v>105</v>
       </c>
       <c r="AW241" s="5" t="n">
+        <v>3100</v>
+      </c>
+      <c r="AX241" s="5" t="n">
+        <v>5700</v>
+      </c>
+      <c r="AY241" s="5" t="n">
         <v>4390</v>
       </c>
-      <c r="AX241" s="5" t="n">
-        <v>3100</v>
-      </c>
-      <c r="AY241" s="5" t="n">
+      <c r="AZ241" s="5" t="n">
         <v>2030</v>
       </c>
-      <c r="AZ241" s="5" t="n">
+      <c r="BA241" s="5" t="n">
         <v>8190</v>
-      </c>
-      <c r="BA241" s="5" t="n">
-        <v>5700</v>
       </c>
       <c r="BB241" s="5" t="n">
         <v>3830</v>
@@ -65735,19 +65735,19 @@
         <v>105</v>
       </c>
       <c r="AW242" s="5" t="n">
+        <v>38160</v>
+      </c>
+      <c r="AX242" s="5" t="n">
+        <v>49650</v>
+      </c>
+      <c r="AY242" s="5" t="n">
         <v>61440</v>
       </c>
-      <c r="AX242" s="5" t="n">
-        <v>38160</v>
-      </c>
-      <c r="AY242" s="5" t="n">
+      <c r="AZ242" s="5" t="n">
         <v>27330</v>
       </c>
-      <c r="AZ242" s="5" t="n">
+      <c r="BA242" s="5" t="n">
         <v>80270</v>
-      </c>
-      <c r="BA242" s="5" t="n">
-        <v>49650</v>
       </c>
       <c r="BB242" s="5" t="n">
         <v>35920</v>
@@ -65996,19 +65996,19 @@
         <v>96</v>
       </c>
       <c r="AW243" s="5" t="n">
+        <v>3900</v>
+      </c>
+      <c r="AX243" s="5" t="n">
+        <v>8690</v>
+      </c>
+      <c r="AY243" s="5" t="n">
         <v>5570</v>
       </c>
-      <c r="AX243" s="5" t="n">
-        <v>3900</v>
-      </c>
-      <c r="AY243" s="5" t="n">
+      <c r="AZ243" s="5" t="n">
         <v>2640</v>
       </c>
-      <c r="AZ243" s="5" t="n">
+      <c r="BA243" s="5" t="n">
         <v>12450</v>
-      </c>
-      <c r="BA243" s="5" t="n">
-        <v>8690</v>
       </c>
       <c r="BB243" s="5" t="n">
         <v>6000</v>
@@ -66257,19 +66257,19 @@
         <v>92</v>
       </c>
       <c r="AW244" s="5" t="n">
+        <v>8800</v>
+      </c>
+      <c r="AX244" s="5" t="n">
+        <v>22470</v>
+      </c>
+      <c r="AY244" s="5" t="n">
         <v>13360</v>
       </c>
-      <c r="AX244" s="5" t="n">
-        <v>8800</v>
-      </c>
-      <c r="AY244" s="5" t="n">
+      <c r="AZ244" s="5" t="n">
         <v>5520</v>
       </c>
-      <c r="AZ244" s="5" t="n">
+      <c r="BA244" s="5" t="n">
         <v>33750</v>
-      </c>
-      <c r="BA244" s="5" t="n">
-        <v>22470</v>
       </c>
       <c r="BB244" s="5" t="n">
         <v>14530</v>
@@ -66518,19 +66518,19 @@
         <v>105</v>
       </c>
       <c r="AW245" s="5" t="n">
+        <v>3660</v>
+      </c>
+      <c r="AX245" s="5" t="n">
+        <v>6970</v>
+      </c>
+      <c r="AY245" s="5" t="n">
         <v>4820</v>
       </c>
-      <c r="AX245" s="5" t="n">
-        <v>3660</v>
-      </c>
-      <c r="AY245" s="5" t="n">
+      <c r="AZ245" s="5" t="n">
         <v>2200</v>
       </c>
-      <c r="AZ245" s="5" t="n">
+      <c r="BA245" s="5" t="n">
         <v>9340</v>
-      </c>
-      <c r="BA245" s="5" t="n">
-        <v>6970</v>
       </c>
       <c r="BB245" s="5" t="n">
         <v>4300</v>
@@ -66779,19 +66779,19 @@
         <v>105</v>
       </c>
       <c r="AW246" s="5" t="n">
+        <v>5680</v>
+      </c>
+      <c r="AX246" s="5" t="n">
+        <v>10210</v>
+      </c>
+      <c r="AY246" s="5" t="n">
         <v>8650</v>
       </c>
-      <c r="AX246" s="5" t="n">
-        <v>5680</v>
-      </c>
-      <c r="AY246" s="5" t="n">
+      <c r="AZ246" s="5" t="n">
         <v>3850</v>
       </c>
-      <c r="AZ246" s="5" t="n">
+      <c r="BA246" s="5" t="n">
         <v>15670</v>
-      </c>
-      <c r="BA246" s="5" t="n">
-        <v>10210</v>
       </c>
       <c r="BB246" s="5" t="n">
         <v>6960</v>
@@ -67040,19 +67040,19 @@
         <v>96</v>
       </c>
       <c r="AW247" s="5" t="n">
+        <v>3440</v>
+      </c>
+      <c r="AX247" s="5" t="n">
+        <v>6520</v>
+      </c>
+      <c r="AY247" s="5" t="n">
         <v>5220</v>
       </c>
-      <c r="AX247" s="5" t="n">
-        <v>3440</v>
-      </c>
-      <c r="AY247" s="5" t="n">
+      <c r="AZ247" s="5" t="n">
         <v>2440</v>
       </c>
-      <c r="AZ247" s="5" t="n">
+      <c r="BA247" s="5" t="n">
         <v>9440</v>
-      </c>
-      <c r="BA247" s="5" t="n">
-        <v>6520</v>
       </c>
       <c r="BB247" s="5" t="n">
         <v>4520</v>
@@ -67301,19 +67301,19 @@
         <v>105</v>
       </c>
       <c r="AW248" s="5" t="n">
+        <v>710</v>
+      </c>
+      <c r="AX248" s="5" t="n">
+        <v>3180</v>
+      </c>
+      <c r="AY248" s="5" t="n">
         <v>840</v>
       </c>
-      <c r="AX248" s="5" t="n">
-        <v>710</v>
-      </c>
-      <c r="AY248" s="5" t="n">
+      <c r="AZ248" s="5" t="n">
         <v>380</v>
       </c>
-      <c r="AZ248" s="5" t="n">
+      <c r="BA248" s="5" t="n">
         <v>4280</v>
-      </c>
-      <c r="BA248" s="5" t="n">
-        <v>3180</v>
       </c>
       <c r="BB248" s="5" t="n">
         <v>2040</v>
@@ -67562,19 +67562,19 @@
         <v>105</v>
       </c>
       <c r="AW249" s="5" t="n">
+        <v>3960</v>
+      </c>
+      <c r="AX249" s="5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="AY249" s="5" t="n">
         <v>5960</v>
       </c>
-      <c r="AX249" s="5" t="n">
-        <v>3960</v>
-      </c>
-      <c r="AY249" s="5" t="n">
+      <c r="AZ249" s="5" t="n">
         <v>2710</v>
       </c>
-      <c r="AZ249" s="5" t="n">
+      <c r="BA249" s="5" t="n">
         <v>11680</v>
-      </c>
-      <c r="BA249" s="5" t="n">
-        <v>7500</v>
       </c>
       <c r="BB249" s="5" t="n">
         <v>5390</v>
@@ -67823,19 +67823,19 @@
         <v>96</v>
       </c>
       <c r="AW250" s="5" t="n">
+        <v>15920</v>
+      </c>
+      <c r="AX250" s="5" t="n">
+        <v>33490</v>
+      </c>
+      <c r="AY250" s="5" t="n">
         <v>28680</v>
       </c>
-      <c r="AX250" s="5" t="n">
-        <v>15920</v>
-      </c>
-      <c r="AY250" s="5" t="n">
+      <c r="AZ250" s="5" t="n">
         <v>10710</v>
       </c>
-      <c r="AZ250" s="5" t="n">
+      <c r="BA250" s="5" t="n">
         <v>60140</v>
-      </c>
-      <c r="BA250" s="5" t="n">
-        <v>33490</v>
       </c>
       <c r="BB250" s="5" t="n">
         <v>22730</v>
@@ -68084,19 +68084,19 @@
         <v>96</v>
       </c>
       <c r="AW251" s="5" t="n">
+        <v>5990</v>
+      </c>
+      <c r="AX251" s="5" t="n">
+        <v>15790</v>
+      </c>
+      <c r="AY251" s="5" t="n">
         <v>6880</v>
       </c>
-      <c r="AX251" s="5" t="n">
-        <v>5990</v>
-      </c>
-      <c r="AY251" s="5" t="n">
+      <c r="AZ251" s="5" t="n">
         <v>2760</v>
       </c>
-      <c r="AZ251" s="5" t="n">
+      <c r="BA251" s="5" t="n">
         <v>16830</v>
-      </c>
-      <c r="BA251" s="5" t="n">
-        <v>15790</v>
       </c>
       <c r="BB251" s="5" t="n">
         <v>5910</v>
@@ -68345,19 +68345,19 @@
         <v>96</v>
       </c>
       <c r="AW252" s="5" t="n">
+        <v>4630</v>
+      </c>
+      <c r="AX252" s="5" t="n">
+        <v>9440</v>
+      </c>
+      <c r="AY252" s="5" t="n">
         <v>7030</v>
       </c>
-      <c r="AX252" s="5" t="n">
-        <v>4630</v>
-      </c>
-      <c r="AY252" s="5" t="n">
+      <c r="AZ252" s="5" t="n">
         <v>3050</v>
       </c>
-      <c r="AZ252" s="5" t="n">
+      <c r="BA252" s="5" t="n">
         <v>14350</v>
-      </c>
-      <c r="BA252" s="5" t="n">
-        <v>9440</v>
       </c>
       <c r="BB252" s="5" t="n">
         <v>6270</v>
@@ -68606,19 +68606,19 @@
         <v>96</v>
       </c>
       <c r="AW253" s="5" t="n">
+        <v>5270</v>
+      </c>
+      <c r="AX253" s="5" t="n">
+        <v>11180</v>
+      </c>
+      <c r="AY253" s="5" t="n">
         <v>8660</v>
       </c>
-      <c r="AX253" s="5" t="n">
-        <v>5270</v>
-      </c>
-      <c r="AY253" s="5" t="n">
+      <c r="AZ253" s="5" t="n">
         <v>3390</v>
       </c>
-      <c r="AZ253" s="5" t="n">
+      <c r="BA253" s="5" t="n">
         <v>18200</v>
-      </c>
-      <c r="BA253" s="5" t="n">
-        <v>11180</v>
       </c>
       <c r="BB253" s="5" t="n">
         <v>7250</v>
@@ -68867,19 +68867,19 @@
         <v>96</v>
       </c>
       <c r="AW254" s="5" t="n">
+        <v>4070</v>
+      </c>
+      <c r="AX254" s="5" t="n">
+        <v>7430</v>
+      </c>
+      <c r="AY254" s="5" t="n">
         <v>6890</v>
       </c>
-      <c r="AX254" s="5" t="n">
-        <v>4070</v>
-      </c>
-      <c r="AY254" s="5" t="n">
+      <c r="AZ254" s="5" t="n">
         <v>2940</v>
       </c>
-      <c r="AZ254" s="5" t="n">
+      <c r="BA254" s="5" t="n">
         <v>12610</v>
-      </c>
-      <c r="BA254" s="5" t="n">
-        <v>7430</v>
       </c>
       <c r="BB254" s="5" t="n">
         <v>5520</v>
@@ -69128,19 +69128,19 @@
         <v>96</v>
       </c>
       <c r="AW255" s="5" t="n">
+        <v>4700</v>
+      </c>
+      <c r="AX255" s="5" t="n">
+        <v>9260</v>
+      </c>
+      <c r="AY255" s="5" t="n">
         <v>7720</v>
       </c>
-      <c r="AX255" s="5" t="n">
-        <v>4700</v>
-      </c>
-      <c r="AY255" s="5" t="n">
+      <c r="AZ255" s="5" t="n">
         <v>3150</v>
       </c>
-      <c r="AZ255" s="5" t="n">
+      <c r="BA255" s="5" t="n">
         <v>15540</v>
-      </c>
-      <c r="BA255" s="5" t="n">
-        <v>9260</v>
       </c>
       <c r="BB255" s="5" t="n">
         <v>6260</v>
@@ -69389,19 +69389,19 @@
         <v>96</v>
       </c>
       <c r="AW256" s="5" t="n">
+        <v>5300</v>
+      </c>
+      <c r="AX256" s="5" t="n">
+        <v>12160</v>
+      </c>
+      <c r="AY256" s="5" t="n">
         <v>9130</v>
       </c>
-      <c r="AX256" s="5" t="n">
-        <v>5300</v>
-      </c>
-      <c r="AY256" s="5" t="n">
+      <c r="AZ256" s="5" t="n">
         <v>3780</v>
       </c>
-      <c r="AZ256" s="5" t="n">
+      <c r="BA256" s="5" t="n">
         <v>21030</v>
-      </c>
-      <c r="BA256" s="5" t="n">
-        <v>12160</v>
       </c>
       <c r="BB256" s="5" t="n">
         <v>8750</v>
@@ -69650,19 +69650,19 @@
         <v>92</v>
       </c>
       <c r="AW257" s="5" t="n">
+        <v>12180</v>
+      </c>
+      <c r="AX257" s="5" t="n">
+        <v>21720</v>
+      </c>
+      <c r="AY257" s="5" t="n">
         <v>10390</v>
       </c>
-      <c r="AX257" s="5" t="n">
-        <v>12180</v>
-      </c>
-      <c r="AY257" s="5" t="n">
+      <c r="AZ257" s="5" t="n">
         <v>4290</v>
       </c>
-      <c r="AZ257" s="5" t="n">
+      <c r="BA257" s="5" t="n">
         <v>20580</v>
-      </c>
-      <c r="BA257" s="5" t="n">
-        <v>21720</v>
       </c>
       <c r="BB257" s="5" t="n">
         <v>8470</v>
@@ -69911,19 +69911,19 @@
         <v>92</v>
       </c>
       <c r="AW258" s="5" t="n">
+        <v>6480</v>
+      </c>
+      <c r="AX258" s="5" t="n">
+        <v>10430</v>
+      </c>
+      <c r="AY258" s="5" t="n">
         <v>6060</v>
       </c>
-      <c r="AX258" s="5" t="n">
-        <v>6480</v>
-      </c>
-      <c r="AY258" s="5" t="n">
+      <c r="AZ258" s="5" t="n">
         <v>2870</v>
       </c>
-      <c r="AZ258" s="5" t="n">
+      <c r="BA258" s="5" t="n">
         <v>9780</v>
-      </c>
-      <c r="BA258" s="5" t="n">
-        <v>10430</v>
       </c>
       <c r="BB258" s="5" t="n">
         <v>4790</v>
@@ -70121,7 +70121,7 @@
         <v>0.35</v>
       </c>
       <c r="AF259" s="5" t="n">
-        <v>9320</v>
+        <v>9300</v>
       </c>
       <c r="AG259" s="5" t="n">
         <v>1598</v>
@@ -70172,19 +70172,19 @@
         <v>92</v>
       </c>
       <c r="AW259" s="5" t="n">
+        <v>6890</v>
+      </c>
+      <c r="AX259" s="5" t="n">
+        <v>12280</v>
+      </c>
+      <c r="AY259" s="5" t="n">
         <v>6990</v>
       </c>
-      <c r="AX259" s="5" t="n">
-        <v>6890</v>
-      </c>
-      <c r="AY259" s="5" t="n">
+      <c r="AZ259" s="5" t="n">
         <v>2990</v>
       </c>
-      <c r="AZ259" s="5" t="n">
+      <c r="BA259" s="5" t="n">
         <v>13450</v>
-      </c>
-      <c r="BA259" s="5" t="n">
-        <v>12280</v>
       </c>
       <c r="BB259" s="5" t="n">
         <v>5730</v>
@@ -70433,19 +70433,19 @@
         <v>96</v>
       </c>
       <c r="AW260" s="5" t="n">
+        <v>16170</v>
+      </c>
+      <c r="AX260" s="5" t="n">
+        <v>32630</v>
+      </c>
+      <c r="AY260" s="5" t="n">
         <v>21070</v>
       </c>
-      <c r="AX260" s="5" t="n">
-        <v>16170</v>
-      </c>
-      <c r="AY260" s="5" t="n">
+      <c r="AZ260" s="5" t="n">
         <v>9530</v>
       </c>
-      <c r="AZ260" s="5" t="n">
+      <c r="BA260" s="5" t="n">
         <v>40460</v>
-      </c>
-      <c r="BA260" s="5" t="n">
-        <v>32630</v>
       </c>
       <c r="BB260" s="5" t="n">
         <v>18300</v>
@@ -70643,7 +70643,7 @@
         <v>0.25</v>
       </c>
       <c r="AF261" s="5" t="n">
-        <v>10050</v>
+        <v>10060</v>
       </c>
       <c r="AG261" s="5" t="n">
         <v>1667</v>
@@ -70694,19 +70694,19 @@
         <v>105</v>
       </c>
       <c r="AW261" s="5" t="n">
+        <v>5770</v>
+      </c>
+      <c r="AX261" s="5" t="n">
+        <v>11890</v>
+      </c>
+      <c r="AY261" s="5" t="n">
         <v>8630</v>
       </c>
-      <c r="AX261" s="5" t="n">
-        <v>5770</v>
-      </c>
-      <c r="AY261" s="5" t="n">
+      <c r="AZ261" s="5" t="n">
         <v>3910</v>
       </c>
-      <c r="AZ261" s="5" t="n">
+      <c r="BA261" s="5" t="n">
         <v>17820</v>
-      </c>
-      <c r="BA261" s="5" t="n">
-        <v>11890</v>
       </c>
       <c r="BB261" s="5" t="n">
         <v>8160</v>
@@ -70955,19 +70955,19 @@
         <v>105</v>
       </c>
       <c r="AW262" s="5" t="n">
+        <v>4240</v>
+      </c>
+      <c r="AX262" s="5" t="n">
+        <v>6970</v>
+      </c>
+      <c r="AY262" s="5" t="n">
         <v>5020</v>
       </c>
-      <c r="AX262" s="5" t="n">
-        <v>4240</v>
-      </c>
-      <c r="AY262" s="5" t="n">
+      <c r="AZ262" s="5" t="n">
         <v>2180</v>
       </c>
-      <c r="AZ262" s="5" t="n">
+      <c r="BA262" s="5" t="n">
         <v>8610</v>
-      </c>
-      <c r="BA262" s="5" t="n">
-        <v>6970</v>
       </c>
       <c r="BB262" s="5" t="n">
         <v>3910</v>
@@ -71165,7 +71165,7 @@
         <v>0.36</v>
       </c>
       <c r="AF263" s="5" t="n">
-        <v>7890</v>
+        <v>7900</v>
       </c>
       <c r="AG263" s="5" t="n">
         <v>3166</v>
@@ -71216,19 +71216,19 @@
         <v>92</v>
       </c>
       <c r="AW263" s="5" t="n">
+        <v>3790</v>
+      </c>
+      <c r="AX263" s="5" t="n">
+        <v>6910</v>
+      </c>
+      <c r="AY263" s="5" t="n">
         <v>4880</v>
       </c>
-      <c r="AX263" s="5" t="n">
-        <v>3790</v>
-      </c>
-      <c r="AY263" s="5" t="n">
+      <c r="AZ263" s="5" t="n">
         <v>2210</v>
       </c>
-      <c r="AZ263" s="5" t="n">
+      <c r="BA263" s="5" t="n">
         <v>9290</v>
-      </c>
-      <c r="BA263" s="5" t="n">
-        <v>6910</v>
       </c>
       <c r="BB263" s="5" t="n">
         <v>4280</v>
@@ -71477,19 +71477,19 @@
         <v>92</v>
       </c>
       <c r="AW264" s="5" t="n">
+        <v>9610</v>
+      </c>
+      <c r="AX264" s="5" t="n">
+        <v>18320</v>
+      </c>
+      <c r="AY264" s="5" t="n">
         <v>11400</v>
       </c>
-      <c r="AX264" s="5" t="n">
-        <v>9610</v>
-      </c>
-      <c r="AY264" s="5" t="n">
+      <c r="AZ264" s="5" t="n">
         <v>4910</v>
       </c>
-      <c r="AZ264" s="5" t="n">
+      <c r="BA264" s="5" t="n">
         <v>21710</v>
-      </c>
-      <c r="BA264" s="5" t="n">
-        <v>18320</v>
       </c>
       <c r="BB264" s="5" t="n">
         <v>9640</v>
@@ -71738,19 +71738,19 @@
         <v>96</v>
       </c>
       <c r="AW265" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="AX265" s="5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AY265" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="AX265" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="AY265" s="5" t="n">
+      <c r="AZ265" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="AZ265" s="5" t="n">
+      <c r="BA265" s="5" t="n">
         <v>360</v>
-      </c>
-      <c r="BA265" s="5" t="n">
-        <v>970</v>
       </c>
       <c r="BB265" s="5" t="n">
         <v>220</v>
@@ -71999,19 +71999,19 @@
         <v>96</v>
       </c>
       <c r="AW266" s="5" t="n">
+        <v>17320</v>
+      </c>
+      <c r="AX266" s="5" t="n">
+        <v>29250</v>
+      </c>
+      <c r="AY266" s="5" t="n">
         <v>31040</v>
       </c>
-      <c r="AX266" s="5" t="n">
-        <v>17320</v>
-      </c>
-      <c r="AY266" s="5" t="n">
+      <c r="AZ266" s="5" t="n">
         <v>10750</v>
       </c>
-      <c r="AZ266" s="5" t="n">
+      <c r="BA266" s="5" t="n">
         <v>54080</v>
-      </c>
-      <c r="BA266" s="5" t="n">
-        <v>29250</v>
       </c>
       <c r="BB266" s="5" t="n">
         <v>18660</v>
@@ -72260,19 +72260,19 @@
         <v>96</v>
       </c>
       <c r="AW267" s="5" t="n">
+        <v>17920</v>
+      </c>
+      <c r="AX267" s="5" t="n">
+        <v>26180</v>
+      </c>
+      <c r="AY267" s="5" t="n">
         <v>31170</v>
       </c>
-      <c r="AX267" s="5" t="n">
-        <v>17920</v>
-      </c>
-      <c r="AY267" s="5" t="n">
+      <c r="AZ267" s="5" t="n">
         <v>12030</v>
       </c>
-      <c r="AZ267" s="5" t="n">
+      <c r="BA267" s="5" t="n">
         <v>46670</v>
-      </c>
-      <c r="BA267" s="5" t="n">
-        <v>26180</v>
       </c>
       <c r="BB267" s="5" t="n">
         <v>17970</v>
@@ -72521,19 +72521,19 @@
         <v>96</v>
       </c>
       <c r="AW268" s="5" t="n">
+        <v>3920</v>
+      </c>
+      <c r="AX268" s="5" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AY268" s="5" t="n">
         <v>6680</v>
       </c>
-      <c r="AX268" s="5" t="n">
-        <v>3920</v>
-      </c>
-      <c r="AY268" s="5" t="n">
+      <c r="AZ268" s="5" t="n">
         <v>2720</v>
       </c>
-      <c r="AZ268" s="5" t="n">
+      <c r="BA268" s="5" t="n">
         <v>14060</v>
-      </c>
-      <c r="BA268" s="5" t="n">
-        <v>8200</v>
       </c>
       <c r="BB268" s="5" t="n">
         <v>5730</v>
@@ -72782,19 +72782,19 @@
         <v>96</v>
       </c>
       <c r="AW269" s="5" t="n">
+        <v>17830</v>
+      </c>
+      <c r="AX269" s="5" t="n">
+        <v>29390</v>
+      </c>
+      <c r="AY269" s="5" t="n">
         <v>30120</v>
       </c>
-      <c r="AX269" s="5" t="n">
-        <v>17830</v>
-      </c>
-      <c r="AY269" s="5" t="n">
+      <c r="AZ269" s="5" t="n">
         <v>10910</v>
       </c>
-      <c r="AZ269" s="5" t="n">
+      <c r="BA269" s="5" t="n">
         <v>51720</v>
-      </c>
-      <c r="BA269" s="5" t="n">
-        <v>29390</v>
       </c>
       <c r="BB269" s="5" t="n">
         <v>18580</v>
@@ -73043,19 +73043,19 @@
         <v>105</v>
       </c>
       <c r="AW270" s="5" t="n">
+        <v>9150</v>
+      </c>
+      <c r="AX270" s="5" t="n">
+        <v>15650</v>
+      </c>
+      <c r="AY270" s="5" t="n">
         <v>16570</v>
       </c>
-      <c r="AX270" s="5" t="n">
-        <v>9150</v>
-      </c>
-      <c r="AY270" s="5" t="n">
+      <c r="AZ270" s="5" t="n">
         <v>6840</v>
       </c>
-      <c r="AZ270" s="5" t="n">
+      <c r="BA270" s="5" t="n">
         <v>27400</v>
-      </c>
-      <c r="BA270" s="5" t="n">
-        <v>15650</v>
       </c>
       <c r="BB270" s="5" t="n">
         <v>11540</v>
@@ -73304,19 +73304,19 @@
         <v>96</v>
       </c>
       <c r="AW271" s="5" t="n">
+        <v>15970</v>
+      </c>
+      <c r="AX271" s="5" t="n">
+        <v>30610</v>
+      </c>
+      <c r="AY271" s="5" t="n">
         <v>19080</v>
       </c>
-      <c r="AX271" s="5" t="n">
-        <v>15970</v>
-      </c>
-      <c r="AY271" s="5" t="n">
+      <c r="AZ271" s="5" t="n">
         <v>8540</v>
       </c>
-      <c r="AZ271" s="5" t="n">
+      <c r="BA271" s="5" t="n">
         <v>32880</v>
-      </c>
-      <c r="BA271" s="5" t="n">
-        <v>30610</v>
       </c>
       <c r="BB271" s="5" t="n">
         <v>14490</v>
@@ -73514,7 +73514,7 @@
         <v>0.48</v>
       </c>
       <c r="AF272" s="5" t="n">
-        <v>4150</v>
+        <v>4160</v>
       </c>
       <c r="AG272" s="5" t="n">
         <v>1361</v>
@@ -73565,19 +73565,19 @@
         <v>96</v>
       </c>
       <c r="AW272" s="5" t="n">
+        <v>14780</v>
+      </c>
+      <c r="AX272" s="5" t="n">
+        <v>25190</v>
+      </c>
+      <c r="AY272" s="5" t="n">
         <v>22040</v>
       </c>
-      <c r="AX272" s="5" t="n">
-        <v>14780</v>
-      </c>
-      <c r="AY272" s="5" t="n">
+      <c r="AZ272" s="5" t="n">
         <v>9010</v>
       </c>
-      <c r="AZ272" s="5" t="n">
+      <c r="BA272" s="5" t="n">
         <v>38440</v>
-      </c>
-      <c r="BA272" s="5" t="n">
-        <v>25190</v>
       </c>
       <c r="BB272" s="5" t="n">
         <v>15820</v>
@@ -73826,19 +73826,19 @@
         <v>96</v>
       </c>
       <c r="AW273" s="5" t="n">
+        <v>10500</v>
+      </c>
+      <c r="AX273" s="5" t="n">
+        <v>18930</v>
+      </c>
+      <c r="AY273" s="5" t="n">
         <v>15230</v>
       </c>
-      <c r="AX273" s="5" t="n">
-        <v>10500</v>
-      </c>
-      <c r="AY273" s="5" t="n">
+      <c r="AZ273" s="5" t="n">
         <v>5640</v>
       </c>
-      <c r="AZ273" s="5" t="n">
+      <c r="BA273" s="5" t="n">
         <v>30010</v>
-      </c>
-      <c r="BA273" s="5" t="n">
-        <v>18930</v>
       </c>
       <c r="BB273" s="5" t="n">
         <v>11150</v>
@@ -74036,7 +74036,7 @@
         <v>0.54</v>
       </c>
       <c r="AF274" s="5" t="n">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="AG274" s="5" t="n">
         <v>726</v>
@@ -74087,19 +74087,19 @@
         <v>96</v>
       </c>
       <c r="AW274" s="5" t="n">
+        <v>6280</v>
+      </c>
+      <c r="AX274" s="5" t="n">
+        <v>14360</v>
+      </c>
+      <c r="AY274" s="5" t="n">
         <v>11400</v>
       </c>
-      <c r="AX274" s="5" t="n">
-        <v>6280</v>
-      </c>
-      <c r="AY274" s="5" t="n">
+      <c r="AZ274" s="5" t="n">
         <v>4230</v>
       </c>
-      <c r="AZ274" s="5" t="n">
+      <c r="BA274" s="5" t="n">
         <v>26440</v>
-      </c>
-      <c r="BA274" s="5" t="n">
-        <v>14360</v>
       </c>
       <c r="BB274" s="5" t="n">
         <v>9940</v>
@@ -74348,19 +74348,19 @@
         <v>96</v>
       </c>
       <c r="AW275" s="5" t="n">
+        <v>10110</v>
+      </c>
+      <c r="AX275" s="5" t="n">
+        <v>20120</v>
+      </c>
+      <c r="AY275" s="5" t="n">
         <v>15050</v>
       </c>
-      <c r="AX275" s="5" t="n">
-        <v>10110</v>
-      </c>
-      <c r="AY275" s="5" t="n">
+      <c r="AZ275" s="5" t="n">
         <v>5730</v>
       </c>
-      <c r="AZ275" s="5" t="n">
+      <c r="BA275" s="5" t="n">
         <v>29680</v>
-      </c>
-      <c r="BA275" s="5" t="n">
-        <v>20120</v>
       </c>
       <c r="BB275" s="5" t="n">
         <v>11630</v>
@@ -74609,19 +74609,19 @@
         <v>96</v>
       </c>
       <c r="AW276" s="5" t="n">
+        <v>28700</v>
+      </c>
+      <c r="AX276" s="5" t="n">
+        <v>44210</v>
+      </c>
+      <c r="AY276" s="5" t="n">
         <v>40080</v>
       </c>
-      <c r="AX276" s="5" t="n">
-        <v>28700</v>
-      </c>
-      <c r="AY276" s="5" t="n">
+      <c r="AZ276" s="5" t="n">
         <v>16400</v>
       </c>
-      <c r="AZ276" s="5" t="n">
+      <c r="BA276" s="5" t="n">
         <v>61280</v>
-      </c>
-      <c r="BA276" s="5" t="n">
-        <v>44210</v>
       </c>
       <c r="BB276" s="5" t="n">
         <v>25180</v>
@@ -74870,19 +74870,19 @@
         <v>96</v>
       </c>
       <c r="AW277" s="5" t="n">
+        <v>38780</v>
+      </c>
+      <c r="AX277" s="5" t="n">
+        <v>47440</v>
+      </c>
+      <c r="AY277" s="5" t="n">
         <v>48910</v>
       </c>
-      <c r="AX277" s="5" t="n">
-        <v>38780</v>
-      </c>
-      <c r="AY277" s="5" t="n">
+      <c r="AZ277" s="5" t="n">
         <v>22650</v>
       </c>
-      <c r="AZ277" s="5" t="n">
+      <c r="BA277" s="5" t="n">
         <v>60980</v>
-      </c>
-      <c r="BA277" s="5" t="n">
-        <v>47440</v>
       </c>
       <c r="BB277" s="5" t="n">
         <v>28010</v>
@@ -75131,19 +75131,19 @@
         <v>96</v>
       </c>
       <c r="AW278" s="5" t="n">
+        <v>21020</v>
+      </c>
+      <c r="AX278" s="5" t="n">
+        <v>29490</v>
+      </c>
+      <c r="AY278" s="5" t="n">
         <v>35600</v>
       </c>
-      <c r="AX278" s="5" t="n">
-        <v>21020</v>
-      </c>
-      <c r="AY278" s="5" t="n">
+      <c r="AZ278" s="5" t="n">
         <v>14280</v>
       </c>
-      <c r="AZ278" s="5" t="n">
+      <c r="BA278" s="5" t="n">
         <v>49750</v>
-      </c>
-      <c r="BA278" s="5" t="n">
-        <v>29490</v>
       </c>
       <c r="BB278" s="5" t="n">
         <v>19960</v>
@@ -75392,19 +75392,19 @@
         <v>96</v>
       </c>
       <c r="AW279" s="5" t="n">
+        <v>11070</v>
+      </c>
+      <c r="AX279" s="5" t="n">
+        <v>17830</v>
+      </c>
+      <c r="AY279" s="5" t="n">
         <v>23120</v>
       </c>
-      <c r="AX279" s="5" t="n">
-        <v>11070</v>
-      </c>
-      <c r="AY279" s="5" t="n">
+      <c r="AZ279" s="5" t="n">
         <v>8100</v>
       </c>
-      <c r="AZ279" s="5" t="n">
+      <c r="BA279" s="5" t="n">
         <v>36500</v>
-      </c>
-      <c r="BA279" s="5" t="n">
-        <v>17830</v>
       </c>
       <c r="BB279" s="5" t="n">
         <v>12870</v>
@@ -75653,19 +75653,19 @@
         <v>105</v>
       </c>
       <c r="AW280" s="5" t="n">
+        <v>6690</v>
+      </c>
+      <c r="AX280" s="5" t="n">
+        <v>11430</v>
+      </c>
+      <c r="AY280" s="5" t="n">
         <v>12510</v>
       </c>
-      <c r="AX280" s="5" t="n">
-        <v>6690</v>
-      </c>
-      <c r="AY280" s="5" t="n">
+      <c r="AZ280" s="5" t="n">
         <v>4940</v>
       </c>
-      <c r="AZ280" s="5" t="n">
+      <c r="BA280" s="5" t="n">
         <v>21230</v>
-      </c>
-      <c r="BA280" s="5" t="n">
-        <v>11430</v>
       </c>
       <c r="BB280" s="5" t="n">
         <v>8450</v>
@@ -75914,19 +75914,19 @@
         <v>96</v>
       </c>
       <c r="AW281" s="5" t="n">
+        <v>12390</v>
+      </c>
+      <c r="AX281" s="5" t="n">
+        <v>21390</v>
+      </c>
+      <c r="AY281" s="5" t="n">
         <v>24480</v>
       </c>
-      <c r="AX281" s="5" t="n">
-        <v>12390</v>
-      </c>
-      <c r="AY281" s="5" t="n">
+      <c r="AZ281" s="5" t="n">
         <v>8780</v>
       </c>
-      <c r="AZ281" s="5" t="n">
+      <c r="BA281" s="5" t="n">
         <v>39400</v>
-      </c>
-      <c r="BA281" s="5" t="n">
-        <v>21390</v>
       </c>
       <c r="BB281" s="5" t="n">
         <v>14230</v>
@@ -76175,19 +76175,19 @@
         <v>96</v>
       </c>
       <c r="AW282" s="5" t="n">
+        <v>5930</v>
+      </c>
+      <c r="AX282" s="5" t="n">
+        <v>13910</v>
+      </c>
+      <c r="AY282" s="5" t="n">
         <v>9900</v>
       </c>
-      <c r="AX282" s="5" t="n">
-        <v>5930</v>
-      </c>
-      <c r="AY282" s="5" t="n">
+      <c r="AZ282" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="AZ282" s="5" t="n">
+      <c r="BA282" s="5" t="n">
         <v>23850</v>
-      </c>
-      <c r="BA282" s="5" t="n">
-        <v>13910</v>
       </c>
       <c r="BB282" s="5" t="n">
         <v>9270</v>
@@ -76436,19 +76436,19 @@
         <v>96</v>
       </c>
       <c r="AW283" s="5" t="n">
+        <v>13250</v>
+      </c>
+      <c r="AX283" s="5" t="n">
+        <v>25930</v>
+      </c>
+      <c r="AY283" s="5" t="n">
         <v>17100</v>
       </c>
-      <c r="AX283" s="5" t="n">
-        <v>13250</v>
-      </c>
-      <c r="AY283" s="5" t="n">
+      <c r="AZ283" s="5" t="n">
         <v>7720</v>
       </c>
-      <c r="AZ283" s="5" t="n">
+      <c r="BA283" s="5" t="n">
         <v>34230</v>
-      </c>
-      <c r="BA283" s="5" t="n">
-        <v>25930</v>
       </c>
       <c r="BB283" s="5" t="n">
         <v>15500</v>
@@ -76697,19 +76697,19 @@
         <v>96</v>
       </c>
       <c r="AW284" s="5" t="n">
+        <v>66130</v>
+      </c>
+      <c r="AX284" s="5" t="n">
+        <v>78830</v>
+      </c>
+      <c r="AY284" s="5" t="n">
         <v>69900</v>
       </c>
-      <c r="AX284" s="5" t="n">
-        <v>66130</v>
-      </c>
-      <c r="AY284" s="5" t="n">
+      <c r="AZ284" s="5" t="n">
         <v>33670</v>
       </c>
-      <c r="AZ284" s="5" t="n">
+      <c r="BA284" s="5" t="n">
         <v>84660</v>
-      </c>
-      <c r="BA284" s="5" t="n">
-        <v>78830</v>
       </c>
       <c r="BB284" s="5" t="n">
         <v>40330</v>
@@ -76958,19 +76958,19 @@
         <v>96</v>
       </c>
       <c r="AW285" s="5" t="n">
+        <v>3750</v>
+      </c>
+      <c r="AX285" s="5" t="n">
+        <v>9940</v>
+      </c>
+      <c r="AY285" s="5" t="n">
         <v>5270</v>
       </c>
-      <c r="AX285" s="5" t="n">
-        <v>3750</v>
-      </c>
-      <c r="AY285" s="5" t="n">
+      <c r="AZ285" s="5" t="n">
         <v>2110</v>
       </c>
-      <c r="AZ285" s="5" t="n">
+      <c r="BA285" s="5" t="n">
         <v>14960</v>
-      </c>
-      <c r="BA285" s="5" t="n">
-        <v>9940</v>
       </c>
       <c r="BB285" s="5" t="n">
         <v>6240</v>
@@ -77219,19 +77219,19 @@
         <v>96</v>
       </c>
       <c r="AW286" s="5" t="n">
+        <v>9090</v>
+      </c>
+      <c r="AX286" s="5" t="n">
+        <v>18070</v>
+      </c>
+      <c r="AY286" s="5" t="n">
         <v>13600</v>
       </c>
-      <c r="AX286" s="5" t="n">
-        <v>9090</v>
-      </c>
-      <c r="AY286" s="5" t="n">
+      <c r="AZ286" s="5" t="n">
         <v>5980</v>
       </c>
-      <c r="AZ286" s="5" t="n">
+      <c r="BA286" s="5" t="n">
         <v>26860</v>
-      </c>
-      <c r="BA286" s="5" t="n">
-        <v>18070</v>
       </c>
       <c r="BB286" s="5" t="n">
         <v>11970</v>
@@ -77480,19 +77480,19 @@
         <v>96</v>
       </c>
       <c r="AW287" s="5" t="n">
+        <v>12770</v>
+      </c>
+      <c r="AX287" s="5" t="n">
+        <v>22870</v>
+      </c>
+      <c r="AY287" s="5" t="n">
         <v>18420</v>
       </c>
-      <c r="AX287" s="5" t="n">
-        <v>12770</v>
-      </c>
-      <c r="AY287" s="5" t="n">
+      <c r="AZ287" s="5" t="n">
         <v>7510</v>
       </c>
-      <c r="AZ287" s="5" t="n">
+      <c r="BA287" s="5" t="n">
         <v>35280</v>
-      </c>
-      <c r="BA287" s="5" t="n">
-        <v>22870</v>
       </c>
       <c r="BB287" s="5" t="n">
         <v>14540</v>
@@ -77741,19 +77741,19 @@
         <v>105</v>
       </c>
       <c r="AW288" s="5" t="n">
+        <v>5660</v>
+      </c>
+      <c r="AX288" s="5" t="n">
+        <v>13900</v>
+      </c>
+      <c r="AY288" s="5" t="n">
         <v>9230</v>
       </c>
-      <c r="AX288" s="5" t="n">
-        <v>5660</v>
-      </c>
-      <c r="AY288" s="5" t="n">
+      <c r="AZ288" s="5" t="n">
         <v>3500</v>
       </c>
-      <c r="AZ288" s="5" t="n">
+      <c r="BA288" s="5" t="n">
         <v>22680</v>
-      </c>
-      <c r="BA288" s="5" t="n">
-        <v>13900</v>
       </c>
       <c r="BB288" s="5" t="n">
         <v>8940</v>
@@ -78002,19 +78002,19 @@
         <v>96</v>
       </c>
       <c r="AW289" s="5" t="n">
+        <v>4920</v>
+      </c>
+      <c r="AX289" s="5" t="n">
+        <v>11860</v>
+      </c>
+      <c r="AY289" s="5" t="n">
         <v>6190</v>
       </c>
-      <c r="AX289" s="5" t="n">
-        <v>4920</v>
-      </c>
-      <c r="AY289" s="5" t="n">
+      <c r="AZ289" s="5" t="n">
         <v>2290</v>
       </c>
-      <c r="AZ289" s="5" t="n">
+      <c r="BA289" s="5" t="n">
         <v>17020</v>
-      </c>
-      <c r="BA289" s="5" t="n">
-        <v>11860</v>
       </c>
       <c r="BB289" s="5" t="n">
         <v>5930</v>
@@ -78263,19 +78263,19 @@
         <v>105</v>
       </c>
       <c r="AW290" s="5" t="n">
+        <v>5430</v>
+      </c>
+      <c r="AX290" s="5" t="n">
+        <v>9950</v>
+      </c>
+      <c r="AY290" s="5" t="n">
         <v>10720</v>
       </c>
-      <c r="AX290" s="5" t="n">
-        <v>5430</v>
-      </c>
-      <c r="AY290" s="5" t="n">
+      <c r="AZ290" s="5" t="n">
         <v>3890</v>
       </c>
-      <c r="AZ290" s="5" t="n">
+      <c r="BA290" s="5" t="n">
         <v>20090</v>
-      </c>
-      <c r="BA290" s="5" t="n">
-        <v>9950</v>
       </c>
       <c r="BB290" s="5" t="n">
         <v>7210</v>
@@ -78473,7 +78473,7 @@
         <v>0.61</v>
       </c>
       <c r="AF291" s="5" t="n">
-        <v>2320</v>
+        <v>2310</v>
       </c>
       <c r="AG291" s="5" t="n">
         <v>1436</v>
@@ -78524,19 +78524,19 @@
         <v>92</v>
       </c>
       <c r="AW291" s="5" t="n">
+        <v>4420</v>
+      </c>
+      <c r="AX291" s="5" t="n">
+        <v>9230</v>
+      </c>
+      <c r="AY291" s="5" t="n">
         <v>6080</v>
       </c>
-      <c r="AX291" s="5" t="n">
-        <v>4420</v>
-      </c>
-      <c r="AY291" s="5" t="n">
+      <c r="AZ291" s="5" t="n">
         <v>2740</v>
       </c>
-      <c r="AZ291" s="5" t="n">
+      <c r="BA291" s="5" t="n">
         <v>14170</v>
-      </c>
-      <c r="BA291" s="5" t="n">
-        <v>9230</v>
       </c>
       <c r="BB291" s="5" t="n">
         <v>6290</v>
@@ -78785,19 +78785,19 @@
         <v>96</v>
       </c>
       <c r="AW292" s="5" t="n">
+        <v>10540</v>
+      </c>
+      <c r="AX292" s="5" t="n">
+        <v>23870</v>
+      </c>
+      <c r="AY292" s="5" t="n">
         <v>13960</v>
       </c>
-      <c r="AX292" s="5" t="n">
-        <v>10540</v>
-      </c>
-      <c r="AY292" s="5" t="n">
+      <c r="AZ292" s="5" t="n">
         <v>6120</v>
       </c>
-      <c r="AZ292" s="5" t="n">
+      <c r="BA292" s="5" t="n">
         <v>31690</v>
-      </c>
-      <c r="BA292" s="5" t="n">
-        <v>23870</v>
       </c>
       <c r="BB292" s="5" t="n">
         <v>13940</v>
@@ -79046,19 +79046,19 @@
         <v>96</v>
       </c>
       <c r="AW293" s="5" t="n">
+        <v>4430</v>
+      </c>
+      <c r="AX293" s="5" t="n">
+        <v>9410</v>
+      </c>
+      <c r="AY293" s="5" t="n">
         <v>7980</v>
       </c>
-      <c r="AX293" s="5" t="n">
-        <v>4430</v>
-      </c>
-      <c r="AY293" s="5" t="n">
+      <c r="AZ293" s="5" t="n">
         <v>3290</v>
       </c>
-      <c r="AZ293" s="5" t="n">
+      <c r="BA293" s="5" t="n">
         <v>17350</v>
-      </c>
-      <c r="BA293" s="5" t="n">
-        <v>9410</v>
       </c>
       <c r="BB293" s="5" t="n">
         <v>7080</v>
@@ -79307,19 +79307,19 @@
         <v>96</v>
       </c>
       <c r="AW294" s="5" t="n">
+        <v>8550</v>
+      </c>
+      <c r="AX294" s="5" t="n">
+        <v>20330</v>
+      </c>
+      <c r="AY294" s="5" t="n">
         <v>9490</v>
       </c>
-      <c r="AX294" s="5" t="n">
-        <v>8550</v>
-      </c>
-      <c r="AY294" s="5" t="n">
+      <c r="AZ294" s="5" t="n">
         <v>3870</v>
       </c>
-      <c r="AZ294" s="5" t="n">
+      <c r="BA294" s="5" t="n">
         <v>24740</v>
-      </c>
-      <c r="BA294" s="5" t="n">
-        <v>20330</v>
       </c>
       <c r="BB294" s="5" t="n">
         <v>9730</v>
@@ -79568,19 +79568,19 @@
         <v>96</v>
       </c>
       <c r="AW295" s="5" t="n">
+        <v>7800</v>
+      </c>
+      <c r="AX295" s="5" t="n">
+        <v>15340</v>
+      </c>
+      <c r="AY295" s="5" t="n">
         <v>14010</v>
       </c>
-      <c r="AX295" s="5" t="n">
-        <v>7800</v>
-      </c>
-      <c r="AY295" s="5" t="n">
+      <c r="AZ295" s="5" t="n">
         <v>5160</v>
       </c>
-      <c r="AZ295" s="5" t="n">
+      <c r="BA295" s="5" t="n">
         <v>27510</v>
-      </c>
-      <c r="BA295" s="5" t="n">
-        <v>15340</v>
       </c>
       <c r="BB295" s="5" t="n">
         <v>10150</v>
@@ -79829,19 +79829,19 @@
         <v>96</v>
       </c>
       <c r="AW296" s="5" t="n">
+        <v>11870</v>
+      </c>
+      <c r="AX296" s="5" t="n">
+        <v>26130</v>
+      </c>
+      <c r="AY296" s="5" t="n">
         <v>17630</v>
       </c>
-      <c r="AX296" s="5" t="n">
-        <v>11870</v>
-      </c>
-      <c r="AY296" s="5" t="n">
+      <c r="AZ296" s="5" t="n">
         <v>7770</v>
       </c>
-      <c r="AZ296" s="5" t="n">
+      <c r="BA296" s="5" t="n">
         <v>39500</v>
-      </c>
-      <c r="BA296" s="5" t="n">
-        <v>26130</v>
       </c>
       <c r="BB296" s="5" t="n">
         <v>16950</v>
@@ -80090,19 +80090,19 @@
         <v>96</v>
       </c>
       <c r="AW297" s="5" t="n">
+        <v>16480</v>
+      </c>
+      <c r="AX297" s="5" t="n">
+        <v>27420</v>
+      </c>
+      <c r="AY297" s="5" t="n">
         <v>13840</v>
       </c>
-      <c r="AX297" s="5" t="n">
-        <v>16480</v>
-      </c>
-      <c r="AY297" s="5" t="n">
+      <c r="AZ297" s="5" t="n">
         <v>6590</v>
       </c>
-      <c r="AZ297" s="5" t="n">
+      <c r="BA297" s="5" t="n">
         <v>24320</v>
-      </c>
-      <c r="BA297" s="5" t="n">
-        <v>27420</v>
       </c>
       <c r="BB297" s="5" t="n">
         <v>11450</v>
@@ -80333,19 +80333,19 @@
       <c r="AU298" s="5"/>
       <c r="AV298" s="5"/>
       <c r="AW298" s="5" t="n">
+        <v>1950</v>
+      </c>
+      <c r="AX298" s="5" t="n">
+        <v>2930</v>
+      </c>
+      <c r="AY298" s="5" t="n">
         <v>1710</v>
       </c>
-      <c r="AX298" s="5" t="n">
-        <v>1950</v>
-      </c>
-      <c r="AY298" s="5" t="n">
+      <c r="AZ298" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="AZ298" s="5" t="n">
+      <c r="BA298" s="5" t="n">
         <v>2590</v>
-      </c>
-      <c r="BA298" s="5" t="n">
-        <v>2930</v>
       </c>
       <c r="BB298" s="5" t="n">
         <v>1110</v>
@@ -80511,7 +80511,7 @@
         <v>0.41</v>
       </c>
       <c r="AF299" s="5" t="n">
-        <v>6710</v>
+        <v>6720</v>
       </c>
       <c r="AG299" s="5" t="n">
         <v>2561</v>
@@ -80554,19 +80554,19 @@
       <c r="AU299" s="5"/>
       <c r="AV299" s="5"/>
       <c r="AW299" s="5" t="n">
+        <v>4860</v>
+      </c>
+      <c r="AX299" s="5" t="n">
+        <v>7140</v>
+      </c>
+      <c r="AY299" s="5" t="n">
         <v>4040</v>
       </c>
-      <c r="AX299" s="5" t="n">
-        <v>4860</v>
-      </c>
-      <c r="AY299" s="5" t="n">
+      <c r="AZ299" s="5" t="n">
         <v>1670</v>
       </c>
-      <c r="AZ299" s="5" t="n">
+      <c r="BA299" s="5" t="n">
         <v>6600</v>
-      </c>
-      <c r="BA299" s="5" t="n">
-        <v>7140</v>
       </c>
       <c r="BB299" s="5" t="n">
         <v>2730</v>
@@ -80732,7 +80732,7 @@
         <v>0.34</v>
       </c>
       <c r="AF300" s="5" t="n">
-        <v>4390</v>
+        <v>4400</v>
       </c>
       <c r="AG300" s="5" t="n">
         <v>1131</v>
@@ -80775,19 +80775,19 @@
       <c r="AU300" s="5"/>
       <c r="AV300" s="5"/>
       <c r="AW300" s="5" t="n">
+        <v>1930</v>
+      </c>
+      <c r="AX300" s="5" t="n">
+        <v>2770</v>
+      </c>
+      <c r="AY300" s="5" t="n">
         <v>1840</v>
       </c>
-      <c r="AX300" s="5" t="n">
-        <v>1930</v>
-      </c>
-      <c r="AY300" s="5" t="n">
+      <c r="AZ300" s="5" t="n">
         <v>790</v>
       </c>
-      <c r="AZ300" s="5" t="n">
+      <c r="BA300" s="5" t="n">
         <v>2870</v>
-      </c>
-      <c r="BA300" s="5" t="n">
-        <v>2770</v>
       </c>
       <c r="BB300" s="5" t="n">
         <v>1230</v>
@@ -80996,19 +80996,19 @@
       <c r="AU301" s="5"/>
       <c r="AV301" s="5"/>
       <c r="AW301" s="5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AX301" s="5" t="n">
+        <v>3520</v>
+      </c>
+      <c r="AY301" s="5" t="n">
         <v>2130</v>
       </c>
-      <c r="AX301" s="5" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AY301" s="5" t="n">
+      <c r="AZ301" s="5" t="n">
         <v>940</v>
       </c>
-      <c r="AZ301" s="5" t="n">
+      <c r="BA301" s="5" t="n">
         <v>2940</v>
-      </c>
-      <c r="BA301" s="5" t="n">
-        <v>3520</v>
       </c>
       <c r="BB301" s="5" t="n">
         <v>1290</v>
@@ -81220,16 +81220,16 @@
         <v>1910</v>
       </c>
       <c r="AX302" s="5" t="n">
+        <v>3270</v>
+      </c>
+      <c r="AY302" s="5" t="n">
         <v>1910</v>
       </c>
-      <c r="AY302" s="5" t="n">
+      <c r="AZ302" s="5" t="n">
         <v>830</v>
       </c>
-      <c r="AZ302" s="5" t="n">
+      <c r="BA302" s="5" t="n">
         <v>3730</v>
-      </c>
-      <c r="BA302" s="5" t="n">
-        <v>3270</v>
       </c>
       <c r="BB302" s="5" t="n">
         <v>1630</v>
@@ -81438,19 +81438,19 @@
       <c r="AU303" s="5"/>
       <c r="AV303" s="5"/>
       <c r="AW303" s="5" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AX303" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="AY303" s="5" t="n">
         <v>1300</v>
       </c>
-      <c r="AX303" s="5" t="n">
-        <v>1460</v>
-      </c>
-      <c r="AY303" s="5" t="n">
+      <c r="AZ303" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="AZ303" s="5" t="n">
+      <c r="BA303" s="5" t="n">
         <v>1880</v>
-      </c>
-      <c r="BA303" s="5" t="n">
-        <v>2010</v>
       </c>
       <c r="BB303" s="5" t="n">
         <v>730</v>
@@ -81616,7 +81616,7 @@
         <v>0.3</v>
       </c>
       <c r="AF304" s="5" t="n">
-        <v>5720</v>
+        <v>5710</v>
       </c>
       <c r="AG304" s="5" t="n">
         <v>4514</v>
@@ -81659,19 +81659,19 @@
       <c r="AU304" s="5"/>
       <c r="AV304" s="5"/>
       <c r="AW304" s="5" t="n">
+        <v>2740</v>
+      </c>
+      <c r="AX304" s="5" t="n">
+        <v>3860</v>
+      </c>
+      <c r="AY304" s="5" t="n">
         <v>2520</v>
       </c>
-      <c r="AX304" s="5" t="n">
-        <v>2740</v>
-      </c>
-      <c r="AY304" s="5" t="n">
+      <c r="AZ304" s="5" t="n">
         <v>1110</v>
       </c>
-      <c r="AZ304" s="5" t="n">
+      <c r="BA304" s="5" t="n">
         <v>3580</v>
-      </c>
-      <c r="BA304" s="5" t="n">
-        <v>3860</v>
       </c>
       <c r="BB304" s="5" t="n">
         <v>1610</v>
@@ -81880,19 +81880,19 @@
       <c r="AU305" s="5"/>
       <c r="AV305" s="5"/>
       <c r="AW305" s="5" t="n">
+        <v>3120</v>
+      </c>
+      <c r="AX305" s="5" t="n">
+        <v>3780</v>
+      </c>
+      <c r="AY305" s="5" t="n">
         <v>2550</v>
       </c>
-      <c r="AX305" s="5" t="n">
-        <v>3120</v>
-      </c>
-      <c r="AY305" s="5" t="n">
+      <c r="AZ305" s="5" t="n">
         <v>1040</v>
       </c>
-      <c r="AZ305" s="5" t="n">
+      <c r="BA305" s="5" t="n">
         <v>2980</v>
-      </c>
-      <c r="BA305" s="5" t="n">
-        <v>3780</v>
       </c>
       <c r="BB305" s="5" t="n">
         <v>1240</v>
@@ -82101,19 +82101,19 @@
       <c r="AU306" s="5"/>
       <c r="AV306" s="5"/>
       <c r="AW306" s="5" t="n">
+        <v>4090</v>
+      </c>
+      <c r="AX306" s="5" t="n">
+        <v>6390</v>
+      </c>
+      <c r="AY306" s="5" t="n">
         <v>4640</v>
       </c>
-      <c r="AX306" s="5" t="n">
-        <v>4090</v>
-      </c>
-      <c r="AY306" s="5" t="n">
+      <c r="AZ306" s="5" t="n">
         <v>1980</v>
       </c>
-      <c r="AZ306" s="5" t="n">
+      <c r="BA306" s="5" t="n">
         <v>7400</v>
-      </c>
-      <c r="BA306" s="5" t="n">
-        <v>6390</v>
       </c>
       <c r="BB306" s="5" t="n">
         <v>3260</v>
@@ -82279,7 +82279,7 @@
         <v>0.48</v>
       </c>
       <c r="AF307" s="5" t="n">
-        <v>6360</v>
+        <v>6350</v>
       </c>
       <c r="AG307" s="5" t="n">
         <v>1059</v>
@@ -82322,19 +82322,19 @@
       <c r="AU307" s="5"/>
       <c r="AV307" s="5"/>
       <c r="AW307" s="5" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AX307" s="5" t="n">
+        <v>2290</v>
+      </c>
+      <c r="AY307" s="5" t="n">
         <v>1510</v>
       </c>
-      <c r="AX307" s="5" t="n">
-        <v>1460</v>
-      </c>
-      <c r="AY307" s="5" t="n">
+      <c r="AZ307" s="5" t="n">
         <v>650</v>
       </c>
-      <c r="AZ307" s="5" t="n">
+      <c r="BA307" s="5" t="n">
         <v>2360</v>
-      </c>
-      <c r="BA307" s="5" t="n">
-        <v>2290</v>
       </c>
       <c r="BB307" s="5" t="n">
         <v>1050</v>
@@ -82500,7 +82500,7 @@
         <v>0.29</v>
       </c>
       <c r="AF308" s="5" t="n">
-        <v>4710</v>
+        <v>4720</v>
       </c>
       <c r="AG308" s="5" t="n">
         <v>593</v>
@@ -82543,19 +82543,19 @@
       <c r="AU308" s="5"/>
       <c r="AV308" s="5"/>
       <c r="AW308" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="AX308" s="5" t="n">
+        <v>6200</v>
+      </c>
+      <c r="AY308" s="5" t="n">
         <v>4130</v>
       </c>
-      <c r="AX308" s="5" t="n">
-        <v>3400</v>
-      </c>
-      <c r="AY308" s="5" t="n">
+      <c r="AZ308" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="AZ308" s="5" t="n">
+      <c r="BA308" s="5" t="n">
         <v>7630</v>
-      </c>
-      <c r="BA308" s="5" t="n">
-        <v>6200</v>
       </c>
       <c r="BB308" s="5" t="n">
         <v>3830</v>
@@ -82764,19 +82764,19 @@
       <c r="AU309" s="5"/>
       <c r="AV309" s="5"/>
       <c r="AW309" s="5" t="n">
+        <v>1830</v>
+      </c>
+      <c r="AX309" s="5" t="n">
+        <v>2750</v>
+      </c>
+      <c r="AY309" s="5" t="n">
         <v>2480</v>
       </c>
-      <c r="AX309" s="5" t="n">
-        <v>1830</v>
-      </c>
-      <c r="AY309" s="5" t="n">
+      <c r="AZ309" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="AZ309" s="5" t="n">
+      <c r="BA309" s="5" t="n">
         <v>3730</v>
-      </c>
-      <c r="BA309" s="5" t="n">
-        <v>2750</v>
       </c>
       <c r="BB309" s="5" t="n">
         <v>1670</v>
@@ -82985,19 +82985,19 @@
       <c r="AU310" s="5"/>
       <c r="AV310" s="5"/>
       <c r="AW310" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="AX310" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="AY310" s="5" t="n">
         <v>1040</v>
       </c>
-      <c r="AX310" s="5" t="n">
-        <v>1070</v>
-      </c>
-      <c r="AY310" s="5" t="n">
+      <c r="AZ310" s="5" t="n">
         <v>440</v>
       </c>
-      <c r="AZ310" s="5" t="n">
+      <c r="BA310" s="5" t="n">
         <v>1790</v>
-      </c>
-      <c r="BA310" s="5" t="n">
-        <v>1700</v>
       </c>
       <c r="BB310" s="5" t="n">
         <v>800</v>
@@ -83163,7 +83163,7 @@
         <v>0.42</v>
       </c>
       <c r="AF311" s="5" t="n">
-        <v>7220</v>
+        <v>7210</v>
       </c>
       <c r="AG311" s="5" t="n">
         <v>982</v>
@@ -83206,19 +83206,19 @@
       <c r="AU311" s="5"/>
       <c r="AV311" s="5"/>
       <c r="AW311" s="5" t="n">
+        <v>940</v>
+      </c>
+      <c r="AX311" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="AY311" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="AX311" s="5" t="n">
-        <v>940</v>
-      </c>
-      <c r="AY311" s="5" t="n">
+      <c r="AZ311" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="AZ311" s="5" t="n">
+      <c r="BA311" s="5" t="n">
         <v>3540</v>
-      </c>
-      <c r="BA311" s="5" t="n">
-        <v>3200</v>
       </c>
       <c r="BB311" s="5" t="n">
         <v>1620</v>
@@ -83427,19 +83427,19 @@
       <c r="AU312" s="5"/>
       <c r="AV312" s="5"/>
       <c r="AW312" s="5" t="n">
+        <v>3910</v>
+      </c>
+      <c r="AX312" s="5" t="n">
+        <v>6010</v>
+      </c>
+      <c r="AY312" s="5" t="n">
         <v>5270</v>
       </c>
-      <c r="AX312" s="5" t="n">
-        <v>3910</v>
-      </c>
-      <c r="AY312" s="5" t="n">
+      <c r="AZ312" s="5" t="n">
         <v>2370</v>
       </c>
-      <c r="AZ312" s="5" t="n">
+      <c r="BA312" s="5" t="n">
         <v>7860</v>
-      </c>
-      <c r="BA312" s="5" t="n">
-        <v>6010</v>
       </c>
       <c r="BB312" s="5" t="n">
         <v>3560</v>
@@ -83648,19 +83648,19 @@
       <c r="AU313" s="5"/>
       <c r="AV313" s="5"/>
       <c r="AW313" s="5" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AX313" s="5" t="n">
+        <v>2450</v>
+      </c>
+      <c r="AY313" s="5" t="n">
         <v>1320</v>
       </c>
-      <c r="AX313" s="5" t="n">
-        <v>1190</v>
-      </c>
-      <c r="AY313" s="5" t="n">
+      <c r="AZ313" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="AZ313" s="5" t="n">
+      <c r="BA313" s="5" t="n">
         <v>3210</v>
-      </c>
-      <c r="BA313" s="5" t="n">
-        <v>2450</v>
       </c>
       <c r="BB313" s="5" t="n">
         <v>1460</v>
@@ -83869,19 +83869,19 @@
       <c r="AU314" s="5"/>
       <c r="AV314" s="5"/>
       <c r="AW314" s="5" t="n">
+        <v>690</v>
+      </c>
+      <c r="AX314" s="5" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AY314" s="5" t="n">
         <v>740</v>
       </c>
-      <c r="AX314" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="AY314" s="5" t="n">
+      <c r="AZ314" s="5" t="n">
         <v>370</v>
       </c>
-      <c r="AZ314" s="5" t="n">
+      <c r="BA314" s="5" t="n">
         <v>1210</v>
-      </c>
-      <c r="BA314" s="5" t="n">
-        <v>1050</v>
       </c>
       <c r="BB314" s="5" t="n">
         <v>600</v>
@@ -84090,19 +84090,19 @@
       <c r="AU315" s="5"/>
       <c r="AV315" s="5"/>
       <c r="AW315" s="5" t="n">
+        <v>790</v>
+      </c>
+      <c r="AX315" s="5" t="n">
+        <v>1420</v>
+      </c>
+      <c r="AY315" s="5" t="n">
         <v>990</v>
       </c>
-      <c r="AX315" s="5" t="n">
-        <v>790</v>
-      </c>
-      <c r="AY315" s="5" t="n">
+      <c r="AZ315" s="5" t="n">
         <v>450</v>
       </c>
-      <c r="AZ315" s="5" t="n">
+      <c r="BA315" s="5" t="n">
         <v>1990</v>
-      </c>
-      <c r="BA315" s="5" t="n">
-        <v>1420</v>
       </c>
       <c r="BB315" s="5" t="n">
         <v>910</v>
@@ -84311,19 +84311,19 @@
       <c r="AU316" s="5"/>
       <c r="AV316" s="5"/>
       <c r="AW316" s="5" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AX316" s="5" t="n">
+        <v>2310</v>
+      </c>
+      <c r="AY316" s="5" t="n">
         <v>1610</v>
       </c>
-      <c r="AX316" s="5" t="n">
-        <v>1630</v>
-      </c>
-      <c r="AY316" s="5" t="n">
+      <c r="AZ316" s="5" t="n">
         <v>640</v>
       </c>
-      <c r="AZ316" s="5" t="n">
+      <c r="BA316" s="5" t="n">
         <v>2200</v>
-      </c>
-      <c r="BA316" s="5" t="n">
-        <v>2310</v>
       </c>
       <c r="BB316" s="5" t="n">
         <v>890</v>
@@ -84532,19 +84532,19 @@
       <c r="AU317" s="5"/>
       <c r="AV317" s="5"/>
       <c r="AW317" s="5" t="n">
+        <v>690</v>
+      </c>
+      <c r="AX317" s="5" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AY317" s="5" t="n">
         <v>750</v>
       </c>
-      <c r="AX317" s="5" t="n">
-        <v>690</v>
-      </c>
-      <c r="AY317" s="5" t="n">
+      <c r="AZ317" s="5" t="n">
         <v>340</v>
       </c>
-      <c r="AZ317" s="5" t="n">
+      <c r="BA317" s="5" t="n">
         <v>1980</v>
-      </c>
-      <c r="BA317" s="5" t="n">
-        <v>1990</v>
       </c>
       <c r="BB317" s="5" t="n">
         <v>880</v>
@@ -84710,7 +84710,7 @@
         <v>0.32</v>
       </c>
       <c r="AF318" s="5" t="n">
-        <v>9650</v>
+        <v>9640</v>
       </c>
       <c r="AG318" s="5" t="n">
         <v>4822</v>
@@ -84753,19 +84753,19 @@
       <c r="AU318" s="5"/>
       <c r="AV318" s="5"/>
       <c r="AW318" s="5" t="n">
+        <v>6370</v>
+      </c>
+      <c r="AX318" s="5" t="n">
+        <v>8380</v>
+      </c>
+      <c r="AY318" s="5" t="n">
         <v>5820</v>
       </c>
-      <c r="AX318" s="5" t="n">
-        <v>6370</v>
-      </c>
-      <c r="AY318" s="5" t="n">
+      <c r="AZ318" s="5" t="n">
         <v>2410</v>
       </c>
-      <c r="AZ318" s="5" t="n">
+      <c r="BA318" s="5" t="n">
         <v>7840</v>
-      </c>
-      <c r="BA318" s="5" t="n">
-        <v>8380</v>
       </c>
       <c r="BB318" s="5" t="n">
         <v>3280</v>
@@ -84974,19 +84974,19 @@
       <c r="AU319" s="7"/>
       <c r="AV319" s="7"/>
       <c r="AW319" s="7" t="n">
+        <v>1130</v>
+      </c>
+      <c r="AX319" s="7" t="n">
+        <v>1880</v>
+      </c>
+      <c r="AY319" s="7" t="n">
         <v>1380</v>
       </c>
-      <c r="AX319" s="7" t="n">
-        <v>1130</v>
-      </c>
-      <c r="AY319" s="7" t="n">
+      <c r="AZ319" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="AZ319" s="7" t="n">
+      <c r="BA319" s="7" t="n">
         <v>2190</v>
-      </c>
-      <c r="BA319" s="7" t="n">
-        <v>1880</v>
       </c>
       <c r="BB319" s="7" t="n">
         <v>1060</v>
